--- a/Results/noise_corrected/2_amp_function_by_season/calculations/storm3_results.xlsx
+++ b/Results/noise_corrected/2_amp_function_by_season/calculations/storm3_results.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\huck4481\Documents\GitHub\shear_stress_paper\Results\noise_corrected\2_amp_function_by_season\calculations\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4F37B2B-325C-4C76-8EF7-F9249C11368C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{843EADE8-54F1-4295-9AED-36F2E7478436}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{ACBE6CE9-2E59-4EB0-85F4-02C616FF90B4}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="49">
   <si>
     <t>max_amp</t>
   </si>
@@ -177,6 +177,9 @@
   </si>
   <si>
     <t>impact</t>
+  </si>
+  <si>
+    <t>max tau</t>
   </si>
 </sst>
 </file>
@@ -322,7 +325,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="33">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -502,6 +505,12 @@
         <bgColor indexed="65"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="10">
     <border>
@@ -663,7 +672,7 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -671,6 +680,9 @@
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="22" fontId="0" fillId="33" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="16" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -820,6 +832,653 @@
         <c:scatterStyle val="smoothMarker"/>
         <c:varyColors val="0"/>
         <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>storm3_results!$I$34</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>tau</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>storm3_results!$E$35:$E$131</c:f>
+              <c:numCache>
+                <c:formatCode>m/d/yyyy\ h:mm</c:formatCode>
+                <c:ptCount val="97"/>
+                <c:pt idx="0">
+                  <c:v>44781.000694444447</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>44781.011111111111</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>44781.021527777775</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>44781.031944444447</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>44781.042361111111</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>44781.052777777775</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>44781.063194444447</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>44781.073611111111</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>44781.084027777775</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>44781.094444444447</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>44781.104861111111</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>44781.115277777775</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>44781.125694444447</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>44781.136111111111</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>44781.146527777775</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>44781.156944444447</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>44781.167361111111</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>44781.177777777775</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>44781.188194444447</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>44781.198611111111</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>44781.209027777775</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>44781.219444444447</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>44781.229861111111</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>44781.240277777775</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>44781.250694444447</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>44781.261111111111</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>44781.271527777775</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>44781.281944444447</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>44781.292361111111</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>44781.302777777775</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>44781.313194444447</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>44781.323611111111</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>44781.334027777775</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>44781.344444444447</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>44781.354861111111</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>44781.365277777775</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>44781.375694444447</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>44781.386111111111</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>44781.396527777775</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>44781.406944444447</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>44781.417361111111</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>44781.427777777775</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>44781.438194444447</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>44781.448611111111</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>44781.459027777775</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>44781.469444444447</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>44781.479861111111</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>44781.490277777775</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>44781.500694444447</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>44781.511111111111</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>44781.521527777775</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>44781.531944444447</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>44781.542361111111</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>44781.552777777775</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>44781.563194444447</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>44781.573611111111</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>44781.584027777775</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>44781.594444444447</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>44781.604861111111</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>44781.615277777775</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>44781.625694444447</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>44781.636111111111</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>44781.646527777775</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>44781.656944444447</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>44781.667361111111</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>44781.677777777775</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>44781.688194444447</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>44781.698611111111</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>44781.709027777775</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>44781.719444444447</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>44781.729861111111</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>44781.740277777775</c:v>
+                </c:pt>
+                <c:pt idx="72">
+                  <c:v>44781.750694444447</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>44781.761111111111</c:v>
+                </c:pt>
+                <c:pt idx="74">
+                  <c:v>44781.771527777775</c:v>
+                </c:pt>
+                <c:pt idx="75">
+                  <c:v>44781.781944444447</c:v>
+                </c:pt>
+                <c:pt idx="76">
+                  <c:v>44781.792361111111</c:v>
+                </c:pt>
+                <c:pt idx="77">
+                  <c:v>44781.802777777775</c:v>
+                </c:pt>
+                <c:pt idx="78">
+                  <c:v>44781.813194444447</c:v>
+                </c:pt>
+                <c:pt idx="79">
+                  <c:v>44781.823611111111</c:v>
+                </c:pt>
+                <c:pt idx="80">
+                  <c:v>44781.834027777775</c:v>
+                </c:pt>
+                <c:pt idx="81">
+                  <c:v>44781.844444444447</c:v>
+                </c:pt>
+                <c:pt idx="82">
+                  <c:v>44781.854861111111</c:v>
+                </c:pt>
+                <c:pt idx="83">
+                  <c:v>44781.865277777775</c:v>
+                </c:pt>
+                <c:pt idx="84">
+                  <c:v>44781.875694444447</c:v>
+                </c:pt>
+                <c:pt idx="85">
+                  <c:v>44781.886111111111</c:v>
+                </c:pt>
+                <c:pt idx="86">
+                  <c:v>44781.896527777775</c:v>
+                </c:pt>
+                <c:pt idx="87">
+                  <c:v>44781.906944444447</c:v>
+                </c:pt>
+                <c:pt idx="88">
+                  <c:v>44781.917361111111</c:v>
+                </c:pt>
+                <c:pt idx="89">
+                  <c:v>44781.927777777775</c:v>
+                </c:pt>
+                <c:pt idx="90">
+                  <c:v>44781.938194444447</c:v>
+                </c:pt>
+                <c:pt idx="91">
+                  <c:v>44781.948611111111</c:v>
+                </c:pt>
+                <c:pt idx="92">
+                  <c:v>44781.959027777775</c:v>
+                </c:pt>
+                <c:pt idx="93">
+                  <c:v>44781.969444444447</c:v>
+                </c:pt>
+                <c:pt idx="94">
+                  <c:v>44781.979861111111</c:v>
+                </c:pt>
+                <c:pt idx="95">
+                  <c:v>44781.990277777775</c:v>
+                </c:pt>
+                <c:pt idx="96">
+                  <c:v>44782.000694444447</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>storm3_results!$I$35:$I$131</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="97"/>
+                <c:pt idx="0">
+                  <c:v>1.4441644075</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1.5123822984999999</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1.3533179835</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1.3056302835</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1.3930697775000001</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1.357638297</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>1.362681324</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>1.428025611</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>1.4664620669999999</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>1.3805518125</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>1.321577692</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>1.3305822285</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>1.3305822285</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>1.3962008465</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>1.4174729134999999</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>1.3100260825000001</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>1.2590209525</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>1.3008491654999901</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>1.3675681405</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>1.3727610129999901</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>1.3106306169999999</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>1.3304172409999999</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>1.2636095315</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>1.269803263</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>1.3586243874999999</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>1.3056302835</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>1.2676346135000001</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>1.2868847735</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>1.2461573855000001</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>1.2263406489999999</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>1.2605418435</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>1.2897381324999999</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>1.326867053</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>1.314942037</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>1.3033880545000001</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>1.2281127095</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>1.1599344165000001</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>1.1715929684999999</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>1.142992303</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>1.1391712730000001</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>1.126503907</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>1.1902769595</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>1.228492825</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>1.212618097</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>1.2029581084999901</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>1.1786703704999999</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>1.251653779</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>1.2937263295000001</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>1.1877777380000001</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>1.141804142</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>1.2578480294999901</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>1.3324552590000001</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>1.5909838079999901</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>2.1687506614999998</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>2.3007473825</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>3.2652481369999999</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>7.0573823745000004</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>13.5126390895</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>21.08342828</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>28.119352749999901</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>32.007500319999998</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>31.620971515000001</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>30.826982135000002</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>30.790400730000002</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>28.530895780000002</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>25.756546825000001</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>23.474647859999902</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>20.642438585000001</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>18.24147606</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>17.286459975</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>16.382398909999999</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>14.39848273</c:v>
+                </c:pt>
+                <c:pt idx="72">
+                  <c:v>15.218093735</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>13.768905965</c:v>
+                </c:pt>
+                <c:pt idx="74">
+                  <c:v>10.713533245000001</c:v>
+                </c:pt>
+                <c:pt idx="75">
+                  <c:v>10.73823973</c:v>
+                </c:pt>
+                <c:pt idx="76">
+                  <c:v>9.41508928649999</c:v>
+                </c:pt>
+                <c:pt idx="77">
+                  <c:v>9.5693059164999994</c:v>
+                </c:pt>
+                <c:pt idx="78">
+                  <c:v>10.085595189999999</c:v>
+                </c:pt>
+                <c:pt idx="79">
+                  <c:v>8.104838397</c:v>
+                </c:pt>
+                <c:pt idx="80">
+                  <c:v>7.0321962280000001</c:v>
+                </c:pt>
+                <c:pt idx="81">
+                  <c:v>7.4050236140000001</c:v>
+                </c:pt>
+                <c:pt idx="82">
+                  <c:v>6.3432970429999997</c:v>
+                </c:pt>
+                <c:pt idx="83">
+                  <c:v>4.9490583829999997</c:v>
+                </c:pt>
+                <c:pt idx="84">
+                  <c:v>6.3638281955</c:v>
+                </c:pt>
+                <c:pt idx="85">
+                  <c:v>6.4040720625000001</c:v>
+                </c:pt>
+                <c:pt idx="86">
+                  <c:v>5.2612970189999997</c:v>
+                </c:pt>
+                <c:pt idx="87">
+                  <c:v>5.4874552459999997</c:v>
+                </c:pt>
+                <c:pt idx="88">
+                  <c:v>5.2076250220000002</c:v>
+                </c:pt>
+                <c:pt idx="89">
+                  <c:v>4.6292118670000004</c:v>
+                </c:pt>
+                <c:pt idx="90">
+                  <c:v>3.8438540350000001</c:v>
+                </c:pt>
+                <c:pt idx="91">
+                  <c:v>3.4907628965000002</c:v>
+                </c:pt>
+                <c:pt idx="92">
+                  <c:v>3.5250784804999999</c:v>
+                </c:pt>
+                <c:pt idx="93">
+                  <c:v>3.3236783504999998</c:v>
+                </c:pt>
+                <c:pt idx="94">
+                  <c:v>3.2549971329999998</c:v>
+                </c:pt>
+                <c:pt idx="95">
+                  <c:v>3.3297358964999999</c:v>
+                </c:pt>
+                <c:pt idx="96">
+                  <c:v>3.3683360045000001</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{0000005F-A210-4D1D-959E-3D828588D8E8}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="389224783"/>
+        <c:axId val="389208463"/>
+      </c:scatterChart>
+      <c:scatterChart>
+        <c:scatterStyle val="smoothMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
           <c:idx val="0"/>
           <c:order val="0"/>
           <c:spPr>
@@ -1153,295 +1812,295 @@
                 <c:formatCode>0.00E+00</c:formatCode>
                 <c:ptCount val="97"/>
                 <c:pt idx="0">
-                  <c:v>2.08679206339447E-8</c:v>
+                  <c:v>2.14077559663646E-6</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>2.5067641795970801E-8</c:v>
+                  <c:v>2.4997227205869898E-6</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1.7594067479801701E-8</c:v>
+                  <c:v>1.8784160616638401E-6</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1.1520902210338401E-8</c:v>
+                  <c:v>1.25742647983648E-6</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>1.73181760643576E-8</c:v>
+                  <c:v>1.81636901898118E-6</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>1.3861372170813401E-8</c:v>
+                  <c:v>1.4770031895482E-6</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>1.7379699605599699E-8</c:v>
+                  <c:v>1.84768662190381E-6</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>1.9817270241934502E-8</c:v>
+                  <c:v>2.0470760564077801E-6</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>2.1170675392527701E-8</c:v>
+                  <c:v>2.1514884035535098E-6</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>1.7242505459809501E-8</c:v>
+                  <c:v>1.81848809218014E-6</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>1.35743675942321E-8</c:v>
+                  <c:v>1.4705399587400599E-6</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>1.4772012007367099E-8</c:v>
+                  <c:v>1.5936219159373299E-6</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>1.29305830131812E-8</c:v>
+                  <c:v>1.39496640440665E-6</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>1.5842012023537899E-8</c:v>
+                  <c:v>1.6592556871550001E-6</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>1.9850834029230498E-8</c:v>
+                  <c:v>2.0599074357341801E-6</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>1.16789922676441E-8</c:v>
+                  <c:v>1.27205172620107E-6</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>9.4925952184214506E-9</c:v>
+                  <c:v>1.05944687842148E-6</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>1.15248404721316E-8</c:v>
+                  <c:v>1.2606942762836699E-6</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>1.5013900722201999E-8</c:v>
+                  <c:v>1.5926654321992501E-6</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>1.4562433557529699E-8</c:v>
+                  <c:v>1.5411817469163499E-6</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>1.29347352580495E-8</c:v>
+                  <c:v>1.4084254359793501E-6</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>1.45156377391152E-8</c:v>
+                  <c:v>1.5660832533450999E-6</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>1.00612811281148E-8</c:v>
+                  <c:v>1.1204099402278601E-6</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>1.09222670926897E-8</c:v>
+                  <c:v>1.2126402176248E-6</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>1.30593320397655E-8</c:v>
+                  <c:v>1.39092101404772E-6</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>1.21468056690243E-8</c:v>
+                  <c:v>1.3257394963463501E-6</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>1.02844136122742E-8</c:v>
+                  <c:v>1.1430223827072299E-6</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>9.7416325055494695E-9</c:v>
+                  <c:v>1.0727190595649201E-6</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>1.14327944707451E-8</c:v>
+                  <c:v>1.28406330661959E-6</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>9.5267729720812402E-9</c:v>
+                  <c:v>1.0805788723734999E-6</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>9.9105736620194694E-9</c:v>
+                  <c:v>1.1052764951298499E-6</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>1.1091989786575401E-8</c:v>
+                  <c:v>1.21975563788356E-6</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>1.3062474946209101E-8</c:v>
+                  <c:v>1.41161759096376E-6</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>1.3348679805796E-8</c:v>
+                  <c:v>1.45056921071862E-6</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>1.18194980557907E-8</c:v>
+                  <c:v>1.2913789611719901E-6</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>1.06206101283769E-8</c:v>
+                  <c:v>1.20357981018381E-6</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>7.40609733328566E-9</c:v>
+                  <c:v>8.6926546504997798E-7</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>8.4461589863701507E-9</c:v>
+                  <c:v>9.852675059605111E-7</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>6.1974236192305796E-9</c:v>
+                  <c:v>7.34006066980003E-7</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>6.9174104480876099E-9</c:v>
+                  <c:v>8.2096638897698601E-7</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>6.32816515555179E-9</c:v>
+                  <c:v>7.5621079985491899E-7</c:v>
                 </c:pt>
                 <c:pt idx="41">
-                  <c:v>7.28540229665392E-9</c:v>
+                  <c:v>8.4164204860494604E-7</c:v>
                 </c:pt>
                 <c:pt idx="42">
-                  <c:v>1.0095850280173401E-8</c:v>
+                  <c:v>1.1438939623874601E-6</c:v>
                 </c:pt>
                 <c:pt idx="43">
-                  <c:v>8.7185632776942095E-9</c:v>
+                  <c:v>9.9576696049404601E-7</c:v>
                 </c:pt>
                 <c:pt idx="44">
-                  <c:v>8.34725172528678E-9</c:v>
+                  <c:v>9.580542360916839E-7</c:v>
                 </c:pt>
                 <c:pt idx="45">
-                  <c:v>7.4372115329053898E-9</c:v>
+                  <c:v>8.6436718894924899E-7</c:v>
                 </c:pt>
                 <c:pt idx="46">
-                  <c:v>9.9835595857672397E-9</c:v>
+                  <c:v>1.1182665401864501E-6</c:v>
                 </c:pt>
                 <c:pt idx="47">
-                  <c:v>1.1165384985735599E-8</c:v>
+                  <c:v>1.2255001677109701E-6</c:v>
                 </c:pt>
                 <c:pt idx="48">
-                  <c:v>6.9466293265400496E-9</c:v>
+                  <c:v>8.0354235413597698E-7</c:v>
                 </c:pt>
                 <c:pt idx="49">
-                  <c:v>6.8117547066147198E-9</c:v>
+                  <c:v>8.0728139075582595E-7</c:v>
                 </c:pt>
                 <c:pt idx="50">
-                  <c:v>1.0063859852835099E-8</c:v>
+                  <c:v>1.1238477036902599E-6</c:v>
                 </c:pt>
                 <c:pt idx="51">
-                  <c:v>1.2842809199053001E-8</c:v>
+                  <c:v>1.3843005327694501E-6</c:v>
                 </c:pt>
                 <c:pt idx="52">
-                  <c:v>3.5780196042316697E-8</c:v>
+                  <c:v>3.4586284454806899E-6</c:v>
                 </c:pt>
                 <c:pt idx="53">
-                  <c:v>1.30816767464494E-7</c:v>
+                  <c:v>1.04538029694326E-5</c:v>
                 </c:pt>
                 <c:pt idx="54">
-                  <c:v>1.5853121918232999E-7</c:v>
+                  <c:v>1.2216960823949901E-5</c:v>
                 </c:pt>
                 <c:pt idx="55">
-                  <c:v>5.9807526318119304E-7</c:v>
-                </c:pt>
-                <c:pt idx="56">
-                  <c:v>1.2616159790631901E-5</c:v>
+                  <c:v>3.7170773087333501E-5</c:v>
+                </c:pt>
+                <c:pt idx="56" formatCode="General">
+                  <c:v>4.8837098868093401E-4</c:v>
                 </c:pt>
                 <c:pt idx="57" formatCode="General">
-                  <c:v>2.05117605670511E-4</c:v>
+                  <c:v>5.3276258426810897E-3</c:v>
                 </c:pt>
                 <c:pt idx="58" formatCode="General">
-                  <c:v>1.63328311290035E-3</c:v>
+                  <c:v>3.2275768961475201E-2</c:v>
                 </c:pt>
                 <c:pt idx="59" formatCode="General">
-                  <c:v>6.7965607237199599E-3</c:v>
+                  <c:v>3.9279704565803299E-2</c:v>
                 </c:pt>
                 <c:pt idx="60" formatCode="General">
-                  <c:v>1.1009406946900099E-2</c:v>
+                  <c:v>3.6602438192205301E-2</c:v>
                 </c:pt>
                 <c:pt idx="61" formatCode="General">
-                  <c:v>8.9943480211758207E-3</c:v>
+                  <c:v>3.1495097104223102E-2</c:v>
                 </c:pt>
                 <c:pt idx="62" formatCode="General">
-                  <c:v>9.0417129480271693E-3</c:v>
+                  <c:v>3.5291894672967998E-2</c:v>
                 </c:pt>
                 <c:pt idx="63" formatCode="General">
-                  <c:v>7.9928147097117E-3</c:v>
+                  <c:v>3.1356353549068197E-2</c:v>
                 </c:pt>
                 <c:pt idx="64" formatCode="General">
-                  <c:v>5.4624617327883604E-3</c:v>
+                  <c:v>2.96706979468652E-2</c:v>
                 </c:pt>
                 <c:pt idx="65" formatCode="General">
-                  <c:v>3.2876564977182398E-3</c:v>
+                  <c:v>2.7637660054618599E-2</c:v>
                 </c:pt>
                 <c:pt idx="66" formatCode="General">
-                  <c:v>2.3816785486162899E-3</c:v>
+                  <c:v>2.9751022048612699E-2</c:v>
                 </c:pt>
                 <c:pt idx="67" formatCode="General">
-                  <c:v>1.2548875026224501E-3</c:v>
+                  <c:v>2.51241617425506E-2</c:v>
                 </c:pt>
                 <c:pt idx="68" formatCode="General">
-                  <c:v>6.8274708682035997E-4</c:v>
+                  <c:v>1.4748069683948499E-2</c:v>
                 </c:pt>
                 <c:pt idx="69" formatCode="General">
-                  <c:v>5.4547237763573103E-4</c:v>
+                  <c:v>1.2178516722712701E-2</c:v>
                 </c:pt>
                 <c:pt idx="70" formatCode="General">
-                  <c:v>4.5094874490155998E-4</c:v>
+                  <c:v>1.04058977869618E-2</c:v>
                 </c:pt>
                 <c:pt idx="71" formatCode="General">
-                  <c:v>2.8259038918480601E-4</c:v>
+                  <c:v>7.0590765229654401E-3</c:v>
                 </c:pt>
                 <c:pt idx="72" formatCode="General">
-                  <c:v>3.6428215953024698E-4</c:v>
+                  <c:v>8.7954581678172297E-3</c:v>
                 </c:pt>
                 <c:pt idx="73" formatCode="General">
-                  <c:v>1.99936701875895E-4</c:v>
-                </c:pt>
-                <c:pt idx="74">
-                  <c:v>7.2645406357815107E-5</c:v>
-                </c:pt>
-                <c:pt idx="75">
-                  <c:v>7.56159547780217E-5</c:v>
-                </c:pt>
-                <c:pt idx="76">
-                  <c:v>4.5464583434314597E-5</c:v>
-                </c:pt>
-                <c:pt idx="77">
-                  <c:v>4.915233559206E-5</c:v>
-                </c:pt>
-                <c:pt idx="78">
-                  <c:v>7.5285953536546199E-5</c:v>
-                </c:pt>
-                <c:pt idx="79">
-                  <c:v>2.36274514213945E-5</c:v>
-                </c:pt>
-                <c:pt idx="80">
-                  <c:v>1.30656236994048E-5</c:v>
-                </c:pt>
-                <c:pt idx="81">
-                  <c:v>1.62552722631288E-5</c:v>
-                </c:pt>
-                <c:pt idx="82">
-                  <c:v>8.4617179272708406E-6</c:v>
-                </c:pt>
-                <c:pt idx="83">
-                  <c:v>2.72060944319374E-6</c:v>
-                </c:pt>
-                <c:pt idx="84">
-                  <c:v>8.6198066168450707E-6</c:v>
-                </c:pt>
-                <c:pt idx="85">
-                  <c:v>9.8737680565131194E-6</c:v>
-                </c:pt>
-                <c:pt idx="86">
-                  <c:v>3.62543062105412E-6</c:v>
-                </c:pt>
-                <c:pt idx="87">
-                  <c:v>5.1770196379375703E-6</c:v>
-                </c:pt>
-                <c:pt idx="88">
-                  <c:v>4.1364578452331496E-6</c:v>
-                </c:pt>
-                <c:pt idx="89">
-                  <c:v>2.24225319101812E-6</c:v>
+                  <c:v>5.1334705034063403E-3</c:v>
+                </c:pt>
+                <c:pt idx="74" formatCode="General">
+                  <c:v>2.1760303881135801E-3</c:v>
+                </c:pt>
+                <c:pt idx="75" formatCode="General">
+                  <c:v>2.2618078613182899E-3</c:v>
+                </c:pt>
+                <c:pt idx="76" formatCode="General">
+                  <c:v>1.4743389202022299E-3</c:v>
+                </c:pt>
+                <c:pt idx="77" formatCode="General">
+                  <c:v>1.5780972943542301E-3</c:v>
+                </c:pt>
+                <c:pt idx="78" formatCode="General">
+                  <c:v>2.3403702735392499E-3</c:v>
+                </c:pt>
+                <c:pt idx="79" formatCode="General">
+                  <c:v>8.4007814809293003E-4</c:v>
+                </c:pt>
+                <c:pt idx="80" formatCode="General">
+                  <c:v>5.0688171603719496E-4</c:v>
+                </c:pt>
+                <c:pt idx="81" formatCode="General">
+                  <c:v>6.1092601709592399E-4</c:v>
+                </c:pt>
+                <c:pt idx="82" formatCode="General">
+                  <c:v>3.4973643501518302E-4</c:v>
+                </c:pt>
+                <c:pt idx="83" formatCode="General">
+                  <c:v>1.30968077187232E-4</c:v>
+                </c:pt>
+                <c:pt idx="84" formatCode="General">
+                  <c:v>3.5556397310524898E-4</c:v>
+                </c:pt>
+                <c:pt idx="85" formatCode="General">
+                  <c:v>4.0571525773627098E-4</c:v>
+                </c:pt>
+                <c:pt idx="86" formatCode="General">
+                  <c:v>1.68088015066737E-4</c:v>
+                </c:pt>
+                <c:pt idx="87" formatCode="General">
+                  <c:v>2.33899170623301E-4</c:v>
+                </c:pt>
+                <c:pt idx="88" formatCode="General">
+                  <c:v>1.92992886362459E-4</c:v>
+                </c:pt>
+                <c:pt idx="89" formatCode="General">
+                  <c:v>1.12462603863556E-4</c:v>
                 </c:pt>
                 <c:pt idx="90">
-                  <c:v>1.1273321181959501E-6</c:v>
+                  <c:v>6.3383183853455395E-5</c:v>
                 </c:pt>
                 <c:pt idx="91">
-                  <c:v>9.824868098894941E-7</c:v>
+                  <c:v>5.8607773952383203E-5</c:v>
                 </c:pt>
                 <c:pt idx="92">
-                  <c:v>7.1336422085263801E-7</c:v>
+                  <c:v>4.2298990704275399E-5</c:v>
                 </c:pt>
                 <c:pt idx="93">
-                  <c:v>6.4931726402399996E-7</c:v>
+                  <c:v>3.99181931276714E-5</c:v>
                 </c:pt>
                 <c:pt idx="94">
-                  <c:v>5.2154391813663602E-7</c:v>
+                  <c:v>3.2476970798245197E-5</c:v>
                 </c:pt>
                 <c:pt idx="95">
-                  <c:v>6.7490505910082797E-7</c:v>
+                  <c:v>4.1444873674415303E-5</c:v>
                 </c:pt>
                 <c:pt idx="96">
-                  <c:v>6.6541966892078898E-7</c:v>
+                  <c:v>4.0574092826454099E-5</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1461,8 +2120,8 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
-        <c:axId val="389224783"/>
-        <c:axId val="389208463"/>
+        <c:axId val="1366977728"/>
+        <c:axId val="1366974368"/>
       </c:scatterChart>
       <c:valAx>
         <c:axId val="389224783"/>
@@ -1547,7 +2206,7 @@
             <a:effectLst/>
           </c:spPr>
         </c:majorGridlines>
-        <c:numFmt formatCode="0.00E+00" sourceLinked="1"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -1586,6 +2245,69 @@
         </c:txPr>
         <c:crossAx val="389224783"/>
         <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="1366974368"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="r"/>
+        <c:numFmt formatCode="0.00E+00" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1366977728"/>
+        <c:crosses val="max"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="1366977728"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="1"/>
+        <c:axPos val="t"/>
+        <c:numFmt formatCode="m/d/yyyy\ h:mm" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="1366974368"/>
+        <c:crosses val="max"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:spPr>
@@ -2054,295 +2776,295 @@
                 <c:formatCode>0.00E+00</c:formatCode>
                 <c:ptCount val="97"/>
                 <c:pt idx="0">
-                  <c:v>1.45527826365573E-8</c:v>
+                  <c:v>1.4929250727909799E-6</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1.6993931409653301E-8</c:v>
+                  <c:v>1.6946195737918801E-6</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1.1110559936786401E-8</c:v>
+                  <c:v>1.18620974161767E-6</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>9.02844072250232E-9</c:v>
+                  <c:v>9.853916150734819E-7</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>1.22777388432218E-8</c:v>
+                  <c:v>1.2877166957693E-6</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>1.10118657841951E-8</c:v>
+                  <c:v>1.1733730749032101E-6</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>1.1343085245931999E-8</c:v>
+                  <c:v>1.20591651961942E-6</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>1.4062870728409799E-8</c:v>
+                  <c:v>1.45266051283058E-6</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>1.5825863676166399E-8</c:v>
+                  <c:v>1.60831723807426E-6</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>1.1932987192739699E-8</c:v>
+                  <c:v>1.2585175144562999E-6</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>9.9537092479160294E-9</c:v>
+                  <c:v>1.07830638037932E-6</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>1.02035026895234E-8</c:v>
+                  <c:v>1.10076579258197E-6</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>9.8920389735566796E-9</c:v>
+                  <c:v>1.06716472296785E-6</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>1.23195177617824E-8</c:v>
+                  <c:v>1.2903177878624699E-6</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>1.3024330135135601E-8</c:v>
+                  <c:v>1.35152580748439E-6</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>9.2950421705949502E-9</c:v>
+                  <c:v>1.01239680335182E-6</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>7.5348576440005792E-9</c:v>
+                  <c:v>8.4094825773544101E-7</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>8.7648104339019099E-9</c:v>
+                  <c:v>9.5877651179806307E-7</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>1.10856575200662E-8</c:v>
+                  <c:v>1.17595978900166E-6</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>1.0820789576809301E-8</c:v>
+                  <c:v>1.14519344017923E-6</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>9.0666964647597404E-9</c:v>
+                  <c:v>9.8724602139471102E-7</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>9.7350771525513093E-9</c:v>
+                  <c:v>1.0503115035420799E-6</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>7.5838404521162604E-9</c:v>
+                  <c:v>8.4452567414119498E-7</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>7.9258275182130999E-9</c:v>
+                  <c:v>8.7996174465338298E-7</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>1.04207326879707E-8</c:v>
+                  <c:v>1.10988954361902E-6</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>8.5784976215300098E-9</c:v>
+                  <c:v>9.36283449822881E-7</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>7.4158309200573703E-9</c:v>
+                  <c:v>8.2420457281510504E-7</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>7.8000359752117498E-9</c:v>
+                  <c:v>8.5891633166344501E-7</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>7.0828735794765198E-9</c:v>
+                  <c:v>7.9550612863448299E-7</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>6.4513988984525204E-9</c:v>
+                  <c:v>7.31753067631339E-7</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>7.2818728205971797E-9</c:v>
+                  <c:v>8.1211069547454604E-7</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>8.0462237070598607E-9</c:v>
+                  <c:v>8.8482111138416005E-7</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>9.1412830066434794E-9</c:v>
+                  <c:v>9.8786760923232295E-7</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>8.6644236888439392E-9</c:v>
+                  <c:v>9.4154226593322999E-7</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>8.1380588993041893E-9</c:v>
+                  <c:v>8.8915096036137399E-7</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>6.50727389293259E-9</c:v>
+                  <c:v>7.3743630377049103E-7</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>5.0829816647472298E-9</c:v>
+                  <c:v>5.96597671056019E-7</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>5.47000075402761E-9</c:v>
+                  <c:v>6.3809052244931604E-7</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>4.72799005264294E-9</c:v>
+                  <c:v>5.5997033548783296E-7</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>4.6877305286759502E-9</c:v>
+                  <c:v>5.5634535980222297E-7</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>4.6070326879360398E-9</c:v>
+                  <c:v>5.5053681253066602E-7</c:v>
                 </c:pt>
                 <c:pt idx="41">
-                  <c:v>5.7395984617146599E-9</c:v>
+                  <c:v>6.6306392026194604E-7</c:v>
                 </c:pt>
                 <c:pt idx="42">
-                  <c:v>6.4907686245721097E-9</c:v>
+                  <c:v>7.3542602501335596E-7</c:v>
                 </c:pt>
                 <c:pt idx="43">
-                  <c:v>6.3293531595371501E-9</c:v>
+                  <c:v>7.2288983366839196E-7</c:v>
                 </c:pt>
                 <c:pt idx="44">
-                  <c:v>5.9759176962636097E-9</c:v>
+                  <c:v>6.8588482196927205E-7</c:v>
                 </c:pt>
                 <c:pt idx="45">
-                  <c:v>5.5646273014940503E-9</c:v>
+                  <c:v>6.4673180759169101E-7</c:v>
                 </c:pt>
                 <c:pt idx="46">
-                  <c:v>7.0267352286048103E-9</c:v>
+                  <c:v>7.8707026541901097E-7</c:v>
                 </c:pt>
                 <c:pt idx="47">
-                  <c:v>8.1120448806285496E-9</c:v>
+                  <c:v>8.9036897286747204E-7</c:v>
                 </c:pt>
                 <c:pt idx="48">
-                  <c:v>5.7165196891903698E-9</c:v>
+                  <c:v>6.6125101436823698E-7</c:v>
                 </c:pt>
                 <c:pt idx="49">
-                  <c:v>4.6825188138704401E-9</c:v>
+                  <c:v>5.5493928704257195E-7</c:v>
                 </c:pt>
                 <c:pt idx="50">
-                  <c:v>6.84540696641487E-9</c:v>
+                  <c:v>7.6443780145253397E-7</c:v>
                 </c:pt>
                 <c:pt idx="51">
-                  <c:v>9.2656323176021903E-9</c:v>
+                  <c:v>9.9872384262512E-7</c:v>
                 </c:pt>
                 <c:pt idx="52">
-                  <c:v>2.3196453906791301E-8</c:v>
+                  <c:v>2.2422435925554199E-6</c:v>
                 </c:pt>
                 <c:pt idx="53">
-                  <c:v>1.00964698710095E-7</c:v>
+                  <c:v>8.0682705102349393E-6</c:v>
                 </c:pt>
                 <c:pt idx="54">
-                  <c:v>1.2432276051555401E-7</c:v>
+                  <c:v>9.5807393811041394E-6</c:v>
                 </c:pt>
                 <c:pt idx="55">
-                  <c:v>4.16410089823409E-7</c:v>
-                </c:pt>
-                <c:pt idx="56">
-                  <c:v>8.6544649020026392E-6</c:v>
+                  <c:v>2.5880162435940098E-5</c:v>
+                </c:pt>
+                <c:pt idx="56" formatCode="General">
+                  <c:v>3.3501395439016602E-4</c:v>
                 </c:pt>
                 <c:pt idx="57" formatCode="General">
-                  <c:v>1.63404252304588E-4</c:v>
+                  <c:v>4.2441833040826197E-3</c:v>
                 </c:pt>
                 <c:pt idx="58" formatCode="General">
-                  <c:v>1.25180167747011E-3</c:v>
+                  <c:v>2.4737206555507499E-2</c:v>
                 </c:pt>
                 <c:pt idx="59" formatCode="General">
-                  <c:v>4.4555820701342201E-3</c:v>
+                  <c:v>2.57503691198461E-2</c:v>
                 </c:pt>
                 <c:pt idx="60" formatCode="General">
-                  <c:v>7.9700859123076097E-3</c:v>
+                  <c:v>2.64977558191964E-2</c:v>
                 </c:pt>
                 <c:pt idx="61" formatCode="General">
-                  <c:v>7.3498348235841596E-3</c:v>
+                  <c:v>2.5736580452733099E-2</c:v>
                 </c:pt>
                 <c:pt idx="62" formatCode="General">
-                  <c:v>6.6699275342222402E-3</c:v>
+                  <c:v>2.6034268215854101E-2</c:v>
                 </c:pt>
                 <c:pt idx="63" formatCode="General">
-                  <c:v>6.3767171823644999E-3</c:v>
+                  <c:v>2.5016293472347899E-2</c:v>
                 </c:pt>
                 <c:pt idx="64" formatCode="General">
-                  <c:v>4.0903457913729997E-3</c:v>
+                  <c:v>2.22177143589136E-2</c:v>
                 </c:pt>
                 <c:pt idx="65" formatCode="General">
-                  <c:v>2.6058417642154902E-3</c:v>
+                  <c:v>2.1905989535808901E-2</c:v>
                 </c:pt>
                 <c:pt idx="66" formatCode="General">
-                  <c:v>1.65565535718085E-3</c:v>
+                  <c:v>2.06818166393531E-2</c:v>
                 </c:pt>
                 <c:pt idx="67" formatCode="General">
-                  <c:v>9.5942405127783501E-4</c:v>
+                  <c:v>1.9208674079211702E-2</c:v>
                 </c:pt>
                 <c:pt idx="68" formatCode="General">
-                  <c:v>5.2223097713969603E-4</c:v>
+                  <c:v>1.1280749475975099E-2</c:v>
                 </c:pt>
                 <c:pt idx="69" formatCode="General">
-                  <c:v>3.9229049757303399E-4</c:v>
+                  <c:v>8.7584937035885494E-3</c:v>
                 </c:pt>
                 <c:pt idx="70" formatCode="General">
-                  <c:v>2.9796641496116199E-4</c:v>
+                  <c:v>6.8757438469777997E-3</c:v>
                 </c:pt>
                 <c:pt idx="71" formatCode="General">
-                  <c:v>1.93269127027081E-4</c:v>
+                  <c:v>4.8278413188092397E-3</c:v>
                 </c:pt>
                 <c:pt idx="72" formatCode="General">
-                  <c:v>2.40544330247799E-4</c:v>
+                  <c:v>5.8078539913804404E-3</c:v>
                 </c:pt>
                 <c:pt idx="73" formatCode="General">
-                  <c:v>1.5881093547220399E-4</c:v>
-                </c:pt>
-                <c:pt idx="74">
-                  <c:v>5.0985964398630101E-5</c:v>
-                </c:pt>
-                <c:pt idx="75">
-                  <c:v>5.4033050677597897E-5</c:v>
-                </c:pt>
-                <c:pt idx="76">
-                  <c:v>2.93148134986538E-5</c:v>
-                </c:pt>
-                <c:pt idx="77">
-                  <c:v>3.2330376324374099E-5</c:v>
-                </c:pt>
-                <c:pt idx="78">
-                  <c:v>4.0580614477313299E-5</c:v>
-                </c:pt>
-                <c:pt idx="79">
-                  <c:v>1.5705980765168301E-5</c:v>
-                </c:pt>
-                <c:pt idx="80">
-                  <c:v>8.77531800676668E-6</c:v>
-                </c:pt>
-                <c:pt idx="81">
-                  <c:v>1.0637917979395899E-5</c:v>
-                </c:pt>
-                <c:pt idx="82">
-                  <c:v>5.7491088964468698E-6</c:v>
+                  <c:v>4.0775467696984903E-3</c:v>
+                </c:pt>
+                <c:pt idx="74" formatCode="General">
+                  <c:v>1.5272405161459201E-3</c:v>
+                </c:pt>
+                <c:pt idx="75" formatCode="General">
+                  <c:v>1.6162247656607599E-3</c:v>
+                </c:pt>
+                <c:pt idx="76" formatCode="General">
+                  <c:v>9.5062941778992205E-4</c:v>
+                </c:pt>
+                <c:pt idx="77" formatCode="General">
+                  <c:v>1.03800722362975E-3</c:v>
+                </c:pt>
+                <c:pt idx="78" formatCode="General">
+                  <c:v>1.26150575693274E-3</c:v>
+                </c:pt>
+                <c:pt idx="79" formatCode="General">
+                  <c:v>5.5842888002905898E-4</c:v>
+                </c:pt>
+                <c:pt idx="80" formatCode="General">
+                  <c:v>3.4043902934367798E-4</c:v>
+                </c:pt>
+                <c:pt idx="81" formatCode="General">
+                  <c:v>3.9980756742577403E-4</c:v>
+                </c:pt>
+                <c:pt idx="82" formatCode="General">
+                  <c:v>2.3761993335777101E-4</c:v>
                 </c:pt>
                 <c:pt idx="83">
-                  <c:v>1.9582358708784901E-6</c:v>
-                </c:pt>
-                <c:pt idx="84">
-                  <c:v>5.7685786368914701E-6</c:v>
-                </c:pt>
-                <c:pt idx="85">
-                  <c:v>6.1346768815599898E-6</c:v>
-                </c:pt>
-                <c:pt idx="86">
-                  <c:v>2.5855560562754599E-6</c:v>
-                </c:pt>
-                <c:pt idx="87">
-                  <c:v>3.1745913603245098E-6</c:v>
-                </c:pt>
-                <c:pt idx="88">
-                  <c:v>2.6973673674495002E-6</c:v>
+                  <c:v>9.4267991067419101E-5</c:v>
+                </c:pt>
+                <c:pt idx="84" formatCode="General">
+                  <c:v>2.3795182775074501E-4</c:v>
+                </c:pt>
+                <c:pt idx="85" formatCode="General">
+                  <c:v>2.5207519539712002E-4</c:v>
+                </c:pt>
+                <c:pt idx="86" formatCode="General">
+                  <c:v>1.1987568671669899E-4</c:v>
+                </c:pt>
+                <c:pt idx="87" formatCode="General">
+                  <c:v>1.43428910490146E-4</c:v>
+                </c:pt>
+                <c:pt idx="88" formatCode="General">
+                  <c:v>1.25849877671578E-4</c:v>
                 </c:pt>
                 <c:pt idx="89">
-                  <c:v>1.6233024868994E-6</c:v>
+                  <c:v>8.1418470166016497E-5</c:v>
                 </c:pt>
                 <c:pt idx="90">
-                  <c:v>7.4225391034485196E-7</c:v>
+                  <c:v>4.1732525229678299E-5</c:v>
                 </c:pt>
                 <c:pt idx="91">
-                  <c:v>5.0977265297958797E-7</c:v>
+                  <c:v>3.0409202559192099E-5</c:v>
                 </c:pt>
                 <c:pt idx="92">
-                  <c:v>4.9967568047369495E-7</c:v>
+                  <c:v>2.9628310960811101E-5</c:v>
                 </c:pt>
                 <c:pt idx="93">
-                  <c:v>4.11723051732112E-7</c:v>
+                  <c:v>2.5311571406873598E-5</c:v>
                 </c:pt>
                 <c:pt idx="94">
-                  <c:v>3.7467868921224398E-7</c:v>
+                  <c:v>2.3331551620226199E-5</c:v>
                 </c:pt>
                 <c:pt idx="95">
-                  <c:v>4.1927363607223701E-7</c:v>
+                  <c:v>2.5746944178216301E-5</c:v>
                 </c:pt>
                 <c:pt idx="96">
-                  <c:v>4.4769911489172599E-7</c:v>
+                  <c:v>2.72985399959777E-5</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2955,295 +3677,295 @@
                 <c:formatCode>0.00E+00</c:formatCode>
                 <c:ptCount val="97"/>
                 <c:pt idx="0">
-                  <c:v>1.44066128501846E-8</c:v>
+                  <c:v>1.4779299653656199E-6</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1.6481765230170301E-8</c:v>
+                  <c:v>1.6435468224834699E-6</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1.0702530073949501E-8</c:v>
+                  <c:v>1.14264677082452E-6</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>9.0574578898280608E-9</c:v>
+                  <c:v>9.8855863741516995E-7</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>1.1891434254351E-8</c:v>
+                  <c:v>1.2472002069378201E-6</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>1.0985248006165E-8</c:v>
+                  <c:v>1.1705368085730099E-6</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>1.12600482521935E-8</c:v>
+                  <c:v>1.19708861429105E-6</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>1.3347457715399E-8</c:v>
+                  <c:v>1.3787600799620401E-6</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>1.5436239139985899E-8</c:v>
+                  <c:v>1.5687213037949599E-6</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>1.17347870714543E-8</c:v>
+                  <c:v>1.2376142552989501E-6</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>9.7997015836837508E-9</c:v>
+                  <c:v>1.0616224043170001E-6</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>1.00688403114362E-8</c:v>
+                  <c:v>1.08623825787637E-6</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>9.9234654398772607E-9</c:v>
+                  <c:v>1.0705550468768499E-6</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>1.21883017770695E-8</c:v>
+                  <c:v>1.27657452922856E-6</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>1.2876765836887899E-8</c:v>
+                  <c:v>1.33621316143475E-6</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>9.2133237857039204E-9</c:v>
+                  <c:v>1.00349620557602E-6</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>7.5066093998211208E-9</c:v>
+                  <c:v>8.3779553569564503E-7</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>8.5507922259153799E-9</c:v>
+                  <c:v>9.3536520903741099E-7</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>1.09391693441101E-8</c:v>
+                  <c:v>1.16042041265386E-6</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>1.06373187943284E-8</c:v>
+                  <c:v>1.1257762308349501E-6</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>8.8524441629148807E-9</c:v>
+                  <c:v>9.6391671579346909E-7</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>9.7062286384277898E-9</c:v>
+                  <c:v>1.0471990550513799E-6</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>7.4776855701739697E-9</c:v>
+                  <c:v>8.3270441762491605E-7</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>7.9085810846291201E-9</c:v>
+                  <c:v>8.7804696645189198E-7</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>1.0275560333004301E-8</c:v>
+                  <c:v>1.0944275522444599E-6</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>8.4399986782839705E-9</c:v>
+                  <c:v>9.2116725185319497E-7</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>7.29414543896144E-9</c:v>
+                  <c:v>8.1068029874225203E-7</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>7.7577005294362308E-9</c:v>
+                  <c:v>8.5425448063396198E-7</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>6.9252956896037996E-9</c:v>
+                  <c:v>7.77807919599486E-7</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>6.4458549186617302E-9</c:v>
+                  <c:v>7.3112423901809603E-7</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>7.1496251672903197E-9</c:v>
+                  <c:v>7.9736177903651001E-7</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>7.9792300750312906E-9</c:v>
+                  <c:v>8.77454005778705E-7</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>9.06250368359216E-9</c:v>
+                  <c:v>9.79354193612616E-7</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>8.6454598933598705E-9</c:v>
+                  <c:v>9.3948151549147396E-7</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>7.8105278519879504E-9</c:v>
+                  <c:v>8.5336545562949604E-7</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>6.2437535947450096E-9</c:v>
+                  <c:v>7.07572886623624E-7</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>5.0427926111127498E-9</c:v>
+                  <c:v>5.9188061766892796E-7</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>5.3460048542051102E-9</c:v>
+                  <c:v>6.2362606218913202E-7</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>4.7060936602565104E-9</c:v>
+                  <c:v>5.5737698607944195E-7</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>4.5779079089452702E-9</c:v>
+                  <c:v>5.4331148243875702E-7</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>4.5918475828262896E-9</c:v>
+                  <c:v>5.4872220431175599E-7</c:v>
                 </c:pt>
                 <c:pt idx="41">
-                  <c:v>5.6509632883029799E-9</c:v>
+                  <c:v>6.5282439114532299E-7</c:v>
                 </c:pt>
                 <c:pt idx="42">
-                  <c:v>6.4023906307448604E-9</c:v>
+                  <c:v>7.25412499582329E-7</c:v>
                 </c:pt>
                 <c:pt idx="43">
-                  <c:v>6.15037878880983E-9</c:v>
+                  <c:v>7.0244876332904202E-7</c:v>
                 </c:pt>
                 <c:pt idx="44">
-                  <c:v>5.8063179443663297E-9</c:v>
+                  <c:v>6.6641904257258096E-7</c:v>
                 </c:pt>
                 <c:pt idx="45">
-                  <c:v>5.4778019322786803E-9</c:v>
+                  <c:v>6.36640794311264E-7</c:v>
                 </c:pt>
                 <c:pt idx="46">
-                  <c:v>6.89016388329679E-9</c:v>
+                  <c:v>7.7177279917421495E-7</c:v>
                 </c:pt>
                 <c:pt idx="47">
-                  <c:v>8.0238818322631193E-9</c:v>
+                  <c:v>8.8069229530340095E-7</c:v>
                 </c:pt>
                 <c:pt idx="48">
-                  <c:v>5.6674283648872199E-9</c:v>
+                  <c:v>6.5557243897037502E-7</c:v>
                 </c:pt>
                 <c:pt idx="49">
-                  <c:v>4.5132726888042003E-9</c:v>
+                  <c:v>5.3488142337848302E-7</c:v>
                 </c:pt>
                 <c:pt idx="50">
-                  <c:v>6.6806401961204599E-9</c:v>
+                  <c:v>7.4603802650363702E-7</c:v>
                 </c:pt>
                 <c:pt idx="51">
-                  <c:v>9.1296565686098997E-9</c:v>
+                  <c:v>9.840672905496551E-7</c:v>
                 </c:pt>
                 <c:pt idx="52">
-                  <c:v>2.3255763140541299E-8</c:v>
+                  <c:v>2.24797661320171E-6</c:v>
                 </c:pt>
                 <c:pt idx="53">
-                  <c:v>9.92270244525908E-8</c:v>
+                  <c:v>7.9294098377719094E-6</c:v>
                 </c:pt>
                 <c:pt idx="54">
-                  <c:v>1.2201232736340701E-7</c:v>
+                  <c:v>9.4026894584821297E-6</c:v>
                 </c:pt>
                 <c:pt idx="55">
-                  <c:v>4.0364332862755902E-7</c:v>
-                </c:pt>
-                <c:pt idx="56">
-                  <c:v>8.5031135066020596E-6</c:v>
+                  <c:v>2.5086699786166399E-5</c:v>
+                </c:pt>
+                <c:pt idx="56" formatCode="General">
+                  <c:v>3.2915514855592399E-4</c:v>
                 </c:pt>
                 <c:pt idx="57" formatCode="General">
-                  <c:v>1.6231017287086301E-4</c:v>
+                  <c:v>4.2157662121337898E-3</c:v>
                 </c:pt>
                 <c:pt idx="58" formatCode="General">
-                  <c:v>1.2599092890278999E-3</c:v>
+                  <c:v>2.48974233577593E-2</c:v>
                 </c:pt>
                 <c:pt idx="59" formatCode="General">
-                  <c:v>4.4166965562598198E-3</c:v>
+                  <c:v>2.5525636117230299E-2</c:v>
                 </c:pt>
                 <c:pt idx="60" formatCode="General">
-                  <c:v>7.8558091078931302E-3</c:v>
+                  <c:v>2.6117825302450701E-2</c:v>
                 </c:pt>
                 <c:pt idx="61" formatCode="General">
-                  <c:v>7.2506506127722097E-3</c:v>
+                  <c:v>2.5389271637974199E-2</c:v>
                 </c:pt>
                 <c:pt idx="62" formatCode="General">
-                  <c:v>6.5501312461542002E-3</c:v>
+                  <c:v>2.5566675625074E-2</c:v>
                 </c:pt>
                 <c:pt idx="63" formatCode="General">
-                  <c:v>6.2249847404091899E-3</c:v>
+                  <c:v>2.4421036823715402E-2</c:v>
                 </c:pt>
                 <c:pt idx="64" formatCode="General">
-                  <c:v>4.1186212620550897E-3</c:v>
+                  <c:v>2.2371299498981301E-2</c:v>
                 </c:pt>
                 <c:pt idx="65" formatCode="General">
-                  <c:v>2.60414846254545E-3</c:v>
+                  <c:v>2.1891754807669299E-2</c:v>
                 </c:pt>
                 <c:pt idx="66" formatCode="General">
-                  <c:v>1.6056248710924999E-3</c:v>
+                  <c:v>2.00568548468801E-2</c:v>
                 </c:pt>
                 <c:pt idx="67" formatCode="General">
-                  <c:v>9.4942941054271496E-4</c:v>
+                  <c:v>1.90085709066799E-2</c:v>
                 </c:pt>
                 <c:pt idx="68" formatCode="General">
-                  <c:v>5.1525208836084198E-4</c:v>
+                  <c:v>1.1129997989932999E-2</c:v>
                 </c:pt>
                 <c:pt idx="69" formatCode="General">
-                  <c:v>3.8322979368790101E-4</c:v>
+                  <c:v>8.5561994382844803E-3</c:v>
                 </c:pt>
                 <c:pt idx="70" formatCode="General">
-                  <c:v>2.9198288635133899E-4</c:v>
+                  <c:v>6.7376705341203897E-3</c:v>
                 </c:pt>
                 <c:pt idx="71" formatCode="General">
-                  <c:v>1.9338695347932401E-4</c:v>
+                  <c:v>4.8307846104402802E-3</c:v>
                 </c:pt>
                 <c:pt idx="72" formatCode="General">
-                  <c:v>2.35452156714537E-4</c:v>
+                  <c:v>5.6849053425008199E-3</c:v>
                 </c:pt>
                 <c:pt idx="73" formatCode="General">
-                  <c:v>1.58555042502395E-4</c:v>
-                </c:pt>
-                <c:pt idx="74">
-                  <c:v>5.0794349781337597E-5</c:v>
-                </c:pt>
-                <c:pt idx="75">
-                  <c:v>5.2433128207794903E-5</c:v>
-                </c:pt>
-                <c:pt idx="76">
-                  <c:v>2.9015048710938999E-5</c:v>
-                </c:pt>
-                <c:pt idx="77">
-                  <c:v>3.1594489524102599E-5</c:v>
-                </c:pt>
-                <c:pt idx="78">
-                  <c:v>3.9677423467233298E-5</c:v>
-                </c:pt>
-                <c:pt idx="79">
-                  <c:v>1.5279521577596499E-5</c:v>
-                </c:pt>
-                <c:pt idx="80">
-                  <c:v>8.7302394871148802E-6</c:v>
-                </c:pt>
-                <c:pt idx="81">
-                  <c:v>1.0440718273887999E-5</c:v>
-                </c:pt>
-                <c:pt idx="82">
-                  <c:v>5.73681912038392E-6</c:v>
+                  <c:v>4.0709765951558296E-3</c:v>
+                </c:pt>
+                <c:pt idx="74" formatCode="General">
+                  <c:v>1.52150086580679E-3</c:v>
+                </c:pt>
+                <c:pt idx="75" formatCode="General">
+                  <c:v>1.56836823553742E-3</c:v>
+                </c:pt>
+                <c:pt idx="76" formatCode="General">
+                  <c:v>9.40908556856773E-4</c:v>
+                </c:pt>
+                <c:pt idx="77" formatCode="General">
+                  <c:v>1.0143806562511099E-3</c:v>
+                </c:pt>
+                <c:pt idx="78" formatCode="General">
+                  <c:v>1.2334287878170301E-3</c:v>
+                </c:pt>
+                <c:pt idx="79" formatCode="General">
+                  <c:v>5.4326604938560198E-4</c:v>
+                </c:pt>
+                <c:pt idx="80" formatCode="General">
+                  <c:v>3.38690205260236E-4</c:v>
+                </c:pt>
+                <c:pt idx="81" formatCode="General">
+                  <c:v>3.9239616092214501E-4</c:v>
+                </c:pt>
+                <c:pt idx="82" formatCode="General">
+                  <c:v>2.37111977112796E-4</c:v>
                 </c:pt>
                 <c:pt idx="83">
-                  <c:v>1.9247524491630602E-6</c:v>
-                </c:pt>
-                <c:pt idx="84">
-                  <c:v>5.8546820975153499E-6</c:v>
-                </c:pt>
-                <c:pt idx="85">
-                  <c:v>6.2000553674498902E-6</c:v>
-                </c:pt>
-                <c:pt idx="86">
-                  <c:v>2.58084513039978E-6</c:v>
-                </c:pt>
-                <c:pt idx="87">
-                  <c:v>3.0173175094738999E-6</c:v>
-                </c:pt>
-                <c:pt idx="88">
-                  <c:v>2.66184554854633E-6</c:v>
+                  <c:v>9.2656124516474797E-5</c:v>
+                </c:pt>
+                <c:pt idx="84" formatCode="General">
+                  <c:v>2.4150356503508999E-4</c:v>
+                </c:pt>
+                <c:pt idx="85" formatCode="General">
+                  <c:v>2.54761611469434E-4</c:v>
+                </c:pt>
+                <c:pt idx="86" formatCode="General">
+                  <c:v>1.19657271234632E-4</c:v>
+                </c:pt>
+                <c:pt idx="87" formatCode="General">
+                  <c:v>1.36323234669229E-4</c:v>
+                </c:pt>
+                <c:pt idx="88" formatCode="General">
+                  <c:v>1.2419255185894699E-4</c:v>
                 </c:pt>
                 <c:pt idx="89">
-                  <c:v>1.59912114367056E-6</c:v>
+                  <c:v>8.0205629064744003E-5</c:v>
                 </c:pt>
                 <c:pt idx="90">
-                  <c:v>7.4792324404798199E-7</c:v>
+                  <c:v>4.20512781631517E-5</c:v>
                 </c:pt>
                 <c:pt idx="91">
-                  <c:v>5.07336801346938E-7</c:v>
+                  <c:v>3.0263897970125302E-5</c:v>
                 </c:pt>
                 <c:pt idx="92">
-                  <c:v>4.8813559378618197E-7</c:v>
+                  <c:v>2.8944040562241099E-5</c:v>
                 </c:pt>
                 <c:pt idx="93">
-                  <c:v>4.0816101818634101E-7</c:v>
+                  <c:v>2.50925876364046E-5</c:v>
                 </c:pt>
                 <c:pt idx="94">
-                  <c:v>3.6512831001573099E-7</c:v>
+                  <c:v>2.2736841615560799E-5</c:v>
                 </c:pt>
                 <c:pt idx="95">
-                  <c:v>4.0834177343066002E-7</c:v>
+                  <c:v>2.5075635436668602E-5</c:v>
                 </c:pt>
                 <c:pt idx="96">
-                  <c:v>4.44382696822977E-7</c:v>
+                  <c:v>2.7096320763431098E-5</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5114,16 +5836,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>152400</xdr:colOff>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>361950</xdr:colOff>
       <xdr:row>33</xdr:row>
-      <xdr:rowOff>38100</xdr:rowOff>
+      <xdr:rowOff>47625</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>17</xdr:col>
-      <xdr:colOff>247651</xdr:colOff>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>457201</xdr:colOff>
       <xdr:row>44</xdr:row>
-      <xdr:rowOff>66675</xdr:rowOff>
+      <xdr:rowOff>76200</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -5152,16 +5874,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>104774</xdr:colOff>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>314324</xdr:colOff>
       <xdr:row>46</xdr:row>
-      <xdr:rowOff>19050</xdr:rowOff>
+      <xdr:rowOff>28575</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>17</xdr:col>
-      <xdr:colOff>200025</xdr:colOff>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>409575</xdr:colOff>
       <xdr:row>57</xdr:row>
-      <xdr:rowOff>47625</xdr:rowOff>
+      <xdr:rowOff>57150</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -5190,16 +5912,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>114299</xdr:colOff>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>323849</xdr:colOff>
       <xdr:row>58</xdr:row>
-      <xdr:rowOff>171450</xdr:rowOff>
+      <xdr:rowOff>180975</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>17</xdr:col>
-      <xdr:colOff>209550</xdr:colOff>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>419100</xdr:colOff>
       <xdr:row>70</xdr:row>
-      <xdr:rowOff>19050</xdr:rowOff>
+      <xdr:rowOff>28575</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -5553,8 +6275,11 @@
     <col min="2" max="2" width="15.140625" customWidth="1"/>
     <col min="3" max="3" width="13.85546875" customWidth="1"/>
     <col min="5" max="5" width="12.85546875" customWidth="1"/>
+    <col min="25" max="25" width="13.5703125" bestFit="1" customWidth="1"/>
     <col min="54" max="54" width="13.7109375" customWidth="1"/>
     <col min="55" max="55" width="13.28515625" customWidth="1"/>
+    <col min="60" max="60" width="15.28515625" customWidth="1"/>
+    <col min="61" max="61" width="16.85546875" customWidth="1"/>
     <col min="63" max="63" width="16.28515625" customWidth="1"/>
   </cols>
   <sheetData>
@@ -5736,7 +6461,7 @@
       <c r="BH1" s="1">
         <v>44781.604861111111</v>
       </c>
-      <c r="BI1" s="1">
+      <c r="BI1" s="5">
         <v>44781.615277777775</v>
       </c>
       <c r="BJ1" s="1">
@@ -5856,295 +6581,295 @@
         <v>0</v>
       </c>
       <c r="B2" s="4">
-        <v>2.08679206339447E-8</v>
+        <v>2.14077559663646E-6</v>
       </c>
       <c r="C2" s="4">
-        <v>2.5067641795970801E-8</v>
+        <v>2.4997227205869898E-6</v>
       </c>
       <c r="D2" s="4">
-        <v>1.7594067479801701E-8</v>
+        <v>1.8784160616638401E-6</v>
       </c>
       <c r="E2" s="4">
-        <v>1.1520902210338401E-8</v>
+        <v>1.25742647983648E-6</v>
       </c>
       <c r="F2" s="4">
-        <v>1.73181760643576E-8</v>
+        <v>1.81636901898118E-6</v>
       </c>
       <c r="G2" s="4">
-        <v>1.3861372170813401E-8</v>
+        <v>1.4770031895482E-6</v>
       </c>
       <c r="H2" s="4">
-        <v>1.7379699605599699E-8</v>
+        <v>1.84768662190381E-6</v>
       </c>
       <c r="I2" s="4">
-        <v>1.9817270241934502E-8</v>
+        <v>2.0470760564077801E-6</v>
       </c>
       <c r="J2" s="4">
-        <v>2.1170675392527701E-8</v>
+        <v>2.1514884035535098E-6</v>
       </c>
       <c r="K2" s="4">
-        <v>1.7242505459809501E-8</v>
+        <v>1.81848809218014E-6</v>
       </c>
       <c r="L2" s="4">
-        <v>1.35743675942321E-8</v>
+        <v>1.4705399587400599E-6</v>
       </c>
       <c r="M2" s="4">
-        <v>1.4772012007367099E-8</v>
+        <v>1.5936219159373299E-6</v>
       </c>
       <c r="N2" s="4">
-        <v>1.29305830131812E-8</v>
+        <v>1.39496640440665E-6</v>
       </c>
       <c r="O2" s="4">
-        <v>1.5842012023537899E-8</v>
+        <v>1.6592556871550001E-6</v>
       </c>
       <c r="P2" s="4">
-        <v>1.9850834029230498E-8</v>
+        <v>2.0599074357341801E-6</v>
       </c>
       <c r="Q2" s="4">
-        <v>1.16789922676441E-8</v>
+        <v>1.27205172620107E-6</v>
       </c>
       <c r="R2" s="4">
-        <v>9.4925952184214506E-9</v>
+        <v>1.05944687842148E-6</v>
       </c>
       <c r="S2" s="4">
-        <v>1.15248404721316E-8</v>
+        <v>1.2606942762836699E-6</v>
       </c>
       <c r="T2" s="4">
-        <v>1.5013900722201999E-8</v>
+        <v>1.5926654321992501E-6</v>
       </c>
       <c r="U2" s="4">
-        <v>1.4562433557529699E-8</v>
+        <v>1.5411817469163499E-6</v>
       </c>
       <c r="V2" s="4">
-        <v>1.29347352580495E-8</v>
+        <v>1.4084254359793501E-6</v>
       </c>
       <c r="W2" s="4">
-        <v>1.45156377391152E-8</v>
+        <v>1.5660832533450999E-6</v>
       </c>
       <c r="X2" s="4">
-        <v>1.00612811281148E-8</v>
+        <v>1.1204099402278601E-6</v>
       </c>
       <c r="Y2" s="4">
-        <v>1.09222670926897E-8</v>
+        <v>1.2126402176248E-6</v>
       </c>
       <c r="Z2" s="4">
-        <v>1.30593320397655E-8</v>
+        <v>1.39092101404772E-6</v>
       </c>
       <c r="AA2" s="4">
-        <v>1.21468056690243E-8</v>
+        <v>1.3257394963463501E-6</v>
       </c>
       <c r="AB2" s="4">
-        <v>1.02844136122742E-8</v>
+        <v>1.1430223827072299E-6</v>
       </c>
       <c r="AC2" s="4">
-        <v>9.7416325055494695E-9</v>
+        <v>1.0727190595649201E-6</v>
       </c>
       <c r="AD2" s="4">
-        <v>1.14327944707451E-8</v>
+        <v>1.28406330661959E-6</v>
       </c>
       <c r="AE2" s="4">
-        <v>9.5267729720812402E-9</v>
+        <v>1.0805788723734999E-6</v>
       </c>
       <c r="AF2" s="4">
-        <v>9.9105736620194694E-9</v>
+        <v>1.1052764951298499E-6</v>
       </c>
       <c r="AG2" s="4">
-        <v>1.1091989786575401E-8</v>
+        <v>1.21975563788356E-6</v>
       </c>
       <c r="AH2" s="4">
-        <v>1.3062474946209101E-8</v>
+        <v>1.41161759096376E-6</v>
       </c>
       <c r="AI2" s="4">
-        <v>1.3348679805796E-8</v>
+        <v>1.45056921071862E-6</v>
       </c>
       <c r="AJ2" s="4">
-        <v>1.18194980557907E-8</v>
+        <v>1.2913789611719901E-6</v>
       </c>
       <c r="AK2" s="4">
-        <v>1.06206101283769E-8</v>
+        <v>1.20357981018381E-6</v>
       </c>
       <c r="AL2" s="4">
-        <v>7.40609733328566E-9</v>
+        <v>8.6926546504997798E-7</v>
       </c>
       <c r="AM2" s="4">
-        <v>8.4461589863701507E-9</v>
+        <v>9.852675059605111E-7</v>
       </c>
       <c r="AN2" s="4">
-        <v>6.1974236192305796E-9</v>
+        <v>7.34006066980003E-7</v>
       </c>
       <c r="AO2" s="4">
-        <v>6.9174104480876099E-9</v>
+        <v>8.2096638897698601E-7</v>
       </c>
       <c r="AP2" s="4">
-        <v>6.32816515555179E-9</v>
+        <v>7.5621079985491899E-7</v>
       </c>
       <c r="AQ2" s="4">
-        <v>7.28540229665392E-9</v>
+        <v>8.4164204860494604E-7</v>
       </c>
       <c r="AR2" s="4">
-        <v>1.0095850280173401E-8</v>
+        <v>1.1438939623874601E-6</v>
       </c>
       <c r="AS2" s="4">
-        <v>8.7185632776942095E-9</v>
+        <v>9.9576696049404601E-7</v>
       </c>
       <c r="AT2" s="4">
-        <v>8.34725172528678E-9</v>
+        <v>9.580542360916839E-7</v>
       </c>
       <c r="AU2" s="4">
-        <v>7.4372115329053898E-9</v>
+        <v>8.6436718894924899E-7</v>
       </c>
       <c r="AV2" s="4">
-        <v>9.9835595857672397E-9</v>
+        <v>1.1182665401864501E-6</v>
       </c>
       <c r="AW2" s="4">
-        <v>1.1165384985735599E-8</v>
+        <v>1.2255001677109701E-6</v>
       </c>
       <c r="AX2" s="4">
-        <v>6.9466293265400496E-9</v>
+        <v>8.0354235413597698E-7</v>
       </c>
       <c r="AY2" s="4">
-        <v>6.8117547066147198E-9</v>
+        <v>8.0728139075582595E-7</v>
       </c>
       <c r="AZ2" s="4">
-        <v>1.0063859852835099E-8</v>
+        <v>1.1238477036902599E-6</v>
       </c>
       <c r="BA2" s="4">
-        <v>1.2842809199053001E-8</v>
+        <v>1.3843005327694501E-6</v>
       </c>
       <c r="BB2" s="4">
-        <v>3.5780196042316697E-8</v>
+        <v>3.4586284454806899E-6</v>
       </c>
       <c r="BC2" s="4">
-        <v>1.30816767464494E-7</v>
+        <v>1.04538029694326E-5</v>
       </c>
       <c r="BD2" s="4">
-        <v>1.5853121918232999E-7</v>
+        <v>1.2216960823949901E-5</v>
       </c>
       <c r="BE2" s="4">
-        <v>5.9807526318119304E-7</v>
-      </c>
-      <c r="BF2" s="4">
-        <v>1.2616159790631901E-5</v>
+        <v>3.7170773087333501E-5</v>
+      </c>
+      <c r="BF2">
+        <v>4.8837098868093401E-4</v>
       </c>
       <c r="BG2">
-        <v>2.05117605670511E-4</v>
+        <v>5.3276258426810897E-3</v>
       </c>
       <c r="BH2">
-        <v>1.63328311290035E-3</v>
-      </c>
-      <c r="BI2">
-        <v>6.7965607237199599E-3</v>
+        <v>3.2275768961475201E-2</v>
+      </c>
+      <c r="BI2" s="6">
+        <v>3.9279704565803299E-2</v>
       </c>
       <c r="BJ2">
-        <v>1.1009406946900099E-2</v>
+        <v>3.6602438192205301E-2</v>
       </c>
       <c r="BK2">
-        <v>8.9943480211758207E-3</v>
+        <v>3.1495097104223102E-2</v>
       </c>
       <c r="BL2">
-        <v>9.0417129480271693E-3</v>
+        <v>3.5291894672967998E-2</v>
       </c>
       <c r="BM2">
-        <v>7.9928147097117E-3</v>
+        <v>3.1356353549068197E-2</v>
       </c>
       <c r="BN2">
-        <v>5.4624617327883604E-3</v>
+        <v>2.96706979468652E-2</v>
       </c>
       <c r="BO2">
-        <v>3.2876564977182398E-3</v>
+        <v>2.7637660054618599E-2</v>
       </c>
       <c r="BP2">
-        <v>2.3816785486162899E-3</v>
+        <v>2.9751022048612699E-2</v>
       </c>
       <c r="BQ2">
-        <v>1.2548875026224501E-3</v>
+        <v>2.51241617425506E-2</v>
       </c>
       <c r="BR2">
-        <v>6.8274708682035997E-4</v>
+        <v>1.4748069683948499E-2</v>
       </c>
       <c r="BS2">
-        <v>5.4547237763573103E-4</v>
+        <v>1.2178516722712701E-2</v>
       </c>
       <c r="BT2">
-        <v>4.5094874490155998E-4</v>
+        <v>1.04058977869618E-2</v>
       </c>
       <c r="BU2">
-        <v>2.8259038918480601E-4</v>
+        <v>7.0590765229654401E-3</v>
       </c>
       <c r="BV2">
-        <v>3.6428215953024698E-4</v>
+        <v>8.7954581678172297E-3</v>
       </c>
       <c r="BW2">
-        <v>1.99936701875895E-4</v>
-      </c>
-      <c r="BX2" s="4">
-        <v>7.2645406357815107E-5</v>
-      </c>
-      <c r="BY2" s="4">
-        <v>7.56159547780217E-5</v>
-      </c>
-      <c r="BZ2" s="4">
-        <v>4.5464583434314597E-5</v>
-      </c>
-      <c r="CA2" s="4">
-        <v>4.915233559206E-5</v>
-      </c>
-      <c r="CB2" s="4">
-        <v>7.5285953536546199E-5</v>
-      </c>
-      <c r="CC2" s="4">
-        <v>2.36274514213945E-5</v>
-      </c>
-      <c r="CD2" s="4">
-        <v>1.30656236994048E-5</v>
-      </c>
-      <c r="CE2" s="4">
-        <v>1.62552722631288E-5</v>
-      </c>
-      <c r="CF2" s="4">
-        <v>8.4617179272708406E-6</v>
-      </c>
-      <c r="CG2" s="4">
-        <v>2.72060944319374E-6</v>
-      </c>
-      <c r="CH2" s="4">
-        <v>8.6198066168450707E-6</v>
-      </c>
-      <c r="CI2" s="4">
-        <v>9.8737680565131194E-6</v>
-      </c>
-      <c r="CJ2" s="4">
-        <v>3.62543062105412E-6</v>
-      </c>
-      <c r="CK2" s="4">
-        <v>5.1770196379375703E-6</v>
-      </c>
-      <c r="CL2" s="4">
-        <v>4.1364578452331496E-6</v>
-      </c>
-      <c r="CM2" s="4">
-        <v>2.24225319101812E-6</v>
+        <v>5.1334705034063403E-3</v>
+      </c>
+      <c r="BX2">
+        <v>2.1760303881135801E-3</v>
+      </c>
+      <c r="BY2">
+        <v>2.2618078613182899E-3</v>
+      </c>
+      <c r="BZ2">
+        <v>1.4743389202022299E-3</v>
+      </c>
+      <c r="CA2">
+        <v>1.5780972943542301E-3</v>
+      </c>
+      <c r="CB2">
+        <v>2.3403702735392499E-3</v>
+      </c>
+      <c r="CC2">
+        <v>8.4007814809293003E-4</v>
+      </c>
+      <c r="CD2">
+        <v>5.0688171603719496E-4</v>
+      </c>
+      <c r="CE2">
+        <v>6.1092601709592399E-4</v>
+      </c>
+      <c r="CF2">
+        <v>3.4973643501518302E-4</v>
+      </c>
+      <c r="CG2">
+        <v>1.30968077187232E-4</v>
+      </c>
+      <c r="CH2">
+        <v>3.5556397310524898E-4</v>
+      </c>
+      <c r="CI2">
+        <v>4.0571525773627098E-4</v>
+      </c>
+      <c r="CJ2">
+        <v>1.68088015066737E-4</v>
+      </c>
+      <c r="CK2">
+        <v>2.33899170623301E-4</v>
+      </c>
+      <c r="CL2">
+        <v>1.92992886362459E-4</v>
+      </c>
+      <c r="CM2">
+        <v>1.12462603863556E-4</v>
       </c>
       <c r="CN2" s="4">
-        <v>1.1273321181959501E-6</v>
+        <v>6.3383183853455395E-5</v>
       </c>
       <c r="CO2" s="4">
-        <v>9.824868098894941E-7</v>
+        <v>5.8607773952383203E-5</v>
       </c>
       <c r="CP2" s="4">
-        <v>7.1336422085263801E-7</v>
+        <v>4.2298990704275399E-5</v>
       </c>
       <c r="CQ2" s="4">
-        <v>6.4931726402399996E-7</v>
+        <v>3.99181931276714E-5</v>
       </c>
       <c r="CR2" s="4">
-        <v>5.2154391813663602E-7</v>
+        <v>3.2476970798245197E-5</v>
       </c>
       <c r="CS2" s="4">
-        <v>6.7490505910082797E-7</v>
+        <v>4.1444873674415303E-5</v>
       </c>
       <c r="CT2" s="4">
-        <v>6.6541966892078898E-7</v>
+        <v>4.0574092826454099E-5</v>
       </c>
     </row>
     <row r="3" spans="1:98" x14ac:dyDescent="0.25">
@@ -6152,295 +6877,295 @@
         <v>1</v>
       </c>
       <c r="B3" s="4">
-        <v>1.45527826365573E-8</v>
+        <v>1.4929250727909799E-6</v>
       </c>
       <c r="C3" s="4">
-        <v>1.6993931409653301E-8</v>
+        <v>1.6946195737918801E-6</v>
       </c>
       <c r="D3" s="4">
-        <v>1.1110559936786401E-8</v>
+        <v>1.18620974161767E-6</v>
       </c>
       <c r="E3" s="4">
-        <v>9.02844072250232E-9</v>
+        <v>9.853916150734819E-7</v>
       </c>
       <c r="F3" s="4">
-        <v>1.22777388432218E-8</v>
+        <v>1.2877166957693E-6</v>
       </c>
       <c r="G3" s="4">
-        <v>1.10118657841951E-8</v>
+        <v>1.1733730749032101E-6</v>
       </c>
       <c r="H3" s="4">
-        <v>1.1343085245931999E-8</v>
+        <v>1.20591651961942E-6</v>
       </c>
       <c r="I3" s="4">
-        <v>1.4062870728409799E-8</v>
+        <v>1.45266051283058E-6</v>
       </c>
       <c r="J3" s="4">
-        <v>1.5825863676166399E-8</v>
+        <v>1.60831723807426E-6</v>
       </c>
       <c r="K3" s="4">
-        <v>1.1932987192739699E-8</v>
+        <v>1.2585175144562999E-6</v>
       </c>
       <c r="L3" s="4">
-        <v>9.9537092479160294E-9</v>
+        <v>1.07830638037932E-6</v>
       </c>
       <c r="M3" s="4">
-        <v>1.02035026895234E-8</v>
+        <v>1.10076579258197E-6</v>
       </c>
       <c r="N3" s="4">
-        <v>9.8920389735566796E-9</v>
+        <v>1.06716472296785E-6</v>
       </c>
       <c r="O3" s="4">
-        <v>1.23195177617824E-8</v>
+        <v>1.2903177878624699E-6</v>
       </c>
       <c r="P3" s="4">
-        <v>1.3024330135135601E-8</v>
+        <v>1.35152580748439E-6</v>
       </c>
       <c r="Q3" s="4">
-        <v>9.2950421705949502E-9</v>
+        <v>1.01239680335182E-6</v>
       </c>
       <c r="R3" s="4">
-        <v>7.5348576440005792E-9</v>
+        <v>8.4094825773544101E-7</v>
       </c>
       <c r="S3" s="4">
-        <v>8.7648104339019099E-9</v>
+        <v>9.5877651179806307E-7</v>
       </c>
       <c r="T3" s="4">
-        <v>1.10856575200662E-8</v>
+        <v>1.17595978900166E-6</v>
       </c>
       <c r="U3" s="4">
-        <v>1.0820789576809301E-8</v>
+        <v>1.14519344017923E-6</v>
       </c>
       <c r="V3" s="4">
-        <v>9.0666964647597404E-9</v>
+        <v>9.8724602139471102E-7</v>
       </c>
       <c r="W3" s="4">
-        <v>9.7350771525513093E-9</v>
+        <v>1.0503115035420799E-6</v>
       </c>
       <c r="X3" s="4">
-        <v>7.5838404521162604E-9</v>
+        <v>8.4452567414119498E-7</v>
       </c>
       <c r="Y3" s="4">
-        <v>7.9258275182130999E-9</v>
+        <v>8.7996174465338298E-7</v>
       </c>
       <c r="Z3" s="4">
-        <v>1.04207326879707E-8</v>
+        <v>1.10988954361902E-6</v>
       </c>
       <c r="AA3" s="4">
-        <v>8.5784976215300098E-9</v>
+        <v>9.36283449822881E-7</v>
       </c>
       <c r="AB3" s="4">
-        <v>7.4158309200573703E-9</v>
+        <v>8.2420457281510504E-7</v>
       </c>
       <c r="AC3" s="4">
-        <v>7.8000359752117498E-9</v>
+        <v>8.5891633166344501E-7</v>
       </c>
       <c r="AD3" s="4">
-        <v>7.0828735794765198E-9</v>
+        <v>7.9550612863448299E-7</v>
       </c>
       <c r="AE3" s="4">
-        <v>6.4513988984525204E-9</v>
+        <v>7.31753067631339E-7</v>
       </c>
       <c r="AF3" s="4">
-        <v>7.2818728205971797E-9</v>
+        <v>8.1211069547454604E-7</v>
       </c>
       <c r="AG3" s="4">
-        <v>8.0462237070598607E-9</v>
+        <v>8.8482111138416005E-7</v>
       </c>
       <c r="AH3" s="4">
-        <v>9.1412830066434794E-9</v>
+        <v>9.8786760923232295E-7</v>
       </c>
       <c r="AI3" s="4">
-        <v>8.6644236888439392E-9</v>
+        <v>9.4154226593322999E-7</v>
       </c>
       <c r="AJ3" s="4">
-        <v>8.1380588993041893E-9</v>
+        <v>8.8915096036137399E-7</v>
       </c>
       <c r="AK3" s="4">
-        <v>6.50727389293259E-9</v>
+        <v>7.3743630377049103E-7</v>
       </c>
       <c r="AL3" s="4">
-        <v>5.0829816647472298E-9</v>
+        <v>5.96597671056019E-7</v>
       </c>
       <c r="AM3" s="4">
-        <v>5.47000075402761E-9</v>
+        <v>6.3809052244931604E-7</v>
       </c>
       <c r="AN3" s="4">
-        <v>4.72799005264294E-9</v>
+        <v>5.5997033548783296E-7</v>
       </c>
       <c r="AO3" s="4">
-        <v>4.6877305286759502E-9</v>
+        <v>5.5634535980222297E-7</v>
       </c>
       <c r="AP3" s="4">
-        <v>4.6070326879360398E-9</v>
+        <v>5.5053681253066602E-7</v>
       </c>
       <c r="AQ3" s="4">
-        <v>5.7395984617146599E-9</v>
+        <v>6.6306392026194604E-7</v>
       </c>
       <c r="AR3" s="4">
-        <v>6.4907686245721097E-9</v>
+        <v>7.3542602501335596E-7</v>
       </c>
       <c r="AS3" s="4">
-        <v>6.3293531595371501E-9</v>
+        <v>7.2288983366839196E-7</v>
       </c>
       <c r="AT3" s="4">
-        <v>5.9759176962636097E-9</v>
+        <v>6.8588482196927205E-7</v>
       </c>
       <c r="AU3" s="4">
-        <v>5.5646273014940503E-9</v>
+        <v>6.4673180759169101E-7</v>
       </c>
       <c r="AV3" s="4">
-        <v>7.0267352286048103E-9</v>
+        <v>7.8707026541901097E-7</v>
       </c>
       <c r="AW3" s="4">
-        <v>8.1120448806285496E-9</v>
+        <v>8.9036897286747204E-7</v>
       </c>
       <c r="AX3" s="4">
-        <v>5.7165196891903698E-9</v>
+        <v>6.6125101436823698E-7</v>
       </c>
       <c r="AY3" s="4">
-        <v>4.6825188138704401E-9</v>
+        <v>5.5493928704257195E-7</v>
       </c>
       <c r="AZ3" s="4">
-        <v>6.84540696641487E-9</v>
+        <v>7.6443780145253397E-7</v>
       </c>
       <c r="BA3" s="4">
-        <v>9.2656323176021903E-9</v>
+        <v>9.9872384262512E-7</v>
       </c>
       <c r="BB3" s="4">
-        <v>2.3196453906791301E-8</v>
+        <v>2.2422435925554199E-6</v>
       </c>
       <c r="BC3" s="4">
-        <v>1.00964698710095E-7</v>
+        <v>8.0682705102349393E-6</v>
       </c>
       <c r="BD3" s="4">
-        <v>1.2432276051555401E-7</v>
+        <v>9.5807393811041394E-6</v>
       </c>
       <c r="BE3" s="4">
-        <v>4.16410089823409E-7</v>
-      </c>
-      <c r="BF3" s="4">
-        <v>8.6544649020026392E-6</v>
+        <v>2.5880162435940098E-5</v>
+      </c>
+      <c r="BF3">
+        <v>3.3501395439016602E-4</v>
       </c>
       <c r="BG3">
-        <v>1.63404252304588E-4</v>
+        <v>4.2441833040826197E-3</v>
       </c>
       <c r="BH3">
-        <v>1.25180167747011E-3</v>
-      </c>
-      <c r="BI3">
-        <v>4.4555820701342201E-3</v>
+        <v>2.4737206555507499E-2</v>
+      </c>
+      <c r="BI3" s="6">
+        <v>2.57503691198461E-2</v>
       </c>
       <c r="BJ3">
-        <v>7.9700859123076097E-3</v>
+        <v>2.64977558191964E-2</v>
       </c>
       <c r="BK3">
-        <v>7.3498348235841596E-3</v>
+        <v>2.5736580452733099E-2</v>
       </c>
       <c r="BL3">
-        <v>6.6699275342222402E-3</v>
+        <v>2.6034268215854101E-2</v>
       </c>
       <c r="BM3">
-        <v>6.3767171823644999E-3</v>
+        <v>2.5016293472347899E-2</v>
       </c>
       <c r="BN3">
-        <v>4.0903457913729997E-3</v>
+        <v>2.22177143589136E-2</v>
       </c>
       <c r="BO3">
-        <v>2.6058417642154902E-3</v>
+        <v>2.1905989535808901E-2</v>
       </c>
       <c r="BP3">
-        <v>1.65565535718085E-3</v>
+        <v>2.06818166393531E-2</v>
       </c>
       <c r="BQ3">
-        <v>9.5942405127783501E-4</v>
+        <v>1.9208674079211702E-2</v>
       </c>
       <c r="BR3">
-        <v>5.2223097713969603E-4</v>
+        <v>1.1280749475975099E-2</v>
       </c>
       <c r="BS3">
-        <v>3.9229049757303399E-4</v>
+        <v>8.7584937035885494E-3</v>
       </c>
       <c r="BT3">
-        <v>2.9796641496116199E-4</v>
+        <v>6.8757438469777997E-3</v>
       </c>
       <c r="BU3">
-        <v>1.93269127027081E-4</v>
+        <v>4.8278413188092397E-3</v>
       </c>
       <c r="BV3">
-        <v>2.40544330247799E-4</v>
+        <v>5.8078539913804404E-3</v>
       </c>
       <c r="BW3">
-        <v>1.5881093547220399E-4</v>
-      </c>
-      <c r="BX3" s="4">
-        <v>5.0985964398630101E-5</v>
-      </c>
-      <c r="BY3" s="4">
-        <v>5.4033050677597897E-5</v>
-      </c>
-      <c r="BZ3" s="4">
-        <v>2.93148134986538E-5</v>
-      </c>
-      <c r="CA3" s="4">
-        <v>3.2330376324374099E-5</v>
-      </c>
-      <c r="CB3" s="4">
-        <v>4.0580614477313299E-5</v>
-      </c>
-      <c r="CC3" s="4">
-        <v>1.5705980765168301E-5</v>
-      </c>
-      <c r="CD3" s="4">
-        <v>8.77531800676668E-6</v>
-      </c>
-      <c r="CE3" s="4">
-        <v>1.0637917979395899E-5</v>
-      </c>
-      <c r="CF3" s="4">
-        <v>5.7491088964468698E-6</v>
+        <v>4.0775467696984903E-3</v>
+      </c>
+      <c r="BX3">
+        <v>1.5272405161459201E-3</v>
+      </c>
+      <c r="BY3">
+        <v>1.6162247656607599E-3</v>
+      </c>
+      <c r="BZ3">
+        <v>9.5062941778992205E-4</v>
+      </c>
+      <c r="CA3">
+        <v>1.03800722362975E-3</v>
+      </c>
+      <c r="CB3">
+        <v>1.26150575693274E-3</v>
+      </c>
+      <c r="CC3">
+        <v>5.5842888002905898E-4</v>
+      </c>
+      <c r="CD3">
+        <v>3.4043902934367798E-4</v>
+      </c>
+      <c r="CE3">
+        <v>3.9980756742577403E-4</v>
+      </c>
+      <c r="CF3">
+        <v>2.3761993335777101E-4</v>
       </c>
       <c r="CG3" s="4">
-        <v>1.9582358708784901E-6</v>
-      </c>
-      <c r="CH3" s="4">
-        <v>5.7685786368914701E-6</v>
-      </c>
-      <c r="CI3" s="4">
-        <v>6.1346768815599898E-6</v>
-      </c>
-      <c r="CJ3" s="4">
-        <v>2.5855560562754599E-6</v>
-      </c>
-      <c r="CK3" s="4">
-        <v>3.1745913603245098E-6</v>
-      </c>
-      <c r="CL3" s="4">
-        <v>2.6973673674495002E-6</v>
+        <v>9.4267991067419101E-5</v>
+      </c>
+      <c r="CH3">
+        <v>2.3795182775074501E-4</v>
+      </c>
+      <c r="CI3">
+        <v>2.5207519539712002E-4</v>
+      </c>
+      <c r="CJ3">
+        <v>1.1987568671669899E-4</v>
+      </c>
+      <c r="CK3">
+        <v>1.43428910490146E-4</v>
+      </c>
+      <c r="CL3">
+        <v>1.25849877671578E-4</v>
       </c>
       <c r="CM3" s="4">
-        <v>1.6233024868994E-6</v>
+        <v>8.1418470166016497E-5</v>
       </c>
       <c r="CN3" s="4">
-        <v>7.4225391034485196E-7</v>
+        <v>4.1732525229678299E-5</v>
       </c>
       <c r="CO3" s="4">
-        <v>5.0977265297958797E-7</v>
+        <v>3.0409202559192099E-5</v>
       </c>
       <c r="CP3" s="4">
-        <v>4.9967568047369495E-7</v>
+        <v>2.9628310960811101E-5</v>
       </c>
       <c r="CQ3" s="4">
-        <v>4.11723051732112E-7</v>
+        <v>2.5311571406873598E-5</v>
       </c>
       <c r="CR3" s="4">
-        <v>3.7467868921224398E-7</v>
+        <v>2.3331551620226199E-5</v>
       </c>
       <c r="CS3" s="4">
-        <v>4.1927363607223701E-7</v>
+        <v>2.5746944178216301E-5</v>
       </c>
       <c r="CT3" s="4">
-        <v>4.4769911489172599E-7</v>
+        <v>2.72985399959777E-5</v>
       </c>
     </row>
     <row r="4" spans="1:98" x14ac:dyDescent="0.25">
@@ -6448,295 +7173,295 @@
         <v>2</v>
       </c>
       <c r="B4" s="4">
-        <v>1.44066128501846E-8</v>
+        <v>1.4779299653656199E-6</v>
       </c>
       <c r="C4" s="4">
-        <v>1.6481765230170301E-8</v>
+        <v>1.6435468224834699E-6</v>
       </c>
       <c r="D4" s="4">
-        <v>1.0702530073949501E-8</v>
+        <v>1.14264677082452E-6</v>
       </c>
       <c r="E4" s="4">
-        <v>9.0574578898280608E-9</v>
+        <v>9.8855863741516995E-7</v>
       </c>
       <c r="F4" s="4">
-        <v>1.1891434254351E-8</v>
+        <v>1.2472002069378201E-6</v>
       </c>
       <c r="G4" s="4">
-        <v>1.0985248006165E-8</v>
+        <v>1.1705368085730099E-6</v>
       </c>
       <c r="H4" s="4">
-        <v>1.12600482521935E-8</v>
+        <v>1.19708861429105E-6</v>
       </c>
       <c r="I4" s="4">
-        <v>1.3347457715399E-8</v>
+        <v>1.3787600799620401E-6</v>
       </c>
       <c r="J4" s="4">
-        <v>1.5436239139985899E-8</v>
+        <v>1.5687213037949599E-6</v>
       </c>
       <c r="K4" s="4">
-        <v>1.17347870714543E-8</v>
+        <v>1.2376142552989501E-6</v>
       </c>
       <c r="L4" s="4">
-        <v>9.7997015836837508E-9</v>
+        <v>1.0616224043170001E-6</v>
       </c>
       <c r="M4" s="4">
-        <v>1.00688403114362E-8</v>
+        <v>1.08623825787637E-6</v>
       </c>
       <c r="N4" s="4">
-        <v>9.9234654398772607E-9</v>
+        <v>1.0705550468768499E-6</v>
       </c>
       <c r="O4" s="4">
-        <v>1.21883017770695E-8</v>
+        <v>1.27657452922856E-6</v>
       </c>
       <c r="P4" s="4">
-        <v>1.2876765836887899E-8</v>
+        <v>1.33621316143475E-6</v>
       </c>
       <c r="Q4" s="4">
-        <v>9.2133237857039204E-9</v>
+        <v>1.00349620557602E-6</v>
       </c>
       <c r="R4" s="4">
-        <v>7.5066093998211208E-9</v>
+        <v>8.3779553569564503E-7</v>
       </c>
       <c r="S4" s="4">
-        <v>8.5507922259153799E-9</v>
+        <v>9.3536520903741099E-7</v>
       </c>
       <c r="T4" s="4">
-        <v>1.09391693441101E-8</v>
+        <v>1.16042041265386E-6</v>
       </c>
       <c r="U4" s="4">
-        <v>1.06373187943284E-8</v>
+        <v>1.1257762308349501E-6</v>
       </c>
       <c r="V4" s="4">
-        <v>8.8524441629148807E-9</v>
+        <v>9.6391671579346909E-7</v>
       </c>
       <c r="W4" s="4">
-        <v>9.7062286384277898E-9</v>
+        <v>1.0471990550513799E-6</v>
       </c>
       <c r="X4" s="4">
-        <v>7.4776855701739697E-9</v>
+        <v>8.3270441762491605E-7</v>
       </c>
       <c r="Y4" s="4">
-        <v>7.9085810846291201E-9</v>
+        <v>8.7804696645189198E-7</v>
       </c>
       <c r="Z4" s="4">
-        <v>1.0275560333004301E-8</v>
+        <v>1.0944275522444599E-6</v>
       </c>
       <c r="AA4" s="4">
-        <v>8.4399986782839705E-9</v>
+        <v>9.2116725185319497E-7</v>
       </c>
       <c r="AB4" s="4">
-        <v>7.29414543896144E-9</v>
+        <v>8.1068029874225203E-7</v>
       </c>
       <c r="AC4" s="4">
-        <v>7.7577005294362308E-9</v>
+        <v>8.5425448063396198E-7</v>
       </c>
       <c r="AD4" s="4">
-        <v>6.9252956896037996E-9</v>
+        <v>7.77807919599486E-7</v>
       </c>
       <c r="AE4" s="4">
-        <v>6.4458549186617302E-9</v>
+        <v>7.3112423901809603E-7</v>
       </c>
       <c r="AF4" s="4">
-        <v>7.1496251672903197E-9</v>
+        <v>7.9736177903651001E-7</v>
       </c>
       <c r="AG4" s="4">
-        <v>7.9792300750312906E-9</v>
+        <v>8.77454005778705E-7</v>
       </c>
       <c r="AH4" s="4">
-        <v>9.06250368359216E-9</v>
+        <v>9.79354193612616E-7</v>
       </c>
       <c r="AI4" s="4">
-        <v>8.6454598933598705E-9</v>
+        <v>9.3948151549147396E-7</v>
       </c>
       <c r="AJ4" s="4">
-        <v>7.8105278519879504E-9</v>
+        <v>8.5336545562949604E-7</v>
       </c>
       <c r="AK4" s="4">
-        <v>6.2437535947450096E-9</v>
+        <v>7.07572886623624E-7</v>
       </c>
       <c r="AL4" s="4">
-        <v>5.0427926111127498E-9</v>
+        <v>5.9188061766892796E-7</v>
       </c>
       <c r="AM4" s="4">
-        <v>5.3460048542051102E-9</v>
+        <v>6.2362606218913202E-7</v>
       </c>
       <c r="AN4" s="4">
-        <v>4.7060936602565104E-9</v>
+        <v>5.5737698607944195E-7</v>
       </c>
       <c r="AO4" s="4">
-        <v>4.5779079089452702E-9</v>
+        <v>5.4331148243875702E-7</v>
       </c>
       <c r="AP4" s="4">
-        <v>4.5918475828262896E-9</v>
+        <v>5.4872220431175599E-7</v>
       </c>
       <c r="AQ4" s="4">
-        <v>5.6509632883029799E-9</v>
+        <v>6.5282439114532299E-7</v>
       </c>
       <c r="AR4" s="4">
-        <v>6.4023906307448604E-9</v>
+        <v>7.25412499582329E-7</v>
       </c>
       <c r="AS4" s="4">
-        <v>6.15037878880983E-9</v>
+        <v>7.0244876332904202E-7</v>
       </c>
       <c r="AT4" s="4">
-        <v>5.8063179443663297E-9</v>
+        <v>6.6641904257258096E-7</v>
       </c>
       <c r="AU4" s="4">
-        <v>5.4778019322786803E-9</v>
+        <v>6.36640794311264E-7</v>
       </c>
       <c r="AV4" s="4">
-        <v>6.89016388329679E-9</v>
+        <v>7.7177279917421495E-7</v>
       </c>
       <c r="AW4" s="4">
-        <v>8.0238818322631193E-9</v>
+        <v>8.8069229530340095E-7</v>
       </c>
       <c r="AX4" s="4">
-        <v>5.6674283648872199E-9</v>
+        <v>6.5557243897037502E-7</v>
       </c>
       <c r="AY4" s="4">
-        <v>4.5132726888042003E-9</v>
+        <v>5.3488142337848302E-7</v>
       </c>
       <c r="AZ4" s="4">
-        <v>6.6806401961204599E-9</v>
+        <v>7.4603802650363702E-7</v>
       </c>
       <c r="BA4" s="4">
-        <v>9.1296565686098997E-9</v>
+        <v>9.840672905496551E-7</v>
       </c>
       <c r="BB4" s="4">
-        <v>2.3255763140541299E-8</v>
+        <v>2.24797661320171E-6</v>
       </c>
       <c r="BC4" s="4">
-        <v>9.92270244525908E-8</v>
+        <v>7.9294098377719094E-6</v>
       </c>
       <c r="BD4" s="4">
-        <v>1.2201232736340701E-7</v>
+        <v>9.4026894584821297E-6</v>
       </c>
       <c r="BE4" s="4">
-        <v>4.0364332862755902E-7</v>
-      </c>
-      <c r="BF4" s="4">
-        <v>8.5031135066020596E-6</v>
+        <v>2.5086699786166399E-5</v>
+      </c>
+      <c r="BF4">
+        <v>3.2915514855592399E-4</v>
       </c>
       <c r="BG4">
-        <v>1.6231017287086301E-4</v>
+        <v>4.2157662121337898E-3</v>
       </c>
       <c r="BH4">
-        <v>1.2599092890278999E-3</v>
-      </c>
-      <c r="BI4">
-        <v>4.4166965562598198E-3</v>
+        <v>2.48974233577593E-2</v>
+      </c>
+      <c r="BI4" s="6">
+        <v>2.5525636117230299E-2</v>
       </c>
       <c r="BJ4">
-        <v>7.8558091078931302E-3</v>
+        <v>2.6117825302450701E-2</v>
       </c>
       <c r="BK4">
-        <v>7.2506506127722097E-3</v>
+        <v>2.5389271637974199E-2</v>
       </c>
       <c r="BL4">
-        <v>6.5501312461542002E-3</v>
+        <v>2.5566675625074E-2</v>
       </c>
       <c r="BM4">
-        <v>6.2249847404091899E-3</v>
+        <v>2.4421036823715402E-2</v>
       </c>
       <c r="BN4">
-        <v>4.1186212620550897E-3</v>
+        <v>2.2371299498981301E-2</v>
       </c>
       <c r="BO4">
-        <v>2.60414846254545E-3</v>
+        <v>2.1891754807669299E-2</v>
       </c>
       <c r="BP4">
-        <v>1.6056248710924999E-3</v>
+        <v>2.00568548468801E-2</v>
       </c>
       <c r="BQ4">
-        <v>9.4942941054271496E-4</v>
+        <v>1.90085709066799E-2</v>
       </c>
       <c r="BR4">
-        <v>5.1525208836084198E-4</v>
+        <v>1.1129997989932999E-2</v>
       </c>
       <c r="BS4">
-        <v>3.8322979368790101E-4</v>
+        <v>8.5561994382844803E-3</v>
       </c>
       <c r="BT4">
-        <v>2.9198288635133899E-4</v>
+        <v>6.7376705341203897E-3</v>
       </c>
       <c r="BU4">
-        <v>1.9338695347932401E-4</v>
+        <v>4.8307846104402802E-3</v>
       </c>
       <c r="BV4">
-        <v>2.35452156714537E-4</v>
+        <v>5.6849053425008199E-3</v>
       </c>
       <c r="BW4">
-        <v>1.58555042502395E-4</v>
-      </c>
-      <c r="BX4" s="4">
-        <v>5.0794349781337597E-5</v>
-      </c>
-      <c r="BY4" s="4">
-        <v>5.2433128207794903E-5</v>
-      </c>
-      <c r="BZ4" s="4">
-        <v>2.9015048710938999E-5</v>
-      </c>
-      <c r="CA4" s="4">
-        <v>3.1594489524102599E-5</v>
-      </c>
-      <c r="CB4" s="4">
-        <v>3.9677423467233298E-5</v>
-      </c>
-      <c r="CC4" s="4">
-        <v>1.5279521577596499E-5</v>
-      </c>
-      <c r="CD4" s="4">
-        <v>8.7302394871148802E-6</v>
-      </c>
-      <c r="CE4" s="4">
-        <v>1.0440718273887999E-5</v>
-      </c>
-      <c r="CF4" s="4">
-        <v>5.73681912038392E-6</v>
+        <v>4.0709765951558296E-3</v>
+      </c>
+      <c r="BX4">
+        <v>1.52150086580679E-3</v>
+      </c>
+      <c r="BY4">
+        <v>1.56836823553742E-3</v>
+      </c>
+      <c r="BZ4">
+        <v>9.40908556856773E-4</v>
+      </c>
+      <c r="CA4">
+        <v>1.0143806562511099E-3</v>
+      </c>
+      <c r="CB4">
+        <v>1.2334287878170301E-3</v>
+      </c>
+      <c r="CC4">
+        <v>5.4326604938560198E-4</v>
+      </c>
+      <c r="CD4">
+        <v>3.38690205260236E-4</v>
+      </c>
+      <c r="CE4">
+        <v>3.9239616092214501E-4</v>
+      </c>
+      <c r="CF4">
+        <v>2.37111977112796E-4</v>
       </c>
       <c r="CG4" s="4">
-        <v>1.9247524491630602E-6</v>
-      </c>
-      <c r="CH4" s="4">
-        <v>5.8546820975153499E-6</v>
-      </c>
-      <c r="CI4" s="4">
-        <v>6.2000553674498902E-6</v>
-      </c>
-      <c r="CJ4" s="4">
-        <v>2.58084513039978E-6</v>
-      </c>
-      <c r="CK4" s="4">
-        <v>3.0173175094738999E-6</v>
-      </c>
-      <c r="CL4" s="4">
-        <v>2.66184554854633E-6</v>
+        <v>9.2656124516474797E-5</v>
+      </c>
+      <c r="CH4">
+        <v>2.4150356503508999E-4</v>
+      </c>
+      <c r="CI4">
+        <v>2.54761611469434E-4</v>
+      </c>
+      <c r="CJ4">
+        <v>1.19657271234632E-4</v>
+      </c>
+      <c r="CK4">
+        <v>1.36323234669229E-4</v>
+      </c>
+      <c r="CL4">
+        <v>1.2419255185894699E-4</v>
       </c>
       <c r="CM4" s="4">
-        <v>1.59912114367056E-6</v>
+        <v>8.0205629064744003E-5</v>
       </c>
       <c r="CN4" s="4">
-        <v>7.4792324404798199E-7</v>
+        <v>4.20512781631517E-5</v>
       </c>
       <c r="CO4" s="4">
-        <v>5.07336801346938E-7</v>
+        <v>3.0263897970125302E-5</v>
       </c>
       <c r="CP4" s="4">
-        <v>4.8813559378618197E-7</v>
+        <v>2.8944040562241099E-5</v>
       </c>
       <c r="CQ4" s="4">
-        <v>4.0816101818634101E-7</v>
+        <v>2.50925876364046E-5</v>
       </c>
       <c r="CR4" s="4">
-        <v>3.6512831001573099E-7</v>
+        <v>2.2736841615560799E-5</v>
       </c>
       <c r="CS4" s="4">
-        <v>4.0834177343066002E-7</v>
+        <v>2.5075635436668602E-5</v>
       </c>
       <c r="CT4" s="4">
-        <v>4.44382696822977E-7</v>
+        <v>2.7096320763431098E-5</v>
       </c>
     </row>
     <row r="5" spans="1:98" x14ac:dyDescent="0.25">
@@ -6920,7 +7645,7 @@
       <c r="BH5">
         <v>0</v>
       </c>
-      <c r="BI5">
+      <c r="BI5" s="6">
         <v>0</v>
       </c>
       <c r="BJ5">
@@ -7214,34 +7939,34 @@
         <v>0</v>
       </c>
       <c r="BH6">
-        <v>0</v>
-      </c>
-      <c r="BI6">
-        <v>0</v>
+        <v>5</v>
+      </c>
+      <c r="BI6" s="6">
+        <v>7</v>
       </c>
       <c r="BJ6">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BK6">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="BL6">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="BM6">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="BN6">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="BO6">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BP6">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BQ6">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="BR6">
         <v>0</v>
@@ -7256,7 +7981,7 @@
         <v>0</v>
       </c>
       <c r="BV6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BW6">
         <v>0</v>
@@ -7510,49 +8235,49 @@
         <v>0</v>
       </c>
       <c r="BH7">
-        <v>0</v>
-      </c>
-      <c r="BI7">
-        <v>1</v>
+        <v>401</v>
+      </c>
+      <c r="BI7" s="6">
+        <v>570</v>
       </c>
       <c r="BJ7">
-        <v>5</v>
+        <v>631</v>
       </c>
       <c r="BK7">
-        <v>17</v>
+        <v>637</v>
       </c>
       <c r="BL7">
+        <v>753</v>
+      </c>
+      <c r="BM7">
+        <v>599</v>
+      </c>
+      <c r="BN7">
+        <v>403</v>
+      </c>
+      <c r="BO7">
+        <v>421</v>
+      </c>
+      <c r="BP7">
+        <v>426</v>
+      </c>
+      <c r="BQ7">
+        <v>292</v>
+      </c>
+      <c r="BR7">
+        <v>46</v>
+      </c>
+      <c r="BS7">
+        <v>22</v>
+      </c>
+      <c r="BT7">
+        <v>25</v>
+      </c>
+      <c r="BU7">
+        <v>4</v>
+      </c>
+      <c r="BV7">
         <v>11</v>
-      </c>
-      <c r="BM7">
-        <v>11</v>
-      </c>
-      <c r="BN7">
-        <v>2</v>
-      </c>
-      <c r="BO7">
-        <v>0</v>
-      </c>
-      <c r="BP7">
-        <v>0</v>
-      </c>
-      <c r="BQ7">
-        <v>0</v>
-      </c>
-      <c r="BR7">
-        <v>0</v>
-      </c>
-      <c r="BS7">
-        <v>0</v>
-      </c>
-      <c r="BT7">
-        <v>0</v>
-      </c>
-      <c r="BU7">
-        <v>0</v>
-      </c>
-      <c r="BV7">
-        <v>0</v>
       </c>
       <c r="BW7">
         <v>0</v>
@@ -7803,76 +8528,76 @@
         <v>0</v>
       </c>
       <c r="BG8">
-        <v>0</v>
+        <v>137</v>
       </c>
       <c r="BH8">
-        <v>3</v>
-      </c>
-      <c r="BI8">
-        <v>191</v>
+        <v>23073</v>
+      </c>
+      <c r="BI8" s="6">
+        <v>21833</v>
       </c>
       <c r="BJ8">
-        <v>1101</v>
+        <v>22473</v>
       </c>
       <c r="BK8">
-        <v>939</v>
+        <v>19799</v>
       </c>
       <c r="BL8">
-        <v>813</v>
+        <v>19913</v>
       </c>
       <c r="BM8">
-        <v>628</v>
+        <v>19355</v>
       </c>
       <c r="BN8">
-        <v>175</v>
+        <v>15467</v>
       </c>
       <c r="BO8">
-        <v>43</v>
+        <v>14599</v>
       </c>
       <c r="BP8">
+        <v>12961</v>
+      </c>
+      <c r="BQ8">
+        <v>11538</v>
+      </c>
+      <c r="BR8">
+        <v>2952</v>
+      </c>
+      <c r="BS8">
+        <v>1602</v>
+      </c>
+      <c r="BT8">
+        <v>716</v>
+      </c>
+      <c r="BU8">
+        <v>336</v>
+      </c>
+      <c r="BV8">
+        <v>482</v>
+      </c>
+      <c r="BW8">
+        <v>172</v>
+      </c>
+      <c r="BX8">
+        <v>16</v>
+      </c>
+      <c r="BY8">
         <v>14</v>
       </c>
-      <c r="BQ8">
-        <v>3</v>
-      </c>
-      <c r="BR8">
-        <v>0</v>
-      </c>
-      <c r="BS8">
-        <v>0</v>
-      </c>
-      <c r="BT8">
-        <v>0</v>
-      </c>
-      <c r="BU8">
-        <v>0</v>
-      </c>
-      <c r="BV8">
-        <v>0</v>
-      </c>
-      <c r="BW8">
-        <v>0</v>
-      </c>
-      <c r="BX8">
-        <v>0</v>
-      </c>
-      <c r="BY8">
-        <v>0</v>
-      </c>
       <c r="BZ8">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="CA8">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="CB8">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="CC8">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="CD8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CE8">
         <v>0</v>
@@ -8096,103 +8821,103 @@
         <v>0</v>
       </c>
       <c r="BF9">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="BG9">
-        <v>0</v>
+        <v>9211</v>
       </c>
       <c r="BH9">
-        <v>201</v>
-      </c>
-      <c r="BI9">
-        <v>10288</v>
+        <v>32593</v>
+      </c>
+      <c r="BI9" s="6">
+        <v>28443</v>
       </c>
       <c r="BJ9">
-        <v>28713</v>
+        <v>27218</v>
       </c>
       <c r="BK9">
-        <v>24043</v>
+        <v>29039</v>
       </c>
       <c r="BL9">
-        <v>20684</v>
+        <v>28599</v>
       </c>
       <c r="BM9">
-        <v>19993</v>
+        <v>29255</v>
       </c>
       <c r="BN9">
-        <v>8091</v>
+        <v>31763</v>
       </c>
       <c r="BO9">
-        <v>2603</v>
+        <v>32952</v>
       </c>
       <c r="BP9">
-        <v>792</v>
+        <v>35312</v>
       </c>
       <c r="BQ9">
-        <v>148</v>
+        <v>37139</v>
       </c>
       <c r="BR9">
-        <v>16</v>
+        <v>38835</v>
       </c>
       <c r="BS9">
+        <v>31740</v>
+      </c>
+      <c r="BT9">
+        <v>25309</v>
+      </c>
+      <c r="BU9">
+        <v>10581</v>
+      </c>
+      <c r="BV9">
+        <v>16698</v>
+      </c>
+      <c r="BW9">
+        <v>7325</v>
+      </c>
+      <c r="BX9">
+        <v>699</v>
+      </c>
+      <c r="BY9">
+        <v>654</v>
+      </c>
+      <c r="BZ9">
+        <v>252</v>
+      </c>
+      <c r="CA9">
+        <v>327</v>
+      </c>
+      <c r="CB9">
+        <v>467</v>
+      </c>
+      <c r="CC9">
+        <v>76</v>
+      </c>
+      <c r="CD9">
+        <v>30</v>
+      </c>
+      <c r="CE9">
+        <v>38</v>
+      </c>
+      <c r="CF9">
+        <v>11</v>
+      </c>
+      <c r="CG9">
+        <v>0</v>
+      </c>
+      <c r="CH9">
         <v>8</v>
       </c>
-      <c r="BT9">
-        <v>11</v>
-      </c>
-      <c r="BU9">
+      <c r="CI9">
+        <v>9</v>
+      </c>
+      <c r="CJ9">
         <v>1</v>
       </c>
-      <c r="BV9">
-        <v>4</v>
-      </c>
-      <c r="BW9">
-        <v>0</v>
-      </c>
-      <c r="BX9">
-        <v>0</v>
-      </c>
-      <c r="BY9">
-        <v>0</v>
-      </c>
-      <c r="BZ9">
-        <v>0</v>
-      </c>
-      <c r="CA9">
-        <v>0</v>
-      </c>
-      <c r="CB9">
-        <v>0</v>
-      </c>
-      <c r="CC9">
-        <v>0</v>
-      </c>
-      <c r="CD9">
-        <v>0</v>
-      </c>
-      <c r="CE9">
-        <v>0</v>
-      </c>
-      <c r="CF9">
-        <v>0</v>
-      </c>
-      <c r="CG9">
-        <v>0</v>
-      </c>
-      <c r="CH9">
-        <v>0</v>
-      </c>
-      <c r="CI9">
-        <v>0</v>
-      </c>
-      <c r="CJ9">
-        <v>0</v>
-      </c>
       <c r="CK9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CL9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CM9">
         <v>0</v>
@@ -8392,127 +9117,127 @@
         <v>0</v>
       </c>
       <c r="BF10">
-        <v>0</v>
+        <v>502</v>
       </c>
       <c r="BG10">
+        <v>34605</v>
+      </c>
+      <c r="BH10">
+        <v>8779</v>
+      </c>
+      <c r="BI10" s="6">
+        <v>7895</v>
+      </c>
+      <c r="BJ10">
+        <v>7432</v>
+      </c>
+      <c r="BK10">
+        <v>8194</v>
+      </c>
+      <c r="BL10">
+        <v>8112</v>
+      </c>
+      <c r="BM10">
+        <v>8398</v>
+      </c>
+      <c r="BN10">
+        <v>9550</v>
+      </c>
+      <c r="BO10">
+        <v>10238</v>
+      </c>
+      <c r="BP10">
+        <v>11016</v>
+      </c>
+      <c r="BQ10">
+        <v>11478</v>
+      </c>
+      <c r="BR10">
+        <v>18935</v>
+      </c>
+      <c r="BS10">
+        <v>24789</v>
+      </c>
+      <c r="BT10">
+        <v>29783</v>
+      </c>
+      <c r="BU10">
+        <v>35276</v>
+      </c>
+      <c r="BV10">
+        <v>31538</v>
+      </c>
+      <c r="BW10">
+        <v>37488</v>
+      </c>
+      <c r="BX10">
+        <v>17692</v>
+      </c>
+      <c r="BY10">
+        <v>19874</v>
+      </c>
+      <c r="BZ10">
+        <v>5619</v>
+      </c>
+      <c r="CA10">
+        <v>6349</v>
+      </c>
+      <c r="CB10">
+        <v>9458</v>
+      </c>
+      <c r="CC10">
+        <v>1630</v>
+      </c>
+      <c r="CD10">
+        <v>561</v>
+      </c>
+      <c r="CE10">
+        <v>901</v>
+      </c>
+      <c r="CF10">
+        <v>302</v>
+      </c>
+      <c r="CG10">
         <v>44</v>
       </c>
-      <c r="BH10">
-        <v>14907</v>
-      </c>
-      <c r="BI10">
-        <v>35091</v>
-      </c>
-      <c r="BJ10">
-        <v>23635</v>
-      </c>
-      <c r="BK10">
-        <v>26403</v>
-      </c>
-      <c r="BL10">
-        <v>28103</v>
-      </c>
-      <c r="BM10">
-        <v>28878</v>
-      </c>
-      <c r="BN10">
-        <v>36173</v>
-      </c>
-      <c r="BO10">
-        <v>34278</v>
-      </c>
-      <c r="BP10">
-        <v>20276</v>
-      </c>
-      <c r="BQ10">
-        <v>6473</v>
-      </c>
-      <c r="BR10">
-        <v>1319</v>
-      </c>
-      <c r="BS10">
-        <v>623</v>
-      </c>
-      <c r="BT10">
-        <v>277</v>
-      </c>
-      <c r="BU10">
-        <v>107</v>
-      </c>
-      <c r="BV10">
-        <v>145</v>
-      </c>
-      <c r="BW10">
-        <v>36</v>
-      </c>
-      <c r="BX10">
+      <c r="CH10">
+        <v>314</v>
+      </c>
+      <c r="CI10">
+        <v>341</v>
+      </c>
+      <c r="CJ10">
+        <v>69</v>
+      </c>
+      <c r="CK10">
+        <v>90</v>
+      </c>
+      <c r="CL10">
+        <v>90</v>
+      </c>
+      <c r="CM10">
+        <v>29</v>
+      </c>
+      <c r="CN10">
+        <v>2</v>
+      </c>
+      <c r="CO10">
+        <v>0</v>
+      </c>
+      <c r="CP10">
+        <v>0</v>
+      </c>
+      <c r="CQ10">
+        <v>0</v>
+      </c>
+      <c r="CR10">
+        <v>2</v>
+      </c>
+      <c r="CS10">
+        <v>0</v>
+      </c>
+      <c r="CT10">
         <v>1</v>
-      </c>
-      <c r="BY10">
-        <v>6</v>
-      </c>
-      <c r="BZ10">
-        <v>0</v>
-      </c>
-      <c r="CA10">
-        <v>1</v>
-      </c>
-      <c r="CB10">
-        <v>2</v>
-      </c>
-      <c r="CC10">
-        <v>0</v>
-      </c>
-      <c r="CD10">
-        <v>0</v>
-      </c>
-      <c r="CE10">
-        <v>0</v>
-      </c>
-      <c r="CF10">
-        <v>0</v>
-      </c>
-      <c r="CG10">
-        <v>0</v>
-      </c>
-      <c r="CH10">
-        <v>0</v>
-      </c>
-      <c r="CI10">
-        <v>0</v>
-      </c>
-      <c r="CJ10">
-        <v>0</v>
-      </c>
-      <c r="CK10">
-        <v>0</v>
-      </c>
-      <c r="CL10">
-        <v>0</v>
-      </c>
-      <c r="CM10">
-        <v>0</v>
-      </c>
-      <c r="CN10">
-        <v>0</v>
-      </c>
-      <c r="CO10">
-        <v>0</v>
-      </c>
-      <c r="CP10">
-        <v>0</v>
-      </c>
-      <c r="CQ10">
-        <v>0</v>
-      </c>
-      <c r="CR10">
-        <v>0</v>
-      </c>
-      <c r="CS10">
-        <v>0</v>
-      </c>
-      <c r="CT10">
-        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:98" x14ac:dyDescent="0.25">
@@ -8696,7 +9421,7 @@
       <c r="BH11">
         <v>0</v>
       </c>
-      <c r="BI11">
+      <c r="BI11" s="6">
         <v>0</v>
       </c>
       <c r="BJ11">
@@ -8992,7 +9717,7 @@
       <c r="BH12">
         <v>0</v>
       </c>
-      <c r="BI12">
+      <c r="BI12" s="6">
         <v>0</v>
       </c>
       <c r="BJ12">
@@ -9288,7 +10013,7 @@
       <c r="BH13">
         <v>0</v>
       </c>
-      <c r="BI13">
+      <c r="BI13" s="6">
         <v>0</v>
       </c>
       <c r="BJ13">
@@ -9582,34 +10307,34 @@
         <v>0</v>
       </c>
       <c r="BH14">
-        <v>0</v>
-      </c>
-      <c r="BI14">
-        <v>0</v>
+        <v>0.115271034104567</v>
+      </c>
+      <c r="BI14" s="6">
+        <v>0.157118818263213</v>
       </c>
       <c r="BJ14">
-        <v>0</v>
+        <v>0.112058641038443</v>
       </c>
       <c r="BK14">
-        <v>0</v>
+        <v>0.12590980652216199</v>
       </c>
       <c r="BL14">
-        <v>0</v>
+        <v>0.13805918950754201</v>
       </c>
       <c r="BM14">
-        <v>0</v>
+        <v>0.12542541419627201</v>
       </c>
       <c r="BN14">
-        <v>0</v>
+        <v>0.107156416029352</v>
       </c>
       <c r="BO14">
-        <v>0</v>
+        <v>9.7393257253257995E-2</v>
       </c>
       <c r="BP14">
-        <v>0</v>
+        <v>0.105395907291619</v>
       </c>
       <c r="BQ14">
-        <v>0</v>
+        <v>9.0880432145408696E-2</v>
       </c>
       <c r="BR14">
         <v>0</v>
@@ -9624,7 +10349,7 @@
         <v>0</v>
       </c>
       <c r="BV14">
-        <v>0</v>
+        <v>3.5181832671268898E-2</v>
       </c>
       <c r="BW14">
         <v>0</v>
@@ -9878,34 +10603,34 @@
         <v>0</v>
       </c>
       <c r="BH15">
-        <v>0</v>
-      </c>
-      <c r="BI15">
-        <v>0</v>
+        <v>0.111730718669316</v>
+      </c>
+      <c r="BI15" s="6">
+        <v>0.12222432291648699</v>
       </c>
       <c r="BJ15">
-        <v>0</v>
+        <v>0.112058641038443</v>
       </c>
       <c r="BK15">
-        <v>0</v>
+        <v>0.11610967778183701</v>
       </c>
       <c r="BL15">
-        <v>0</v>
+        <v>0.12295818461944701</v>
       </c>
       <c r="BM15">
-        <v>0</v>
+        <v>0.115703286756331</v>
       </c>
       <c r="BN15">
-        <v>0</v>
+        <v>9.7831442413827796E-2</v>
       </c>
       <c r="BO15">
-        <v>0</v>
+        <v>9.1451690386585696E-2</v>
       </c>
       <c r="BP15">
-        <v>0</v>
+        <v>9.1715550071271496E-2</v>
       </c>
       <c r="BQ15">
-        <v>0</v>
+        <v>8.2824650353532994E-2</v>
       </c>
       <c r="BR15">
         <v>0</v>
@@ -9920,7 +10645,7 @@
         <v>0</v>
       </c>
       <c r="BV15">
-        <v>0</v>
+        <v>3.5181832671268898E-2</v>
       </c>
       <c r="BW15">
         <v>0</v>
@@ -10174,34 +10899,34 @@
         <v>0</v>
       </c>
       <c r="BH16">
-        <v>0</v>
-      </c>
-      <c r="BI16">
-        <v>0</v>
+        <v>0.111297029303968</v>
+      </c>
+      <c r="BI16" s="6">
+        <v>0.114723726562534</v>
       </c>
       <c r="BJ16">
-        <v>0</v>
+        <v>0.112058641038443</v>
       </c>
       <c r="BK16">
-        <v>0</v>
+        <v>0.120146144859892</v>
       </c>
       <c r="BL16">
-        <v>0</v>
+        <v>0.122308947032243</v>
       </c>
       <c r="BM16">
-        <v>0</v>
+        <v>0.1185792808338</v>
       </c>
       <c r="BN16">
-        <v>0</v>
+        <v>9.90275373142845E-2</v>
       </c>
       <c r="BO16">
-        <v>0</v>
+        <v>9.1451690386585696E-2</v>
       </c>
       <c r="BP16">
-        <v>0</v>
+        <v>9.1715550071271496E-2</v>
       </c>
       <c r="BQ16">
-        <v>0</v>
+        <v>8.2231146677194306E-2</v>
       </c>
       <c r="BR16">
         <v>0</v>
@@ -10216,7 +10941,7 @@
         <v>0</v>
       </c>
       <c r="BV16">
-        <v>0</v>
+        <v>3.5181832671268898E-2</v>
       </c>
       <c r="BW16">
         <v>0</v>
@@ -10470,49 +11195,49 @@
         <v>0</v>
       </c>
       <c r="BH17">
-        <v>0</v>
-      </c>
-      <c r="BI17">
-        <v>0.108744971579519</v>
+        <v>0.516412303383603</v>
+      </c>
+      <c r="BI17" s="6">
+        <v>0.628475273052853</v>
       </c>
       <c r="BJ17">
-        <v>0.14248089133001501</v>
+        <v>0.58563901107528504</v>
       </c>
       <c r="BK17">
-        <v>0.14382894142458799</v>
+        <v>0.50392155366756997</v>
       </c>
       <c r="BL17">
-        <v>0.14148195475431999</v>
+        <v>0.56467031476748897</v>
       </c>
       <c r="BM17">
-        <v>0.12788503535538701</v>
+        <v>0.50170165678509104</v>
       </c>
       <c r="BN17">
-        <v>7.8911230605376498E-2</v>
+        <v>0.47473116714984298</v>
       </c>
       <c r="BO17">
-        <v>0</v>
+        <v>0.44220256087389798</v>
       </c>
       <c r="BP17">
-        <v>0</v>
+        <v>0.47601635277780302</v>
       </c>
       <c r="BQ17">
-        <v>0</v>
+        <v>0.40198658788080999</v>
       </c>
       <c r="BR17">
-        <v>0</v>
+        <v>0.23596911494317599</v>
       </c>
       <c r="BS17">
-        <v>0</v>
+        <v>0.19485626756340399</v>
       </c>
       <c r="BT17">
-        <v>0</v>
+        <v>0.16649436459139</v>
       </c>
       <c r="BU17">
-        <v>0</v>
+        <v>9.5182959949655699E-2</v>
       </c>
       <c r="BV17">
-        <v>0</v>
+        <v>0.14072733068507501</v>
       </c>
       <c r="BW17">
         <v>0</v>
@@ -10766,49 +11491,49 @@
         <v>0</v>
       </c>
       <c r="BH18">
-        <v>0</v>
-      </c>
-      <c r="BI18">
-        <v>0.108744971579519</v>
+        <v>0.39804894523814299</v>
+      </c>
+      <c r="BI18" s="6">
+        <v>0.41325134938454</v>
       </c>
       <c r="BJ18">
-        <v>0.13735789073556501</v>
+        <v>0.423964093107142</v>
       </c>
       <c r="BK18">
-        <v>0.12855473603043399</v>
+        <v>0.41371420488275901</v>
       </c>
       <c r="BL18">
-        <v>0.12600656555491199</v>
+        <v>0.41654829145366501</v>
       </c>
       <c r="BM18">
-        <v>0.11797225476671699</v>
+        <v>0.40026069555756599</v>
       </c>
       <c r="BN18">
-        <v>7.5918130207376699E-2</v>
+        <v>0.35799090492579599</v>
       </c>
       <c r="BO18">
-        <v>0</v>
+        <v>0.35368556592233102</v>
       </c>
       <c r="BP18">
-        <v>0</v>
+        <v>0.33544115828997301</v>
       </c>
       <c r="BQ18">
-        <v>0</v>
+        <v>0.31101324688188497</v>
       </c>
       <c r="BR18">
-        <v>0</v>
+        <v>0.198021424039065</v>
       </c>
       <c r="BS18">
-        <v>0</v>
+        <v>0.15242178686235999</v>
       </c>
       <c r="BT18">
-        <v>0</v>
+        <v>0.13189405350537201</v>
       </c>
       <c r="BU18">
-        <v>0</v>
+        <v>8.5513031579996499E-2</v>
       </c>
       <c r="BV18">
-        <v>0</v>
+        <v>0.101957056442622</v>
       </c>
       <c r="BW18">
         <v>0</v>
@@ -11062,49 +11787,49 @@
         <v>0</v>
       </c>
       <c r="BH19">
-        <v>0</v>
-      </c>
-      <c r="BI19">
-        <v>0.108744971579519</v>
+        <v>0.398500863122767</v>
+      </c>
+      <c r="BI19" s="6">
+        <v>0.40902712276833098</v>
       </c>
       <c r="BJ19">
-        <v>0.137945758770084</v>
+        <v>0.41788520483921099</v>
       </c>
       <c r="BK19">
-        <v>0.12797104615789201</v>
+        <v>0.40741803298824703</v>
       </c>
       <c r="BL19">
-        <v>0.12534123206185099</v>
+        <v>0.409066810001184</v>
       </c>
       <c r="BM19">
-        <v>0.120904647749076</v>
+        <v>0.39073658917944698</v>
       </c>
       <c r="BN19">
-        <v>7.5918130207376699E-2</v>
+        <v>0.36016165944192302</v>
       </c>
       <c r="BO19">
-        <v>0</v>
+        <v>0.35416385235721598</v>
       </c>
       <c r="BP19">
-        <v>0</v>
+        <v>0.32622337575256299</v>
       </c>
       <c r="BQ19">
-        <v>0</v>
+        <v>0.30799155865256</v>
       </c>
       <c r="BR19">
-        <v>0</v>
+        <v>0.19604178800581201</v>
       </c>
       <c r="BS19">
-        <v>0</v>
+        <v>0.15354641341984401</v>
       </c>
       <c r="BT19">
-        <v>0</v>
+        <v>0.12476197757377799</v>
       </c>
       <c r="BU19">
-        <v>0</v>
+        <v>8.8842856176915896E-2</v>
       </c>
       <c r="BV19">
-        <v>0</v>
+        <v>9.2256973568308795E-2</v>
       </c>
       <c r="BW19">
         <v>0</v>
@@ -11355,76 +12080,76 @@
         <v>0</v>
       </c>
       <c r="BG20">
-        <v>0</v>
+        <v>0.34096805393159002</v>
       </c>
       <c r="BH20">
-        <v>8.7949022715134606E-2</v>
-      </c>
-      <c r="BI20">
-        <v>0.43497988631807699</v>
+        <v>2.0656492135344098</v>
+      </c>
+      <c r="BI20" s="6">
+        <v>2.5139010922114098</v>
       </c>
       <c r="BJ20">
-        <v>0.70460204460160802</v>
+        <v>2.3425560443011402</v>
       </c>
       <c r="BK20">
-        <v>0.57563827335525197</v>
+        <v>2.0156862146702799</v>
       </c>
       <c r="BL20">
-        <v>0.57866962867373795</v>
+        <v>2.2586812590699501</v>
       </c>
       <c r="BM20">
-        <v>0.51154014142154802</v>
+        <v>2.0068066271403602</v>
       </c>
       <c r="BN20">
-        <v>0.34959755089845501</v>
+        <v>1.8989246685993699</v>
       </c>
       <c r="BO20">
-        <v>0.21041001585396699</v>
+        <v>1.7688102434955899</v>
       </c>
       <c r="BP20">
-        <v>0.148346486238562</v>
+        <v>1.9040654111112101</v>
       </c>
       <c r="BQ20">
-        <v>6.9013181017917105E-2</v>
+        <v>1.6079463515232399</v>
       </c>
       <c r="BR20">
-        <v>0</v>
+        <v>0.94387645977270596</v>
       </c>
       <c r="BS20">
-        <v>0</v>
+        <v>0.77942507025361796</v>
       </c>
       <c r="BT20">
-        <v>0</v>
+        <v>0.66597745836555999</v>
       </c>
       <c r="BU20">
-        <v>0</v>
+        <v>0.451780897469788</v>
       </c>
       <c r="BV20">
-        <v>0</v>
+        <v>0.56290932274030203</v>
       </c>
       <c r="BW20">
-        <v>0</v>
+        <v>0.328542112218006</v>
       </c>
       <c r="BX20">
-        <v>0</v>
+        <v>0.13926594483926899</v>
       </c>
       <c r="BY20">
-        <v>0</v>
+        <v>0.14475570312437</v>
       </c>
       <c r="BZ20">
-        <v>0</v>
+        <v>9.43576908929427E-2</v>
       </c>
       <c r="CA20">
-        <v>0</v>
+        <v>0.100998226838671</v>
       </c>
       <c r="CB20">
-        <v>0</v>
+        <v>0.14978369750651199</v>
       </c>
       <c r="CC20">
-        <v>0</v>
+        <v>4.5477090361547498E-2</v>
       </c>
       <c r="CD20">
-        <v>0</v>
+        <v>3.0045049785312201E-2</v>
       </c>
       <c r="CE20">
         <v>0</v>
@@ -11651,76 +12376,76 @@
         <v>0</v>
       </c>
       <c r="BG21">
-        <v>0</v>
+        <v>0.27896451525951699</v>
       </c>
       <c r="BH21">
-        <v>8.7949022715134606E-2</v>
-      </c>
-      <c r="BI21">
-        <v>0.29262851518342098</v>
+        <v>1.5831812195524799</v>
+      </c>
+      <c r="BI21" s="6">
+        <v>1.64802362367015</v>
       </c>
       <c r="BJ21">
-        <v>0.51008549838768702</v>
+        <v>1.69585637242857</v>
       </c>
       <c r="BK21">
-        <v>0.472592864563813</v>
+        <v>1.6471411489749199</v>
       </c>
       <c r="BL21">
-        <v>0.42687536219022298</v>
+        <v>1.66619316581466</v>
       </c>
       <c r="BM21">
-        <v>0.40810989967132799</v>
+        <v>1.60104278223026</v>
       </c>
       <c r="BN21">
-        <v>0.26933357905466099</v>
+        <v>1.4219337189704699</v>
       </c>
       <c r="BO21">
-        <v>0.17940026812955601</v>
+        <v>1.4019833302917699</v>
       </c>
       <c r="BP21">
-        <v>0.12327844683726</v>
+        <v>1.3236362649186</v>
       </c>
       <c r="BQ21">
-        <v>6.4360317332734104E-2</v>
+        <v>1.22935514106955</v>
       </c>
       <c r="BR21">
-        <v>0</v>
+        <v>0.72196796646240602</v>
       </c>
       <c r="BS21">
-        <v>0</v>
+        <v>0.56054359702966705</v>
       </c>
       <c r="BT21">
-        <v>0</v>
+        <v>0.44004760620657901</v>
       </c>
       <c r="BU21">
-        <v>0</v>
+        <v>0.31085662428906202</v>
       </c>
       <c r="BV21">
-        <v>0</v>
+        <v>0.37457436361281699</v>
       </c>
       <c r="BW21">
-        <v>0</v>
+        <v>0.265505039145222</v>
       </c>
       <c r="BX21">
-        <v>0</v>
+        <v>0.111990425811099</v>
       </c>
       <c r="BY21">
-        <v>0</v>
+        <v>0.119647445189057</v>
       </c>
       <c r="BZ21">
-        <v>0</v>
+        <v>7.7898115953515604E-2</v>
       </c>
       <c r="CA21">
-        <v>0</v>
+        <v>8.1931079795284398E-2</v>
       </c>
       <c r="CB21">
-        <v>0</v>
+        <v>9.4793792095688306E-2</v>
       </c>
       <c r="CC21">
-        <v>0</v>
+        <v>4.3465060920105103E-2</v>
       </c>
       <c r="CD21">
-        <v>0</v>
+        <v>3.0045049785312201E-2</v>
       </c>
       <c r="CE21">
         <v>0</v>
@@ -11947,76 +12672,76 @@
         <v>0</v>
       </c>
       <c r="BG22">
-        <v>0</v>
+        <v>0.277539775756317</v>
       </c>
       <c r="BH22">
-        <v>8.7949022715134606E-2</v>
-      </c>
-      <c r="BI22">
-        <v>0.29150033992500002</v>
+        <v>1.5934350948965901</v>
+      </c>
+      <c r="BI22" s="6">
+        <v>1.63364071150274</v>
       </c>
       <c r="BJ22">
-        <v>0.50277178290516</v>
+        <v>1.67154081935684</v>
       </c>
       <c r="BK22">
-        <v>0.46540063892621603</v>
+        <v>1.6249133848303401</v>
       </c>
       <c r="BL22">
-        <v>0.41920839975386798</v>
+        <v>1.63626724000473</v>
       </c>
       <c r="BM22">
-        <v>0.39839902338618799</v>
+        <v>1.5629463567177799</v>
       </c>
       <c r="BN22">
-        <v>0.270960518475028</v>
+        <v>1.4317631679348</v>
       </c>
       <c r="BO22">
-        <v>0.18210033392674699</v>
+        <v>1.40107230769084</v>
       </c>
       <c r="BP22">
-        <v>0.119793603281023</v>
+        <v>1.2836387102003199</v>
       </c>
       <c r="BQ22">
-        <v>6.2242539949236397E-2</v>
+        <v>1.2165485380275101</v>
       </c>
       <c r="BR22">
-        <v>0</v>
+        <v>0.71231987135571595</v>
       </c>
       <c r="BS22">
-        <v>0</v>
+        <v>0.54759676405020696</v>
       </c>
       <c r="BT22">
-        <v>0</v>
+        <v>0.431210914183705</v>
       </c>
       <c r="BU22">
-        <v>0</v>
+        <v>0.31116749175351399</v>
       </c>
       <c r="BV22">
-        <v>0</v>
+        <v>0.36686449472593902</v>
       </c>
       <c r="BW22">
-        <v>0</v>
+        <v>0.26641259681149498</v>
       </c>
       <c r="BX22">
-        <v>0</v>
+        <v>0.110469223445117</v>
       </c>
       <c r="BY22">
-        <v>0</v>
+        <v>0.11995522301684899</v>
       </c>
       <c r="BZ22">
-        <v>0</v>
+        <v>7.9298357726803506E-2</v>
       </c>
       <c r="CA22">
-        <v>0</v>
+        <v>7.8937096907269799E-2</v>
       </c>
       <c r="CB22">
-        <v>0</v>
+        <v>8.9404811854014499E-2</v>
       </c>
       <c r="CC22">
-        <v>0</v>
+        <v>4.3216948354527399E-2</v>
       </c>
       <c r="CD22">
-        <v>0</v>
+        <v>3.0045049785312201E-2</v>
       </c>
       <c r="CE22">
         <v>0</v>
@@ -12240,103 +12965,103 @@
         <v>0</v>
       </c>
       <c r="BF23">
-        <v>0</v>
+        <v>0.125022973102319</v>
       </c>
       <c r="BG23">
-        <v>0</v>
+        <v>1.3638722157263601</v>
       </c>
       <c r="BH23">
-        <v>0.41812047690249099</v>
-      </c>
-      <c r="BI23">
-        <v>1.73991954527231</v>
+        <v>8.2625968541376604</v>
+      </c>
+      <c r="BI23" s="6">
+        <v>10.0556043688456</v>
       </c>
       <c r="BJ23">
-        <v>2.8184081784064299</v>
+        <v>9.3702241772045696</v>
       </c>
       <c r="BK23">
-        <v>2.3025530934210101</v>
+        <v>8.0627448586811301</v>
       </c>
       <c r="BL23">
-        <v>2.31467851469495</v>
+        <v>9.0347250362798306</v>
       </c>
       <c r="BM23">
-        <v>2.0461605656861899</v>
+        <v>8.0272265085614496</v>
       </c>
       <c r="BN23">
-        <v>1.39839020359382</v>
+        <v>7.5956986743974904</v>
       </c>
       <c r="BO23">
-        <v>0.84164006341586906</v>
+        <v>7.0752409739823801</v>
       </c>
       <c r="BP23">
-        <v>0.60970970844577199</v>
+        <v>7.6162616444448599</v>
       </c>
       <c r="BQ23">
-        <v>0.32125120067134799</v>
+        <v>6.4317854060929696</v>
       </c>
       <c r="BR23">
-        <v>0.17478325422601201</v>
+        <v>3.7755058390908198</v>
       </c>
       <c r="BS23">
-        <v>0.116342651448462</v>
+        <v>3.1177002810144701</v>
       </c>
       <c r="BT23">
-        <v>9.4519312152586202E-2</v>
+        <v>2.66390983346224</v>
       </c>
       <c r="BU23">
-        <v>5.8738158793933001E-2</v>
+        <v>1.80712358987915</v>
       </c>
       <c r="BV23">
-        <v>9.32562328397432E-2</v>
+        <v>2.2516372909612099</v>
       </c>
       <c r="BW23">
-        <v>0</v>
+        <v>1.31416844887202</v>
       </c>
       <c r="BX23">
-        <v>0</v>
+        <v>0.55706377935707696</v>
       </c>
       <c r="BY23">
-        <v>0</v>
+        <v>0.579022812497483</v>
       </c>
       <c r="BZ23">
-        <v>0</v>
+        <v>0.37743076357177002</v>
       </c>
       <c r="CA23">
-        <v>0</v>
+        <v>0.40399290735468402</v>
       </c>
       <c r="CB23">
-        <v>0</v>
+        <v>0.59913479002604997</v>
       </c>
       <c r="CC23">
-        <v>0</v>
+        <v>0.21506000591179</v>
       </c>
       <c r="CD23">
-        <v>0</v>
+        <v>0.12976171930552199</v>
       </c>
       <c r="CE23">
-        <v>0</v>
+        <v>0.15639706037655601</v>
       </c>
       <c r="CF23">
-        <v>0</v>
+        <v>8.9532527363886893E-2</v>
       </c>
       <c r="CG23">
         <v>0</v>
       </c>
       <c r="CH23">
-        <v>0</v>
+        <v>9.1024377114943905E-2</v>
       </c>
       <c r="CI23">
-        <v>0</v>
+        <v>0.103863105980485</v>
       </c>
       <c r="CJ23">
-        <v>0</v>
+        <v>3.15391317194939E-2</v>
       </c>
       <c r="CK23">
-        <v>0</v>
+        <v>4.7981001680930301E-2</v>
       </c>
       <c r="CL23">
-        <v>0</v>
+        <v>3.6370051858590297E-2</v>
       </c>
       <c r="CM23">
         <v>0</v>
@@ -12536,103 +13261,103 @@
         <v>0</v>
       </c>
       <c r="BF24">
-        <v>0</v>
+        <v>9.7233743246969997E-2</v>
       </c>
       <c r="BG24">
-        <v>0</v>
+        <v>1.08651092584515</v>
       </c>
       <c r="BH24">
-        <v>0.32514551583774098</v>
-      </c>
-      <c r="BI24">
-        <v>1.1406290099543599</v>
+        <v>6.3327248782099197</v>
+      </c>
+      <c r="BI24" s="6">
+        <v>6.5920944946805999</v>
       </c>
       <c r="BJ24">
-        <v>2.0403419935507401</v>
+        <v>6.7834254897142801</v>
       </c>
       <c r="BK24">
-        <v>1.88155771483754</v>
+        <v>6.5885645958996903</v>
       </c>
       <c r="BL24">
-        <v>1.7075014487608899</v>
+        <v>6.6647726632586499</v>
       </c>
       <c r="BM24">
-        <v>1.63243959868531</v>
+        <v>6.4041711289210603</v>
       </c>
       <c r="BN24">
-        <v>1.0471285225914799</v>
+        <v>5.6877348758818904</v>
       </c>
       <c r="BO24">
-        <v>0.66709549163916704</v>
+        <v>5.6079333211670903</v>
       </c>
       <c r="BP24">
-        <v>0.42531759363613197</v>
+        <v>5.2945450596744097</v>
       </c>
       <c r="BQ24">
-        <v>0.250148582571667</v>
+        <v>4.9174205642782098</v>
       </c>
       <c r="BR24">
-        <v>0.15598840302274</v>
+        <v>2.8878718658496201</v>
       </c>
       <c r="BS24">
-        <v>0.104380865170433</v>
+        <v>2.24217438811867</v>
       </c>
       <c r="BT24">
-        <v>8.7162431102421903E-2</v>
+        <v>1.7601904248263101</v>
       </c>
       <c r="BU24">
-        <v>5.8738158793933001E-2</v>
+        <v>1.23592737761516</v>
       </c>
       <c r="BV24">
-        <v>7.8436113695945803E-2</v>
+        <v>1.4868106217933901</v>
       </c>
       <c r="BW24">
-        <v>0</v>
+        <v>1.04385197304281</v>
       </c>
       <c r="BX24">
-        <v>0</v>
+        <v>0.39097357213335499</v>
       </c>
       <c r="BY24">
-        <v>0</v>
+        <v>0.41497989227775101</v>
       </c>
       <c r="BZ24">
-        <v>0</v>
+        <v>0.24669832358235899</v>
       </c>
       <c r="CA24">
-        <v>0</v>
+        <v>0.269483973111312</v>
       </c>
       <c r="CB24">
-        <v>0</v>
+        <v>0.322945473774782</v>
       </c>
       <c r="CC24">
-        <v>0</v>
+        <v>0.15363473266612901</v>
       </c>
       <c r="CD24">
-        <v>0</v>
+        <v>9.7730118304597796E-2</v>
       </c>
       <c r="CE24">
-        <v>0</v>
+        <v>0.115309782911975</v>
       </c>
       <c r="CF24">
-        <v>0</v>
+        <v>7.0997461288460906E-2</v>
       </c>
       <c r="CG24">
         <v>0</v>
       </c>
       <c r="CH24">
-        <v>0</v>
+        <v>6.9808333500316802E-2</v>
       </c>
       <c r="CI24">
-        <v>0</v>
+        <v>7.5848974424109594E-2</v>
       </c>
       <c r="CJ24">
-        <v>0</v>
+        <v>3.15391317194939E-2</v>
       </c>
       <c r="CK24">
-        <v>0</v>
+        <v>4.7981001680930301E-2</v>
       </c>
       <c r="CL24">
-        <v>0</v>
+        <v>3.6370051858590297E-2</v>
       </c>
       <c r="CM24">
         <v>0</v>
@@ -12832,103 +13557,103 @@
         <v>0</v>
       </c>
       <c r="BF25">
-        <v>0</v>
+        <v>9.7848604682633095E-2</v>
       </c>
       <c r="BG25">
-        <v>0</v>
+        <v>1.07923615030625</v>
       </c>
       <c r="BH25">
-        <v>0.32800666915712801</v>
-      </c>
-      <c r="BI25">
-        <v>1.1306743184025101</v>
+        <v>6.3737403795863798</v>
+      </c>
+      <c r="BI25" s="6">
+        <v>6.5345628460109699</v>
       </c>
       <c r="BJ25">
-        <v>2.01108713162064</v>
+        <v>6.6861632774273803</v>
       </c>
       <c r="BK25">
-        <v>1.8561665568696799</v>
+        <v>6.4996535393213897</v>
       </c>
       <c r="BL25">
-        <v>1.6768335990154699</v>
+        <v>6.5450689600189396</v>
       </c>
       <c r="BM25">
-        <v>1.59359609354475</v>
+        <v>6.2517854268711499</v>
       </c>
       <c r="BN25">
-        <v>1.0543670430861001</v>
+        <v>5.7270526717392203</v>
       </c>
       <c r="BO25">
-        <v>0.66666200641163698</v>
+        <v>5.6042892307633601</v>
       </c>
       <c r="BP25">
-        <v>0.41176376467682302</v>
+        <v>5.13455484080131</v>
       </c>
       <c r="BQ25">
-        <v>0.248346299965924</v>
+        <v>4.86619415211005</v>
       </c>
       <c r="BR25">
-        <v>0.156016583320815</v>
+        <v>2.8492794854228598</v>
       </c>
       <c r="BS25">
-        <v>0.106376528929697</v>
+        <v>2.1903870562008199</v>
       </c>
       <c r="BT25">
-        <v>8.6506722781860196E-2</v>
+        <v>1.72484365673482</v>
       </c>
       <c r="BU25">
-        <v>5.8738158793933001E-2</v>
+        <v>1.23668086027271</v>
       </c>
       <c r="BV25">
-        <v>7.6385292812015504E-2</v>
+        <v>1.4553357676802099</v>
       </c>
       <c r="BW25">
-        <v>0</v>
+        <v>1.0421700083598899</v>
       </c>
       <c r="BX25">
-        <v>0</v>
+        <v>0.38950422164654003</v>
       </c>
       <c r="BY25">
-        <v>0</v>
+        <v>0.403343826591545</v>
       </c>
       <c r="BZ25">
-        <v>0</v>
+        <v>0.244418895366045</v>
       </c>
       <c r="CA25">
-        <v>0</v>
+        <v>0.26289854223673897</v>
       </c>
       <c r="CB25">
-        <v>0</v>
+        <v>0.31575776968116098</v>
       </c>
       <c r="CC25">
-        <v>0</v>
+        <v>0.15024738715710301</v>
       </c>
       <c r="CD25">
-        <v>0</v>
+        <v>9.4172529243446795E-2</v>
       </c>
       <c r="CE25">
-        <v>0</v>
+        <v>0.114272220334785</v>
       </c>
       <c r="CF25">
-        <v>0</v>
+        <v>7.0355975326819004E-2</v>
       </c>
       <c r="CG25">
         <v>0</v>
       </c>
       <c r="CH25">
-        <v>0</v>
+        <v>6.5213731067744696E-2</v>
       </c>
       <c r="CI25">
-        <v>0</v>
+        <v>7.2548378653519499E-2</v>
       </c>
       <c r="CJ25">
-        <v>0</v>
+        <v>3.15391317194939E-2</v>
       </c>
       <c r="CK25">
-        <v>0</v>
+        <v>4.7981001680930301E-2</v>
       </c>
       <c r="CL25">
-        <v>0</v>
+        <v>3.6370051858590297E-2</v>
       </c>
       <c r="CM25">
         <v>0</v>
@@ -13128,109 +13853,109 @@
         <v>0</v>
       </c>
       <c r="BF26">
-        <v>0</v>
+        <v>0.50009189240927598</v>
       </c>
       <c r="BG26">
-        <v>0.21004042820660301</v>
+        <v>5.4554888629054403</v>
       </c>
       <c r="BH26">
-        <v>1.67248190760996</v>
-      </c>
-      <c r="BI26">
-        <v>6.9596781810892399</v>
+        <v>33.050387416550599</v>
+      </c>
+      <c r="BI26" s="6">
+        <v>40.222417475382599</v>
       </c>
       <c r="BJ26">
-        <v>11.2736327136257</v>
+        <v>37.4808967088182</v>
       </c>
       <c r="BK26">
-        <v>9.2102123736840404</v>
+        <v>32.250979434724499</v>
       </c>
       <c r="BL26">
-        <v>9.2587140587798196</v>
+        <v>36.138900145119301</v>
       </c>
       <c r="BM26">
-        <v>8.1846422627447808</v>
+        <v>32.108906034245798</v>
       </c>
       <c r="BN26">
-        <v>5.5935608143752802</v>
+        <v>30.382794697589901</v>
       </c>
       <c r="BO26">
-        <v>3.36656025366347</v>
+        <v>28.300963895929499</v>
       </c>
       <c r="BP26">
-        <v>2.43883883378308</v>
+        <v>30.4650465777794</v>
       </c>
       <c r="BQ26">
-        <v>1.28500480268539</v>
+        <v>25.7271416243719</v>
       </c>
       <c r="BR26">
-        <v>0.69913301690404805</v>
+        <v>15.102023356363301</v>
       </c>
       <c r="BS26">
-        <v>0.55856371469898802</v>
+        <v>12.4708011240578</v>
       </c>
       <c r="BT26">
-        <v>0.46177151477919798</v>
+        <v>10.655639333848899</v>
       </c>
       <c r="BU26">
-        <v>0.28937255852524102</v>
+        <v>7.2284943595166098</v>
       </c>
       <c r="BV26">
-        <v>0.37302493135897302</v>
+        <v>9.0065491638448396</v>
       </c>
       <c r="BW26">
-        <v>0.20473518272091701</v>
+        <v>5.2566737954881004</v>
       </c>
       <c r="BX26">
-        <v>7.4388896110402697E-2</v>
+        <v>2.2282551174282998</v>
       </c>
       <c r="BY26">
-        <v>7.7430737692694193E-2</v>
+        <v>2.3160912499899302</v>
       </c>
       <c r="BZ26">
-        <v>0</v>
+        <v>1.5097230542870801</v>
       </c>
       <c r="CA26">
-        <v>5.0331991646269399E-2</v>
+        <v>1.6159716294187301</v>
       </c>
       <c r="CB26">
-        <v>7.7092816421423294E-2</v>
+        <v>2.3965391601041999</v>
       </c>
       <c r="CC26">
-        <v>0</v>
+        <v>0.86024002364716001</v>
       </c>
       <c r="CD26">
-        <v>0</v>
+        <v>0.51904687722208798</v>
       </c>
       <c r="CE26">
-        <v>0</v>
+        <v>0.62558824150622605</v>
       </c>
       <c r="CF26">
-        <v>0</v>
+        <v>0.35813010945554702</v>
       </c>
       <c r="CG26">
-        <v>0</v>
+        <v>0.13411131103972501</v>
       </c>
       <c r="CH26">
-        <v>0</v>
+        <v>0.36409750845977501</v>
       </c>
       <c r="CI26">
-        <v>0</v>
+        <v>0.41545242392194198</v>
       </c>
       <c r="CJ26">
-        <v>0</v>
+        <v>0.17212212742833899</v>
       </c>
       <c r="CK26">
-        <v>0</v>
+        <v>0.239512750718261</v>
       </c>
       <c r="CL26">
-        <v>0</v>
+        <v>0.19762471563515799</v>
       </c>
       <c r="CM26">
-        <v>0</v>
+        <v>0.11516170635628099</v>
       </c>
       <c r="CN26">
-        <v>0</v>
+        <v>4.7787744958032299E-2</v>
       </c>
       <c r="CO26">
         <v>0</v>
@@ -13242,13 +13967,13 @@
         <v>0</v>
       </c>
       <c r="CR26">
-        <v>0</v>
+        <v>3.2549479153174701E-2</v>
       </c>
       <c r="CS26">
         <v>0</v>
       </c>
       <c r="CT26">
-        <v>0</v>
+        <v>4.1547871054288997E-2</v>
       </c>
     </row>
     <row r="27" spans="1:98" x14ac:dyDescent="0.25">
@@ -13424,109 +14149,109 @@
         <v>0</v>
       </c>
       <c r="BF27">
-        <v>0</v>
+        <v>0.34407348338504401</v>
       </c>
       <c r="BG27">
-        <v>0.17462212690478299</v>
+        <v>4.3460437033806096</v>
       </c>
       <c r="BH27">
-        <v>1.28184491772939</v>
-      </c>
-      <c r="BI27">
-        <v>4.5625160398174396</v>
+        <v>25.3308995128397</v>
+      </c>
+      <c r="BI27" s="6">
+        <v>26.3683779787224</v>
       </c>
       <c r="BJ27">
-        <v>8.1613679742029905</v>
+        <v>27.133701958857099</v>
       </c>
       <c r="BK27">
-        <v>7.5262308593501803</v>
+        <v>26.354258383598701</v>
       </c>
       <c r="BL27">
-        <v>6.8300057950435704</v>
+        <v>26.6590906530346</v>
       </c>
       <c r="BM27">
-        <v>6.5297583947412496</v>
+        <v>25.616684515684199</v>
       </c>
       <c r="BN27">
-        <v>4.1885140903659499</v>
+        <v>22.750939503527501</v>
       </c>
       <c r="BO27">
-        <v>2.6683819665566602</v>
+        <v>22.431733284668301</v>
       </c>
       <c r="BP27">
-        <v>1.69539108575319</v>
+        <v>21.1781802386976</v>
       </c>
       <c r="BQ27">
-        <v>0.98245022850850305</v>
+        <v>19.6696822571128</v>
       </c>
       <c r="BR27">
-        <v>0.53476452059104895</v>
+        <v>11.5514874633985</v>
       </c>
       <c r="BS27">
-        <v>0.40325488932027997</v>
+        <v>8.9686975524746799</v>
       </c>
       <c r="BT27">
-        <v>0.31139224704242402</v>
+        <v>7.0407616993052704</v>
       </c>
       <c r="BU27">
-        <v>0.20882111186275201</v>
+        <v>4.9437095104606597</v>
       </c>
       <c r="BV27">
-        <v>0.26035644689084497</v>
+        <v>5.9472424871735701</v>
       </c>
       <c r="BW27">
-        <v>0.16924700135710899</v>
+        <v>4.1754078921712496</v>
       </c>
       <c r="BX27">
-        <v>7.4388896110402697E-2</v>
+        <v>1.5638942885334199</v>
       </c>
       <c r="BY27">
-        <v>6.5538842255186802E-2</v>
+        <v>1.6550141600366199</v>
       </c>
       <c r="BZ27">
-        <v>0</v>
+        <v>0.97344452381687996</v>
       </c>
       <c r="CA27">
-        <v>5.0331991646269399E-2</v>
+        <v>1.06291939699687</v>
       </c>
       <c r="CB27">
-        <v>6.4560067614150202E-2</v>
+        <v>1.29178189509913</v>
       </c>
       <c r="CC27">
-        <v>0</v>
+        <v>0.57183117314975596</v>
       </c>
       <c r="CD27">
-        <v>0</v>
+        <v>0.350308027490907</v>
       </c>
       <c r="CE27">
-        <v>0</v>
+        <v>0.40940294904399299</v>
       </c>
       <c r="CF27">
-        <v>0</v>
+        <v>0.24950428010877601</v>
       </c>
       <c r="CG27">
-        <v>0</v>
+        <v>0.10015467821738</v>
       </c>
       <c r="CH27">
-        <v>0</v>
+        <v>0.243662671616763</v>
       </c>
       <c r="CI27">
-        <v>0</v>
+        <v>0.262958112958464</v>
       </c>
       <c r="CJ27">
-        <v>0</v>
+        <v>0.130422919524183</v>
       </c>
       <c r="CK27">
-        <v>0</v>
+        <v>0.158444750127407</v>
       </c>
       <c r="CL27">
-        <v>0</v>
+        <v>0.13814685866356899</v>
       </c>
       <c r="CM27">
-        <v>0</v>
+        <v>9.3963070742294694E-2</v>
       </c>
       <c r="CN27">
-        <v>0</v>
+        <v>4.7787744958032299E-2</v>
       </c>
       <c r="CO27">
         <v>0</v>
@@ -13538,13 +14263,13 @@
         <v>0</v>
       </c>
       <c r="CR27">
-        <v>0</v>
+        <v>3.1724115410896203E-2</v>
       </c>
       <c r="CS27">
         <v>0</v>
       </c>
       <c r="CT27">
-        <v>0</v>
+        <v>4.1547871054288997E-2</v>
       </c>
     </row>
     <row r="28" spans="1:98" x14ac:dyDescent="0.25">
@@ -13720,109 +14445,109 @@
         <v>0</v>
       </c>
       <c r="BF28">
-        <v>0</v>
+        <v>0.337741326324007</v>
       </c>
       <c r="BG28">
-        <v>0.172077386847411</v>
+        <v>4.3169446012249999</v>
       </c>
       <c r="BH28">
-        <v>1.29014711196457</v>
-      </c>
-      <c r="BI28">
-        <v>4.5226972736100599</v>
+        <v>25.494961518345502</v>
+      </c>
+      <c r="BI28" s="6">
+        <v>26.138251384043901</v>
       </c>
       <c r="BJ28">
-        <v>8.0443485264825707</v>
+        <v>26.7446531097095</v>
       </c>
       <c r="BK28">
-        <v>7.4246662274787498</v>
+        <v>25.998614157285498</v>
       </c>
       <c r="BL28">
-        <v>6.7073343960619001</v>
+        <v>26.180275840075701</v>
       </c>
       <c r="BM28">
-        <v>6.3743843741790096</v>
+        <v>25.0071417074846</v>
       </c>
       <c r="BN28">
-        <v>4.2174681723444101</v>
+        <v>22.908210686956899</v>
       </c>
       <c r="BO28">
-        <v>2.6666480256465399</v>
+        <v>22.417156923053401</v>
       </c>
       <c r="BP28">
-        <v>1.6441598679987199</v>
+        <v>20.538219363205201</v>
       </c>
       <c r="BQ28">
-        <v>0.97221571639574</v>
+        <v>19.4647766084402</v>
       </c>
       <c r="BR28">
-        <v>0.52761813848150296</v>
+        <v>11.3971179416914</v>
       </c>
       <c r="BS28">
-        <v>0.39390766458743498</v>
+        <v>8.7615482248033096</v>
       </c>
       <c r="BT28">
-        <v>0.303418388271677</v>
+        <v>6.8993746269392799</v>
       </c>
       <c r="BU28">
-        <v>0.20641032365226999</v>
+        <v>4.9467234410908496</v>
       </c>
       <c r="BV28">
-        <v>0.25791577588606002</v>
+        <v>5.8213430707208396</v>
       </c>
       <c r="BW28">
-        <v>0.169833212199514</v>
+        <v>4.1686800334395704</v>
       </c>
       <c r="BX28">
-        <v>7.4388896110402697E-2</v>
+        <v>1.5580168865861601</v>
       </c>
       <c r="BY28">
-        <v>6.2844241817975696E-2</v>
+        <v>1.60600907319032</v>
       </c>
       <c r="BZ28">
-        <v>0</v>
+        <v>0.96349036222133499</v>
       </c>
       <c r="CA28">
-        <v>5.0331991646269399E-2</v>
+        <v>1.0387257920011399</v>
       </c>
       <c r="CB28">
-        <v>6.4560067614150202E-2</v>
+        <v>1.2630310787246399</v>
       </c>
       <c r="CC28">
-        <v>0</v>
+        <v>0.55630443457085599</v>
       </c>
       <c r="CD28">
-        <v>0</v>
+        <v>0.34900388516185099</v>
       </c>
       <c r="CE28">
-        <v>0</v>
+        <v>0.40181366878427699</v>
       </c>
       <c r="CF28">
-        <v>0</v>
+        <v>0.25004456460729602</v>
       </c>
       <c r="CG28">
-        <v>0</v>
+        <v>0.101167063043085</v>
       </c>
       <c r="CH28">
-        <v>0</v>
+        <v>0.24729965059593201</v>
       </c>
       <c r="CI28">
-        <v>0</v>
+        <v>0.26318206010928002</v>
       </c>
       <c r="CJ28">
-        <v>0</v>
+        <v>0.12932125984071999</v>
       </c>
       <c r="CK28">
-        <v>0</v>
+        <v>0.15420741723087</v>
       </c>
       <c r="CL28">
-        <v>0</v>
+        <v>0.13565403981010499</v>
       </c>
       <c r="CM28">
-        <v>0</v>
+        <v>9.3724788397339998E-2</v>
       </c>
       <c r="CN28">
-        <v>0</v>
+        <v>4.7787744958032299E-2</v>
       </c>
       <c r="CO28">
         <v>0</v>
@@ -13834,13 +14559,13 @@
         <v>0</v>
       </c>
       <c r="CR28">
-        <v>0</v>
+        <v>3.1724115410896203E-2</v>
       </c>
       <c r="CS28">
         <v>0</v>
       </c>
       <c r="CT28">
-        <v>0</v>
+        <v>4.1547871054288997E-2</v>
       </c>
     </row>
     <row r="29" spans="1:98" x14ac:dyDescent="0.25">
@@ -14024,7 +14749,7 @@
       <c r="BH29">
         <v>21.08342828</v>
       </c>
-      <c r="BI29">
+      <c r="BI29" s="7">
         <v>28.119352749999901</v>
       </c>
       <c r="BJ29">
@@ -14143,296 +14868,296 @@
       <c r="A30" t="s">
         <v>33</v>
       </c>
-      <c r="B30" s="4">
-        <v>3.3616256555522898E-5</v>
-      </c>
-      <c r="C30" s="4">
-        <v>4.0938058974160502E-5</v>
-      </c>
-      <c r="D30" s="4">
-        <v>2.5473195707319401E-5</v>
-      </c>
-      <c r="E30" s="4">
-        <v>2.1855929595681901E-5</v>
-      </c>
-      <c r="F30" s="4">
-        <v>2.8824475629275101E-5</v>
-      </c>
-      <c r="G30" s="4">
-        <v>2.5822192478414901E-5</v>
-      </c>
-      <c r="H30" s="4">
-        <v>2.62341888939973E-5</v>
-      </c>
-      <c r="I30" s="4">
-        <v>3.2041469774141503E-5</v>
-      </c>
-      <c r="J30" s="4">
-        <v>3.5888731617002501E-5</v>
-      </c>
-      <c r="K30" s="4">
-        <v>2.7734802451560101E-5</v>
-      </c>
-      <c r="L30" s="4">
-        <v>2.3018610317801999E-5</v>
-      </c>
-      <c r="M30" s="4">
-        <v>2.3695689445349999E-5</v>
-      </c>
-      <c r="N30" s="4">
-        <v>2.3695689445349999E-5</v>
-      </c>
-      <c r="O30" s="4">
-        <v>2.91020844462054E-5</v>
-      </c>
-      <c r="P30" s="4">
-        <v>3.1042739614213602E-5</v>
-      </c>
-      <c r="Q30" s="4">
-        <v>2.2171817672009699E-5</v>
-      </c>
-      <c r="R30" s="4">
-        <v>1.871409139455E-5</v>
-      </c>
-      <c r="S30" s="4">
-        <v>2.1516276984798801E-5</v>
-      </c>
-      <c r="T30" s="4">
-        <v>2.6638207513109101E-5</v>
-      </c>
-      <c r="U30" s="4">
-        <v>2.7072733150313399E-5</v>
-      </c>
-      <c r="V30" s="4">
-        <v>2.2215532292813901E-5</v>
-      </c>
-      <c r="W30" s="4">
-        <v>2.3683148007861301E-5</v>
-      </c>
-      <c r="X30" s="4">
-        <v>1.9007017071501699E-5</v>
-      </c>
-      <c r="Y30" s="4">
-        <v>1.94079657869824E-5</v>
-      </c>
-      <c r="Z30" s="4">
-        <v>2.59023599328052E-5</v>
-      </c>
-      <c r="AA30" s="4">
-        <v>2.1855929595681901E-5</v>
-      </c>
-      <c r="AB30" s="4">
-        <v>1.9266849530061699E-5</v>
-      </c>
-      <c r="AC30" s="4">
-        <v>2.0547345345601601E-5</v>
-      </c>
-      <c r="AD30" s="4">
-        <v>1.7911312195157501E-5</v>
-      </c>
-      <c r="AE30" s="4">
-        <v>1.6726516804458398E-5</v>
-      </c>
-      <c r="AF30" s="4">
-        <v>1.8810796202709E-5</v>
-      </c>
-      <c r="AG30" s="4">
-        <v>2.0742555772470701E-5</v>
-      </c>
-      <c r="AH30" s="4">
-        <v>2.3414511595025501E-5</v>
-      </c>
-      <c r="AI30" s="4">
-        <v>2.25292133435283E-5</v>
-      </c>
-      <c r="AJ30" s="4">
-        <v>2.1696133414285899E-5</v>
-      </c>
-      <c r="AK30" s="4">
-        <v>1.6829948905785501E-5</v>
-      </c>
-      <c r="AL30" s="4">
-        <v>1.31881446642499E-5</v>
-      </c>
-      <c r="AM30" s="4">
-        <v>1.37634289941702E-5</v>
-      </c>
-      <c r="AN30" s="4">
-        <v>1.23851800803213E-5</v>
-      </c>
-      <c r="AO30" s="4">
-        <v>1.2209378653577E-5</v>
-      </c>
-      <c r="AP30" s="4">
-        <v>1.1640200632872101E-5</v>
-      </c>
-      <c r="AQ30" s="4">
-        <v>1.4725232523496201E-5</v>
-      </c>
-      <c r="AR30" s="4">
-        <v>1.6852199240507699E-5</v>
-      </c>
-      <c r="AS30" s="4">
-        <v>1.5941937666438101E-5</v>
-      </c>
-      <c r="AT30" s="4">
-        <v>1.5406767049535601E-5</v>
-      </c>
-      <c r="AU30" s="4">
-        <v>1.41219109841651E-5</v>
-      </c>
-      <c r="AV30" s="4">
-        <v>1.8251030833310299E-5</v>
-      </c>
-      <c r="AW30" s="4">
-        <v>2.10177813788286E-5</v>
-      </c>
-      <c r="AX30" s="4">
-        <v>1.45936843718971E-5</v>
-      </c>
-      <c r="AY30" s="4">
-        <v>1.23303078054263E-5</v>
-      </c>
-      <c r="AZ30" s="4">
-        <v>1.8639772275142401E-5</v>
-      </c>
-      <c r="BA30" s="4">
-        <v>2.38384237636583E-5</v>
-      </c>
-      <c r="BB30" s="4">
-        <v>5.0824096615162702E-5</v>
+      <c r="B30">
+        <v>3.4485880480097601E-3</v>
+      </c>
+      <c r="C30">
+        <v>4.0823064645131198E-3</v>
+      </c>
+      <c r="D30">
+        <v>2.7196246696594502E-3</v>
+      </c>
+      <c r="E30">
+        <v>2.3854229567972802E-3</v>
+      </c>
+      <c r="F30">
+        <v>3.0231754388004599E-3</v>
+      </c>
+      <c r="G30">
+        <v>2.7514924339520799E-3</v>
+      </c>
+      <c r="H30">
+        <v>2.78903323741989E-3</v>
+      </c>
+      <c r="I30">
+        <v>3.3098062844357499E-3</v>
+      </c>
+      <c r="J30">
+        <v>3.6472237403769002E-3</v>
+      </c>
+      <c r="K30">
+        <v>2.9250626085244799E-3</v>
+      </c>
+      <c r="L30">
+        <v>2.4936547527373699E-3</v>
+      </c>
+      <c r="M30">
+        <v>2.5563186649666301E-3</v>
+      </c>
+      <c r="N30">
+        <v>2.5563186649666301E-3</v>
+      </c>
+      <c r="O30">
+        <v>3.0480849941377998E-3</v>
+      </c>
+      <c r="P30">
+        <v>3.2212838041335901E-3</v>
+      </c>
+      <c r="Q30">
+        <v>2.4149086065203798E-3</v>
+      </c>
+      <c r="R30">
+        <v>2.08863701173931E-3</v>
+      </c>
+      <c r="S30">
+        <v>2.3536505609517999E-3</v>
+      </c>
+      <c r="T30">
+        <v>2.8257648073262E-3</v>
+      </c>
+      <c r="U30">
+        <v>2.86518060362568E-3</v>
+      </c>
+      <c r="V30">
+        <v>2.41898424132989E-3</v>
+      </c>
+      <c r="W30">
+        <v>2.5551603138880201E-3</v>
+      </c>
+      <c r="X30">
+        <v>2.11659435705757E-3</v>
+      </c>
+      <c r="Y30">
+        <v>2.1547614296114699E-3</v>
+      </c>
+      <c r="Z30">
+        <v>2.7588039445103798E-3</v>
+      </c>
+      <c r="AA30">
+        <v>2.3854229567972802E-3</v>
+      </c>
+      <c r="AB30">
+        <v>2.1413413625317799E-3</v>
+      </c>
+      <c r="AC30">
+        <v>2.2626114220155201E-3</v>
+      </c>
+      <c r="AD30">
+        <v>2.01169178911014E-3</v>
+      </c>
+      <c r="AE30">
+        <v>1.89721332926298E-3</v>
+      </c>
+      <c r="AF30">
+        <v>2.0978736052062702E-3</v>
+      </c>
+      <c r="AG30">
+        <v>2.2810018612066298E-3</v>
+      </c>
+      <c r="AH30">
+        <v>2.5303272608330398E-3</v>
+      </c>
+      <c r="AI30">
+        <v>2.4481959034882198E-3</v>
+      </c>
+      <c r="AJ30">
+        <v>2.3704839323873302E-3</v>
+      </c>
+      <c r="AK30">
+        <v>1.9072526403951099E-3</v>
+      </c>
+      <c r="AL30">
+        <v>1.5479135891472099E-3</v>
+      </c>
+      <c r="AM30">
+        <v>1.6055415697864E-3</v>
+      </c>
+      <c r="AN30">
+        <v>1.46686718192173E-3</v>
+      </c>
+      <c r="AO30">
+        <v>1.4490233852996999E-3</v>
+      </c>
+      <c r="AP30">
+        <v>1.39099489578954E-3</v>
+      </c>
+      <c r="AQ30">
+        <v>1.7011242979896E-3</v>
+      </c>
+      <c r="AR30">
+        <v>1.90941113712455E-3</v>
+      </c>
+      <c r="AS30">
+        <v>1.8207649940838501E-3</v>
+      </c>
+      <c r="AT30">
+        <v>1.7683087706461299E-3</v>
+      </c>
+      <c r="AU30">
+        <v>1.6412759601948199E-3</v>
+      </c>
+      <c r="AV30">
+        <v>2.0443126451855E-3</v>
+      </c>
+      <c r="AW30">
+        <v>2.3068881760132998E-3</v>
+      </c>
+      <c r="AX30">
+        <v>1.6881055465317E-3</v>
+      </c>
+      <c r="AY30">
+        <v>1.4613015974076699E-3</v>
+      </c>
+      <c r="AZ30">
+        <v>2.0815338821261299E-3</v>
+      </c>
+      <c r="BA30">
+        <v>2.5694956768456899E-3</v>
+      </c>
+      <c r="BB30">
+        <v>4.9128200991749599E-3</v>
       </c>
       <c r="BC30">
-        <v>1.9075581695994999E-4</v>
+        <v>1.52436401267036E-2</v>
       </c>
       <c r="BD30">
-        <v>2.4548507390875101E-4</v>
+        <v>1.8917923840616701E-2</v>
       </c>
       <c r="BE30">
-        <v>1.0943605560743499E-3</v>
+        <v>6.8015232211486906E-2</v>
       </c>
       <c r="BF30">
-        <v>2.9390865037473901E-2</v>
+        <v>1.1377190884339199</v>
       </c>
       <c r="BG30">
-        <v>0.47050807245973703</v>
+        <v>12.2207499341045</v>
       </c>
       <c r="BH30">
-        <v>3.1434049824010599</v>
-      </c>
-      <c r="BI30">
-        <v>10.748217649315199</v>
+        <v>62.117713801532297</v>
+      </c>
+      <c r="BI30" s="6">
+        <v>62.117713801532297</v>
       </c>
       <c r="BJ30">
-        <v>18.683979090804002</v>
+        <v>62.117713801532297</v>
       </c>
       <c r="BK30">
-        <v>17.7395336921047</v>
+        <v>62.117713801532297</v>
       </c>
       <c r="BL30">
-        <v>15.9144342453443</v>
+        <v>62.117713801532297</v>
       </c>
       <c r="BM30">
-        <v>15.833964106869299</v>
+        <v>62.117713801532297</v>
       </c>
       <c r="BN30">
-        <v>11.4360516618536</v>
+        <v>62.117713801532297</v>
       </c>
       <c r="BO30">
-        <v>7.3892545533265004</v>
+        <v>62.117713801532297</v>
       </c>
       <c r="BP30">
-        <v>4.97275106076171</v>
+        <v>62.117713801532297</v>
       </c>
       <c r="BQ30">
-        <v>2.8721504285382702</v>
+        <v>57.503458887200701</v>
       </c>
       <c r="BR30">
-        <v>1.6941092050722799</v>
+        <v>36.594576660211999</v>
       </c>
       <c r="BS30">
-        <v>1.3465935908567801</v>
+        <v>30.064790148620499</v>
       </c>
       <c r="BT30">
-        <v>1.07063117934011</v>
+        <v>24.705421061451201</v>
       </c>
       <c r="BU30">
-        <v>0.61702058709288998</v>
+        <v>15.41310570786</v>
       </c>
       <c r="BV30">
-        <v>0.78153543851691798</v>
+        <v>18.869884446318501</v>
       </c>
       <c r="BW30">
-        <v>0.50980183371239995</v>
+        <v>13.089406054231601</v>
       </c>
       <c r="BX30">
-        <v>0.174658533104187</v>
+        <v>5.2317454694609902</v>
       </c>
       <c r="BY30">
-        <v>0.176384615954438</v>
+        <v>5.2759779618936697</v>
       </c>
       <c r="BZ30">
-        <v>0.100611293901248</v>
+        <v>3.2626527113947401</v>
       </c>
       <c r="CA30">
-        <v>0.107837769482182</v>
+        <v>3.46226664914506</v>
       </c>
       <c r="CB30">
-        <v>0.13495873336155001</v>
+        <v>4.1953829747885099</v>
       </c>
       <c r="CC30">
-        <v>5.3064042909588403E-2</v>
+        <v>1.8867012824548099</v>
       </c>
       <c r="CD30">
-        <v>2.89456672114577E-2</v>
+        <v>1.1229490306302401</v>
       </c>
       <c r="CE30">
-        <v>3.60883730572557E-2</v>
+        <v>1.3563184706215099</v>
       </c>
       <c r="CF30">
-        <v>1.86389600940008E-2</v>
+        <v>0.77037825081440503</v>
       </c>
       <c r="CG30">
-        <v>6.4598625670602896E-3</v>
+        <v>0.31097288933759998</v>
       </c>
       <c r="CH30">
-        <v>1.8897885073583899E-2</v>
+        <v>0.77953107289018997</v>
       </c>
       <c r="CI30">
-        <v>1.9413397108989299E-2</v>
+        <v>0.79770067178179405</v>
       </c>
       <c r="CJ30">
-        <v>8.3880230705090705E-3</v>
+        <v>0.38889894625742999</v>
       </c>
       <c r="CK30">
-        <v>1.00390961362788E-2</v>
+        <v>0.453569123614041</v>
       </c>
       <c r="CL30">
-        <v>8.0287499598036705E-3</v>
+        <v>0.374593840085793</v>
       </c>
       <c r="CM30">
-        <v>4.8567675898360798E-3</v>
+        <v>0.243596366240557</v>
       </c>
       <c r="CN30">
-        <v>2.1960555076186998E-3</v>
+        <v>0.12347114727207301</v>
       </c>
       <c r="CO30">
-        <v>1.4554185144762201E-3</v>
+        <v>8.6819322606491903E-2</v>
       </c>
       <c r="CP30">
-        <v>1.5174897162113E-3</v>
+        <v>8.99796787166698E-2</v>
       </c>
       <c r="CQ30">
-        <v>1.1804456237418199E-3</v>
+        <v>7.2570465927839098E-2</v>
       </c>
       <c r="CR30">
-        <v>1.0797677720712901E-3</v>
+        <v>6.7238031511924895E-2</v>
       </c>
       <c r="CS30">
-        <v>1.18965805174856E-3</v>
+        <v>7.3055057161704698E-2</v>
       </c>
       <c r="CT30">
-        <v>1.2496622172830799E-3</v>
+        <v>7.6198395050107795E-2</v>
       </c>
     </row>
     <row r="31" spans="1:98" x14ac:dyDescent="0.25">
@@ -14616,7 +15341,7 @@
       <c r="BH31" s="1">
         <v>44781.604861111111</v>
       </c>
-      <c r="BI31" s="1">
+      <c r="BI31" s="5">
         <v>44781.615277777775</v>
       </c>
       <c r="BJ31" s="1">
@@ -14732,7 +15457,7 @@
       </c>
     </row>
     <row r="32" spans="1:98" x14ac:dyDescent="0.25">
-      <c r="BK32" t="s">
+      <c r="BI32" t="s">
         <v>47</v>
       </c>
     </row>
@@ -14740,6 +15465,9 @@
       <c r="C34" s="2" t="s">
         <v>27</v>
       </c>
+      <c r="D34" t="s">
+        <v>32</v>
+      </c>
       <c r="E34" t="s">
         <v>28</v>
       </c>
@@ -14752,11 +15480,20 @@
       <c r="H34" t="s">
         <v>31</v>
       </c>
+      <c r="I34" t="s">
+        <v>32</v>
+      </c>
       <c r="U34" t="s">
         <v>45</v>
       </c>
       <c r="V34" t="s">
         <v>46</v>
+      </c>
+      <c r="X34" t="s">
+        <v>48</v>
+      </c>
+      <c r="Y34" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="35" spans="1:27" x14ac:dyDescent="0.25">
@@ -14766,23 +15503,30 @@
       </c>
       <c r="B35" s="2">
         <f t="shared" ref="B35:B60" si="1">MAX(B2:CT2)</f>
-        <v>1.1009406946900099E-2</v>
+        <v>3.9279704565803299E-2</v>
       </c>
       <c r="C35" s="3">
         <f t="shared" ref="C35:C60" si="2">_xlfn.XLOOKUP(MAX(B2:CS2), B2:CS2, $B$1:$CS$1)</f>
-        <v>44781.625694444447</v>
+        <v>44781.615277777775</v>
+      </c>
+      <c r="D35">
+        <f>_xlfn.XLOOKUP(MAX(B2:CS2), B2:CS2, $B$29:$CS$29)</f>
+        <v>28.119352749999901</v>
       </c>
       <c r="E35" s="1">
         <v>44781.000694444447</v>
       </c>
       <c r="F35" s="4">
-        <v>2.08679206339447E-8</v>
+        <v>2.14077559663646E-6</v>
       </c>
       <c r="G35" s="4">
-        <v>1.45527826365573E-8</v>
+        <v>1.4929250727909799E-6</v>
       </c>
       <c r="H35" s="4">
-        <v>1.44066128501846E-8</v>
+        <v>1.4779299653656199E-6</v>
+      </c>
+      <c r="I35">
+        <v>1.4441644075</v>
       </c>
       <c r="T35" t="s">
         <v>0</v>
@@ -14792,6 +15536,14 @@
       </c>
       <c r="V35">
         <v>1.03130225848837E-2</v>
+      </c>
+      <c r="X35">
+        <f>MAX(B29:CT29)</f>
+        <v>32.007500319999998</v>
+      </c>
+      <c r="Y35" s="1">
+        <f>_xlfn.XLOOKUP(MAX(B29:CS29), B29:CS29, $B$1:$CS$1)</f>
+        <v>44781.625694444447</v>
       </c>
     </row>
     <row r="36" spans="1:27" x14ac:dyDescent="0.25">
@@ -14801,7 +15553,7 @@
       </c>
       <c r="B36" s="2">
         <f t="shared" si="1"/>
-        <v>7.9700859123076097E-3</v>
+        <v>2.64977558191964E-2</v>
       </c>
       <c r="C36" s="3">
         <f t="shared" si="2"/>
@@ -14811,13 +15563,16 @@
         <v>44781.011111111111</v>
       </c>
       <c r="F36" s="4">
-        <v>2.5067641795970801E-8</v>
+        <v>2.4997227205869898E-6</v>
       </c>
       <c r="G36" s="4">
-        <v>1.6993931409653301E-8</v>
+        <v>1.6946195737918801E-6</v>
       </c>
       <c r="H36" s="4">
-        <v>1.6481765230170301E-8</v>
+        <v>1.6435468224834699E-6</v>
+      </c>
+      <c r="I36">
+        <v>1.5123822984999999</v>
       </c>
       <c r="T36" t="s">
         <v>1</v>
@@ -14836,7 +15591,7 @@
       </c>
       <c r="B37" s="2">
         <f t="shared" si="1"/>
-        <v>7.8558091078931302E-3</v>
+        <v>2.6117825302450701E-2</v>
       </c>
       <c r="C37" s="3">
         <f t="shared" si="2"/>
@@ -14846,13 +15601,16 @@
         <v>44781.021527777775</v>
       </c>
       <c r="F37" s="4">
-        <v>1.7594067479801701E-8</v>
+        <v>1.8784160616638401E-6</v>
       </c>
       <c r="G37" s="4">
-        <v>1.1110559936786401E-8</v>
+        <v>1.18620974161767E-6</v>
       </c>
       <c r="H37" s="4">
-        <v>1.0702530073949501E-8</v>
+        <v>1.14264677082452E-6</v>
+      </c>
+      <c r="I37">
+        <v>1.3533179835</v>
       </c>
       <c r="T37" t="s">
         <v>2</v>
@@ -14881,13 +15639,16 @@
         <v>44781.031944444447</v>
       </c>
       <c r="F38" s="4">
-        <v>1.1520902210338401E-8</v>
+        <v>1.25742647983648E-6</v>
       </c>
       <c r="G38" s="4">
-        <v>9.02844072250232E-9</v>
+        <v>9.853916150734819E-7</v>
       </c>
       <c r="H38" s="4">
-        <v>9.0574578898280608E-9</v>
+        <v>9.8855863741516995E-7</v>
+      </c>
+      <c r="I38">
+        <v>1.3056302835</v>
       </c>
       <c r="T38" t="s">
         <v>3</v>
@@ -14906,23 +15667,26 @@
       </c>
       <c r="B39" s="2">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="C39" s="3">
         <f t="shared" si="2"/>
-        <v>44781.000694444447</v>
+        <v>44781.636111111111</v>
       </c>
       <c r="E39" s="1">
         <v>44781.042361111111</v>
       </c>
       <c r="F39" s="4">
-        <v>1.73181760643576E-8</v>
+        <v>1.81636901898118E-6</v>
       </c>
       <c r="G39" s="4">
-        <v>1.22777388432218E-8</v>
+        <v>1.2877166957693E-6</v>
       </c>
       <c r="H39" s="4">
-        <v>1.1891434254351E-8</v>
+        <v>1.2472002069378201E-6</v>
+      </c>
+      <c r="I39">
+        <v>1.3930697775000001</v>
       </c>
       <c r="T39" t="s">
         <v>4</v>
@@ -14941,23 +15705,26 @@
       </c>
       <c r="B40" s="2">
         <f t="shared" si="1"/>
-        <v>17</v>
+        <v>753</v>
       </c>
       <c r="C40" s="3">
         <f t="shared" si="2"/>
-        <v>44781.636111111111</v>
+        <v>44781.646527777775</v>
       </c>
       <c r="E40" s="1">
         <v>44781.052777777775</v>
       </c>
       <c r="F40" s="4">
-        <v>1.3861372170813401E-8</v>
+        <v>1.4770031895482E-6</v>
       </c>
       <c r="G40" s="4">
-        <v>1.10118657841951E-8</v>
+        <v>1.1733730749032101E-6</v>
       </c>
       <c r="H40" s="4">
-        <v>1.0985248006165E-8</v>
+        <v>1.1705368085730099E-6</v>
+      </c>
+      <c r="I40">
+        <v>1.357638297</v>
       </c>
       <c r="T40" t="s">
         <v>5</v>
@@ -14976,23 +15743,26 @@
       </c>
       <c r="B41" s="2">
         <f t="shared" si="1"/>
-        <v>1101</v>
+        <v>23073</v>
       </c>
       <c r="C41" s="3">
         <f t="shared" si="2"/>
-        <v>44781.625694444447</v>
+        <v>44781.604861111111</v>
       </c>
       <c r="E41" s="1">
         <v>44781.063194444447</v>
       </c>
       <c r="F41" s="4">
-        <v>1.7379699605599699E-8</v>
+        <v>1.84768662190381E-6</v>
       </c>
       <c r="G41" s="4">
-        <v>1.1343085245931999E-8</v>
+        <v>1.20591651961942E-6</v>
       </c>
       <c r="H41" s="4">
-        <v>1.12600482521935E-8</v>
+        <v>1.19708861429105E-6</v>
+      </c>
+      <c r="I41">
+        <v>1.362681324</v>
       </c>
       <c r="T41" t="s">
         <v>6</v>
@@ -15011,23 +15781,26 @@
       </c>
       <c r="B42" s="2">
         <f t="shared" si="1"/>
-        <v>28713</v>
+        <v>38835</v>
       </c>
       <c r="C42" s="3">
         <f t="shared" si="2"/>
-        <v>44781.625694444447</v>
+        <v>44781.709027777775</v>
       </c>
       <c r="E42" s="1">
         <v>44781.073611111111</v>
       </c>
       <c r="F42" s="4">
-        <v>1.9817270241934502E-8</v>
+        <v>2.0470760564077801E-6</v>
       </c>
       <c r="G42" s="4">
-        <v>1.4062870728409799E-8</v>
+        <v>1.45266051283058E-6</v>
       </c>
       <c r="H42" s="4">
-        <v>1.3347457715399E-8</v>
+        <v>1.3787600799620401E-6</v>
+      </c>
+      <c r="I42">
+        <v>1.428025611</v>
       </c>
       <c r="T42" t="s">
         <v>7</v>
@@ -15046,23 +15819,26 @@
       </c>
       <c r="B43" s="2">
         <f t="shared" si="1"/>
-        <v>36173</v>
+        <v>37488</v>
       </c>
       <c r="C43" s="3">
         <f t="shared" si="2"/>
-        <v>44781.667361111111</v>
+        <v>44781.761111111111</v>
       </c>
       <c r="E43" s="1">
         <v>44781.084027777775</v>
       </c>
       <c r="F43" s="4">
-        <v>2.1170675392527701E-8</v>
+        <v>2.1514884035535098E-6</v>
       </c>
       <c r="G43" s="4">
-        <v>1.5825863676166399E-8</v>
+        <v>1.60831723807426E-6</v>
       </c>
       <c r="H43" s="4">
-        <v>1.5436239139985899E-8</v>
+        <v>1.5687213037949599E-6</v>
+      </c>
+      <c r="I43">
+        <v>1.4664620669999999</v>
       </c>
       <c r="T43" t="s">
         <v>8</v>
@@ -15091,13 +15867,16 @@
         <v>44781.094444444447</v>
       </c>
       <c r="F44" s="4">
-        <v>1.7242505459809501E-8</v>
+        <v>1.81848809218014E-6</v>
       </c>
       <c r="G44" s="4">
-        <v>1.1932987192739699E-8</v>
+        <v>1.2585175144562999E-6</v>
       </c>
       <c r="H44" s="4">
-        <v>1.17347870714543E-8</v>
+        <v>1.2376142552989501E-6</v>
+      </c>
+      <c r="I44">
+        <v>1.3805518125</v>
       </c>
     </row>
     <row r="45" spans="1:27" x14ac:dyDescent="0.25">
@@ -15117,13 +15896,16 @@
         <v>44781.104861111111</v>
       </c>
       <c r="F45" s="4">
-        <v>1.35743675942321E-8</v>
+        <v>1.4705399587400599E-6</v>
       </c>
       <c r="G45" s="4">
-        <v>9.9537092479160294E-9</v>
+        <v>1.07830638037932E-6</v>
       </c>
       <c r="H45" s="4">
-        <v>9.7997015836837508E-9</v>
+        <v>1.0616224043170001E-6</v>
+      </c>
+      <c r="I45">
+        <v>1.321577692</v>
       </c>
     </row>
     <row r="46" spans="1:27" x14ac:dyDescent="0.25">
@@ -15143,13 +15925,16 @@
         <v>44781.115277777775</v>
       </c>
       <c r="F46" s="4">
-        <v>1.4772012007367099E-8</v>
+        <v>1.5936219159373299E-6</v>
       </c>
       <c r="G46" s="4">
-        <v>1.02035026895234E-8</v>
+        <v>1.10076579258197E-6</v>
       </c>
       <c r="H46" s="4">
-        <v>1.00688403114362E-8</v>
+        <v>1.08623825787637E-6</v>
+      </c>
+      <c r="I46">
+        <v>1.3305822285</v>
       </c>
       <c r="U46" t="s">
         <v>35</v>
@@ -15162,23 +15947,26 @@
       </c>
       <c r="B47" s="2">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>0.157118818263213</v>
       </c>
       <c r="C47" s="3">
         <f t="shared" si="2"/>
-        <v>44781.000694444447</v>
+        <v>44781.615277777775</v>
       </c>
       <c r="E47" s="1">
         <v>44781.125694444447</v>
       </c>
       <c r="F47" s="4">
-        <v>1.29305830131812E-8</v>
+        <v>1.39496640440665E-6</v>
       </c>
       <c r="G47" s="4">
-        <v>9.8920389735566796E-9</v>
+        <v>1.06716472296785E-6</v>
       </c>
       <c r="H47" s="4">
-        <v>9.9234654398772607E-9</v>
+        <v>1.0705550468768499E-6</v>
+      </c>
+      <c r="I47">
+        <v>1.3305822285</v>
       </c>
       <c r="U47" t="s">
         <v>36</v>
@@ -15206,23 +15994,26 @@
       </c>
       <c r="B48" s="2">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>0.12295818461944701</v>
       </c>
       <c r="C48" s="3">
         <f t="shared" si="2"/>
-        <v>44781.000694444447</v>
+        <v>44781.646527777775</v>
       </c>
       <c r="E48" s="1">
         <v>44781.136111111111</v>
       </c>
       <c r="F48" s="4">
-        <v>1.5842012023537899E-8</v>
+        <v>1.6592556871550001E-6</v>
       </c>
       <c r="G48" s="4">
-        <v>1.23195177617824E-8</v>
+        <v>1.2903177878624699E-6</v>
       </c>
       <c r="H48" s="4">
-        <v>1.21883017770695E-8</v>
+        <v>1.27657452922856E-6</v>
+      </c>
+      <c r="I48">
+        <v>1.3962008465</v>
       </c>
       <c r="T48" t="s">
         <v>39</v>
@@ -15256,38 +16047,41 @@
       </c>
       <c r="B49" s="2">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>0.122308947032243</v>
       </c>
       <c r="C49" s="3">
         <f t="shared" si="2"/>
-        <v>44781.000694444447</v>
+        <v>44781.646527777775</v>
       </c>
       <c r="E49" s="1">
         <v>44781.146527777775</v>
       </c>
       <c r="F49" s="4">
-        <v>1.9850834029230498E-8</v>
+        <v>2.0599074357341801E-6</v>
       </c>
       <c r="G49" s="4">
-        <v>1.3024330135135601E-8</v>
+        <v>1.35152580748439E-6</v>
       </c>
       <c r="H49" s="4">
-        <v>1.2876765836887899E-8</v>
+        <v>1.33621316143475E-6</v>
+      </c>
+      <c r="I49">
+        <v>1.4174729134999999</v>
       </c>
       <c r="T49" t="s">
         <v>40</v>
       </c>
       <c r="U49" s="4">
         <f>B47</f>
-        <v>0</v>
+        <v>0.157118818263213</v>
       </c>
       <c r="V49" s="4">
         <f>B48</f>
-        <v>0</v>
+        <v>0.12295818461944701</v>
       </c>
       <c r="W49" s="4">
         <f>B49</f>
-        <v>0</v>
+        <v>0.122308947032243</v>
       </c>
       <c r="Y49" s="2">
         <v>0</v>
@@ -15306,38 +16100,41 @@
       </c>
       <c r="B50" s="2">
         <f t="shared" si="1"/>
-        <v>0.14382894142458799</v>
+        <v>0.628475273052853</v>
       </c>
       <c r="C50" s="3">
         <f t="shared" si="2"/>
-        <v>44781.636111111111</v>
+        <v>44781.615277777775</v>
       </c>
       <c r="E50" s="1">
         <v>44781.156944444447</v>
       </c>
       <c r="F50" s="4">
-        <v>1.16789922676441E-8</v>
+        <v>1.27205172620107E-6</v>
       </c>
       <c r="G50" s="4">
-        <v>9.2950421705949502E-9</v>
+        <v>1.01239680335182E-6</v>
       </c>
       <c r="H50" s="4">
-        <v>9.2133237857039204E-9</v>
+        <v>1.00349620557602E-6</v>
+      </c>
+      <c r="I50">
+        <v>1.3100260825000001</v>
       </c>
       <c r="T50" t="s">
         <v>41</v>
       </c>
       <c r="U50" s="4">
         <f>B50</f>
-        <v>0.14382894142458799</v>
+        <v>0.628475273052853</v>
       </c>
       <c r="V50" s="4">
         <f>B51</f>
-        <v>0.13735789073556501</v>
+        <v>0.423964093107142</v>
       </c>
       <c r="W50" s="4">
         <f>B52</f>
-        <v>0.137945758770084</v>
+        <v>0.41788520483921099</v>
       </c>
       <c r="Y50" s="2">
         <v>0.15462933529162801</v>
@@ -15356,7 +16153,7 @@
       </c>
       <c r="B51" s="2">
         <f t="shared" si="1"/>
-        <v>0.13735789073556501</v>
+        <v>0.423964093107142</v>
       </c>
       <c r="C51" s="3">
         <f t="shared" si="2"/>
@@ -15366,28 +16163,31 @@
         <v>44781.167361111111</v>
       </c>
       <c r="F51" s="4">
-        <v>9.4925952184214506E-9</v>
+        <v>1.05944687842148E-6</v>
       </c>
       <c r="G51" s="4">
-        <v>7.5348576440005792E-9</v>
+        <v>8.4094825773544101E-7</v>
       </c>
       <c r="H51" s="4">
-        <v>7.5066093998211208E-9</v>
+        <v>8.3779553569564503E-7</v>
+      </c>
+      <c r="I51">
+        <v>1.2590209525</v>
       </c>
       <c r="T51" t="s">
         <v>42</v>
       </c>
       <c r="U51" s="4">
         <f>B53</f>
-        <v>0.70460204460160802</v>
+        <v>2.5139010922114098</v>
       </c>
       <c r="V51" s="4">
         <f>B54</f>
-        <v>0.51008549838768702</v>
+        <v>1.69585637242857</v>
       </c>
       <c r="W51" s="4">
         <f>B55</f>
-        <v>0.50277178290516</v>
+        <v>1.67154081935684</v>
       </c>
       <c r="Y51" s="2">
         <v>0.66003344543256104</v>
@@ -15406,7 +16206,7 @@
       </c>
       <c r="B52" s="2">
         <f t="shared" si="1"/>
-        <v>0.137945758770084</v>
+        <v>0.41788520483921099</v>
       </c>
       <c r="C52" s="3">
         <f t="shared" si="2"/>
@@ -15416,28 +16216,31 @@
         <v>44781.177777777775</v>
       </c>
       <c r="F52" s="4">
-        <v>1.15248404721316E-8</v>
+        <v>1.2606942762836699E-6</v>
       </c>
       <c r="G52" s="4">
-        <v>8.7648104339019099E-9</v>
+        <v>9.5877651179806307E-7</v>
       </c>
       <c r="H52" s="4">
-        <v>8.5507922259153799E-9</v>
+        <v>9.3536520903741099E-7</v>
+      </c>
+      <c r="I52">
+        <v>1.3008491654999901</v>
       </c>
       <c r="T52" t="s">
         <v>43</v>
       </c>
       <c r="U52" s="4">
         <f>B56</f>
-        <v>2.8184081784064299</v>
+        <v>10.0556043688456</v>
       </c>
       <c r="V52" s="4">
         <f>B57</f>
-        <v>2.0403419935507401</v>
+        <v>6.7834254897142801</v>
       </c>
       <c r="W52" s="4">
         <f>B58</f>
-        <v>2.01108713162064</v>
+        <v>6.6861632774273803</v>
       </c>
       <c r="Y52" s="2">
         <v>2.6401337817302402</v>
@@ -15456,38 +16259,41 @@
       </c>
       <c r="B53" s="2">
         <f t="shared" si="1"/>
-        <v>0.70460204460160802</v>
+        <v>2.5139010922114098</v>
       </c>
       <c r="C53" s="3">
         <f t="shared" si="2"/>
-        <v>44781.625694444447</v>
+        <v>44781.615277777775</v>
       </c>
       <c r="E53" s="1">
         <v>44781.188194444447</v>
       </c>
       <c r="F53" s="4">
-        <v>1.5013900722201999E-8</v>
+        <v>1.5926654321992501E-6</v>
       </c>
       <c r="G53" s="4">
-        <v>1.10856575200662E-8</v>
+        <v>1.17595978900166E-6</v>
       </c>
       <c r="H53" s="4">
-        <v>1.09391693441101E-8</v>
+        <v>1.16042041265386E-6</v>
+      </c>
+      <c r="I53">
+        <v>1.3675681405</v>
       </c>
       <c r="T53" t="s">
         <v>44</v>
       </c>
       <c r="U53" s="4">
         <f>B59</f>
-        <v>11.2736327136257</v>
+        <v>40.222417475382599</v>
       </c>
       <c r="V53" s="4">
         <f>B60</f>
-        <v>8.1613679742029905</v>
+        <v>27.133701958857099</v>
       </c>
       <c r="W53" s="4">
         <f>B61</f>
-        <v>8.0443485264825707</v>
+        <v>26.7446531097095</v>
       </c>
       <c r="Y53" s="2">
         <v>10.5605351269209</v>
@@ -15506,7 +16312,7 @@
       </c>
       <c r="B54" s="2">
         <f t="shared" si="1"/>
-        <v>0.51008549838768702</v>
+        <v>1.69585637242857</v>
       </c>
       <c r="C54" s="3">
         <f t="shared" si="2"/>
@@ -15516,13 +16322,16 @@
         <v>44781.198611111111</v>
       </c>
       <c r="F54" s="4">
-        <v>1.4562433557529699E-8</v>
+        <v>1.5411817469163499E-6</v>
       </c>
       <c r="G54" s="4">
-        <v>1.0820789576809301E-8</v>
+        <v>1.14519344017923E-6</v>
       </c>
       <c r="H54" s="4">
-        <v>1.06373187943284E-8</v>
+        <v>1.1257762308349501E-6</v>
+      </c>
+      <c r="I54">
+        <v>1.3727610129999901</v>
       </c>
     </row>
     <row r="55" spans="1:27" x14ac:dyDescent="0.25">
@@ -15532,7 +16341,7 @@
       </c>
       <c r="B55" s="2">
         <f t="shared" si="1"/>
-        <v>0.50277178290516</v>
+        <v>1.67154081935684</v>
       </c>
       <c r="C55" s="3">
         <f t="shared" si="2"/>
@@ -15542,13 +16351,16 @@
         <v>44781.209027777775</v>
       </c>
       <c r="F55" s="4">
-        <v>1.29347352580495E-8</v>
+        <v>1.4084254359793501E-6</v>
       </c>
       <c r="G55" s="4">
-        <v>9.0666964647597404E-9</v>
+        <v>9.8724602139471102E-7</v>
       </c>
       <c r="H55" s="4">
-        <v>8.8524441629148807E-9</v>
+        <v>9.6391671579346909E-7</v>
+      </c>
+      <c r="I55">
+        <v>1.3106306169999999</v>
       </c>
     </row>
     <row r="56" spans="1:27" x14ac:dyDescent="0.25">
@@ -15558,23 +16370,26 @@
       </c>
       <c r="B56" s="2">
         <f t="shared" si="1"/>
-        <v>2.8184081784064299</v>
+        <v>10.0556043688456</v>
       </c>
       <c r="C56" s="3">
         <f t="shared" si="2"/>
-        <v>44781.625694444447</v>
+        <v>44781.615277777775</v>
       </c>
       <c r="E56" s="1">
         <v>44781.219444444447</v>
       </c>
       <c r="F56" s="4">
-        <v>1.45156377391152E-8</v>
+        <v>1.5660832533450999E-6</v>
       </c>
       <c r="G56" s="4">
-        <v>9.7350771525513093E-9</v>
+        <v>1.0503115035420799E-6</v>
       </c>
       <c r="H56" s="4">
-        <v>9.7062286384277898E-9</v>
+        <v>1.0471990550513799E-6</v>
+      </c>
+      <c r="I56">
+        <v>1.3304172409999999</v>
       </c>
     </row>
     <row r="57" spans="1:27" x14ac:dyDescent="0.25">
@@ -15584,7 +16399,7 @@
       </c>
       <c r="B57" s="2">
         <f t="shared" si="1"/>
-        <v>2.0403419935507401</v>
+        <v>6.7834254897142801</v>
       </c>
       <c r="C57" s="3">
         <f t="shared" si="2"/>
@@ -15594,13 +16409,16 @@
         <v>44781.229861111111</v>
       </c>
       <c r="F57" s="4">
-        <v>1.00612811281148E-8</v>
+        <v>1.1204099402278601E-6</v>
       </c>
       <c r="G57" s="4">
-        <v>7.5838404521162604E-9</v>
+        <v>8.4452567414119498E-7</v>
       </c>
       <c r="H57" s="4">
-        <v>7.4776855701739697E-9</v>
+        <v>8.3270441762491605E-7</v>
+      </c>
+      <c r="I57">
+        <v>1.2636095315</v>
       </c>
     </row>
     <row r="58" spans="1:27" x14ac:dyDescent="0.25">
@@ -15610,7 +16428,7 @@
       </c>
       <c r="B58" s="2">
         <f t="shared" si="1"/>
-        <v>2.01108713162064</v>
+        <v>6.6861632774273803</v>
       </c>
       <c r="C58" s="3">
         <f t="shared" si="2"/>
@@ -15620,13 +16438,16 @@
         <v>44781.240277777775</v>
       </c>
       <c r="F58" s="4">
-        <v>1.09222670926897E-8</v>
+        <v>1.2126402176248E-6</v>
       </c>
       <c r="G58" s="4">
-        <v>7.9258275182130999E-9</v>
+        <v>8.7996174465338298E-7</v>
       </c>
       <c r="H58" s="4">
-        <v>7.9085810846291201E-9</v>
+        <v>8.7804696645189198E-7</v>
+      </c>
+      <c r="I58">
+        <v>1.269803263</v>
       </c>
     </row>
     <row r="59" spans="1:27" x14ac:dyDescent="0.25">
@@ -15636,23 +16457,26 @@
       </c>
       <c r="B59" s="2">
         <f t="shared" si="1"/>
-        <v>11.2736327136257</v>
+        <v>40.222417475382599</v>
       </c>
       <c r="C59" s="3">
         <f t="shared" si="2"/>
-        <v>44781.625694444447</v>
+        <v>44781.615277777775</v>
       </c>
       <c r="E59" s="1">
         <v>44781.250694444447</v>
       </c>
       <c r="F59" s="4">
-        <v>1.30593320397655E-8</v>
+        <v>1.39092101404772E-6</v>
       </c>
       <c r="G59" s="4">
-        <v>1.04207326879707E-8</v>
+        <v>1.10988954361902E-6</v>
       </c>
       <c r="H59" s="4">
-        <v>1.0275560333004301E-8</v>
+        <v>1.0944275522444599E-6</v>
+      </c>
+      <c r="I59">
+        <v>1.3586243874999999</v>
       </c>
     </row>
     <row r="60" spans="1:27" x14ac:dyDescent="0.25">
@@ -15662,7 +16486,7 @@
       </c>
       <c r="B60" s="2">
         <f t="shared" si="1"/>
-        <v>8.1613679742029905</v>
+        <v>27.133701958857099</v>
       </c>
       <c r="C60" s="3">
         <f t="shared" si="2"/>
@@ -15672,13 +16496,16 @@
         <v>44781.261111111111</v>
       </c>
       <c r="F60" s="4">
-        <v>1.21468056690243E-8</v>
+        <v>1.3257394963463501E-6</v>
       </c>
       <c r="G60" s="4">
-        <v>8.5784976215300098E-9</v>
+        <v>9.36283449822881E-7</v>
       </c>
       <c r="H60" s="4">
-        <v>8.4399986782839705E-9</v>
+        <v>9.2116725185319497E-7</v>
+      </c>
+      <c r="I60">
+        <v>1.3056302835</v>
       </c>
     </row>
     <row r="61" spans="1:27" x14ac:dyDescent="0.25">
@@ -15688,7 +16515,7 @@
       </c>
       <c r="B61" s="2">
         <f t="shared" ref="B61" si="4">MAX(B28:CT28)</f>
-        <v>8.0443485264825707</v>
+        <v>26.7446531097095</v>
       </c>
       <c r="C61" s="3">
         <f t="shared" ref="C61" si="5">_xlfn.XLOOKUP(MAX(B28:CS28), B28:CS28, $B$1:$CS$1)</f>
@@ -15698,13 +16525,16 @@
         <v>44781.271527777775</v>
       </c>
       <c r="F61" s="4">
-        <v>1.02844136122742E-8</v>
+        <v>1.1430223827072299E-6</v>
       </c>
       <c r="G61" s="4">
-        <v>7.4158309200573703E-9</v>
+        <v>8.2420457281510504E-7</v>
       </c>
       <c r="H61" s="4">
-        <v>7.29414543896144E-9</v>
+        <v>8.1068029874225203E-7</v>
+      </c>
+      <c r="I61">
+        <v>1.2676346135000001</v>
       </c>
     </row>
     <row r="62" spans="1:27" x14ac:dyDescent="0.25">
@@ -15723,13 +16553,16 @@
         <v>44781.281944444447</v>
       </c>
       <c r="F62" s="4">
-        <v>9.7416325055494695E-9</v>
+        <v>1.0727190595649201E-6</v>
       </c>
       <c r="G62" s="4">
-        <v>7.8000359752117498E-9</v>
+        <v>8.5891633166344501E-7</v>
       </c>
       <c r="H62" s="4">
-        <v>7.7577005294362308E-9</v>
+        <v>8.5425448063396198E-7</v>
+      </c>
+      <c r="I62">
+        <v>1.2868847735</v>
       </c>
     </row>
     <row r="63" spans="1:27" x14ac:dyDescent="0.25">
@@ -15738,23 +16571,26 @@
       </c>
       <c r="B63" s="2">
         <f t="shared" si="6"/>
-        <v>18.683979090804002</v>
+        <v>62.117713801532297</v>
       </c>
       <c r="C63" s="3">
         <f t="shared" si="7"/>
-        <v>44781.625694444447</v>
+        <v>44781.604861111111</v>
       </c>
       <c r="E63" s="1">
         <v>44781.292361111111</v>
       </c>
       <c r="F63" s="4">
-        <v>1.14327944707451E-8</v>
+        <v>1.28406330661959E-6</v>
       </c>
       <c r="G63" s="4">
-        <v>7.0828735794765198E-9</v>
+        <v>7.9550612863448299E-7</v>
       </c>
       <c r="H63" s="4">
-        <v>6.9252956896037996E-9</v>
+        <v>7.77807919599486E-7</v>
+      </c>
+      <c r="I63">
+        <v>1.2461573855000001</v>
       </c>
     </row>
     <row r="64" spans="1:27" x14ac:dyDescent="0.25">
@@ -15762,955 +16598,1160 @@
         <v>44781.302777777775</v>
       </c>
       <c r="F64" s="4">
-        <v>9.5267729720812402E-9</v>
+        <v>1.0805788723734999E-6</v>
       </c>
       <c r="G64" s="4">
-        <v>6.4513988984525204E-9</v>
+        <v>7.31753067631339E-7</v>
       </c>
       <c r="H64" s="4">
-        <v>6.4458549186617302E-9</v>
+        <v>7.3112423901809603E-7</v>
+      </c>
+      <c r="I64">
+        <v>1.2263406489999999</v>
       </c>
     </row>
-    <row r="65" spans="5:8" x14ac:dyDescent="0.25">
+    <row r="65" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E65" s="1">
         <v>44781.313194444447</v>
       </c>
       <c r="F65" s="4">
-        <v>9.9105736620194694E-9</v>
+        <v>1.1052764951298499E-6</v>
       </c>
       <c r="G65" s="4">
-        <v>7.2818728205971797E-9</v>
+        <v>8.1211069547454604E-7</v>
       </c>
       <c r="H65" s="4">
-        <v>7.1496251672903197E-9</v>
+        <v>7.9736177903651001E-7</v>
+      </c>
+      <c r="I65">
+        <v>1.2605418435</v>
       </c>
     </row>
-    <row r="66" spans="5:8" x14ac:dyDescent="0.25">
+    <row r="66" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E66" s="1">
         <v>44781.323611111111</v>
       </c>
       <c r="F66" s="4">
-        <v>1.1091989786575401E-8</v>
+        <v>1.21975563788356E-6</v>
       </c>
       <c r="G66" s="4">
-        <v>8.0462237070598607E-9</v>
+        <v>8.8482111138416005E-7</v>
       </c>
       <c r="H66" s="4">
-        <v>7.9792300750312906E-9</v>
+        <v>8.77454005778705E-7</v>
+      </c>
+      <c r="I66">
+        <v>1.2897381324999999</v>
       </c>
     </row>
-    <row r="67" spans="5:8" x14ac:dyDescent="0.25">
+    <row r="67" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E67" s="1">
         <v>44781.334027777775</v>
       </c>
       <c r="F67" s="4">
-        <v>1.3062474946209101E-8</v>
+        <v>1.41161759096376E-6</v>
       </c>
       <c r="G67" s="4">
-        <v>9.1412830066434794E-9</v>
+        <v>9.8786760923232295E-7</v>
       </c>
       <c r="H67" s="4">
-        <v>9.06250368359216E-9</v>
+        <v>9.79354193612616E-7</v>
+      </c>
+      <c r="I67">
+        <v>1.326867053</v>
       </c>
     </row>
-    <row r="68" spans="5:8" x14ac:dyDescent="0.25">
+    <row r="68" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E68" s="1">
         <v>44781.344444444447</v>
       </c>
       <c r="F68" s="4">
-        <v>1.3348679805796E-8</v>
+        <v>1.45056921071862E-6</v>
       </c>
       <c r="G68" s="4">
-        <v>8.6644236888439392E-9</v>
+        <v>9.4154226593322999E-7</v>
       </c>
       <c r="H68" s="4">
-        <v>8.6454598933598705E-9</v>
+        <v>9.3948151549147396E-7</v>
+      </c>
+      <c r="I68">
+        <v>1.314942037</v>
       </c>
     </row>
-    <row r="69" spans="5:8" x14ac:dyDescent="0.25">
+    <row r="69" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E69" s="1">
         <v>44781.354861111111</v>
       </c>
       <c r="F69" s="4">
-        <v>1.18194980557907E-8</v>
+        <v>1.2913789611719901E-6</v>
       </c>
       <c r="G69" s="4">
-        <v>8.1380588993041893E-9</v>
+        <v>8.8915096036137399E-7</v>
       </c>
       <c r="H69" s="4">
-        <v>7.8105278519879504E-9</v>
+        <v>8.5336545562949604E-7</v>
+      </c>
+      <c r="I69">
+        <v>1.3033880545000001</v>
       </c>
     </row>
-    <row r="70" spans="5:8" x14ac:dyDescent="0.25">
+    <row r="70" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E70" s="1">
         <v>44781.365277777775</v>
       </c>
       <c r="F70" s="4">
-        <v>1.06206101283769E-8</v>
+        <v>1.20357981018381E-6</v>
       </c>
       <c r="G70" s="4">
-        <v>6.50727389293259E-9</v>
+        <v>7.3743630377049103E-7</v>
       </c>
       <c r="H70" s="4">
-        <v>6.2437535947450096E-9</v>
+        <v>7.07572886623624E-7</v>
+      </c>
+      <c r="I70">
+        <v>1.2281127095</v>
       </c>
     </row>
-    <row r="71" spans="5:8" x14ac:dyDescent="0.25">
+    <row r="71" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E71" s="1">
         <v>44781.375694444447</v>
       </c>
       <c r="F71" s="4">
-        <v>7.40609733328566E-9</v>
+        <v>8.6926546504997798E-7</v>
       </c>
       <c r="G71" s="4">
-        <v>5.0829816647472298E-9</v>
+        <v>5.96597671056019E-7</v>
       </c>
       <c r="H71" s="4">
-        <v>5.0427926111127498E-9</v>
+        <v>5.9188061766892796E-7</v>
+      </c>
+      <c r="I71">
+        <v>1.1599344165000001</v>
       </c>
     </row>
-    <row r="72" spans="5:8" x14ac:dyDescent="0.25">
+    <row r="72" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E72" s="1">
         <v>44781.386111111111</v>
       </c>
       <c r="F72" s="4">
-        <v>8.4461589863701507E-9</v>
+        <v>9.852675059605111E-7</v>
       </c>
       <c r="G72" s="4">
-        <v>5.47000075402761E-9</v>
+        <v>6.3809052244931604E-7</v>
       </c>
       <c r="H72" s="4">
-        <v>5.3460048542051102E-9</v>
+        <v>6.2362606218913202E-7</v>
+      </c>
+      <c r="I72">
+        <v>1.1715929684999999</v>
       </c>
     </row>
-    <row r="73" spans="5:8" x14ac:dyDescent="0.25">
+    <row r="73" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E73" s="1">
         <v>44781.396527777775</v>
       </c>
       <c r="F73" s="4">
-        <v>6.1974236192305796E-9</v>
+        <v>7.34006066980003E-7</v>
       </c>
       <c r="G73" s="4">
-        <v>4.72799005264294E-9</v>
+        <v>5.5997033548783296E-7</v>
       </c>
       <c r="H73" s="4">
-        <v>4.7060936602565104E-9</v>
+        <v>5.5737698607944195E-7</v>
+      </c>
+      <c r="I73">
+        <v>1.142992303</v>
       </c>
     </row>
-    <row r="74" spans="5:8" x14ac:dyDescent="0.25">
+    <row r="74" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E74" s="1">
         <v>44781.406944444447</v>
       </c>
       <c r="F74" s="4">
-        <v>6.9174104480876099E-9</v>
+        <v>8.2096638897698601E-7</v>
       </c>
       <c r="G74" s="4">
-        <v>4.6877305286759502E-9</v>
+        <v>5.5634535980222297E-7</v>
       </c>
       <c r="H74" s="4">
-        <v>4.5779079089452702E-9</v>
+        <v>5.4331148243875702E-7</v>
+      </c>
+      <c r="I74">
+        <v>1.1391712730000001</v>
       </c>
     </row>
-    <row r="75" spans="5:8" x14ac:dyDescent="0.25">
+    <row r="75" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E75" s="1">
         <v>44781.417361111111</v>
       </c>
       <c r="F75" s="4">
-        <v>6.32816515555179E-9</v>
+        <v>7.5621079985491899E-7</v>
       </c>
       <c r="G75" s="4">
-        <v>4.6070326879360398E-9</v>
+        <v>5.5053681253066602E-7</v>
       </c>
       <c r="H75" s="4">
-        <v>4.5918475828262896E-9</v>
+        <v>5.4872220431175599E-7</v>
+      </c>
+      <c r="I75">
+        <v>1.126503907</v>
       </c>
     </row>
-    <row r="76" spans="5:8" x14ac:dyDescent="0.25">
+    <row r="76" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E76" s="1">
         <v>44781.427777777775</v>
       </c>
       <c r="F76" s="4">
-        <v>7.28540229665392E-9</v>
+        <v>8.4164204860494604E-7</v>
       </c>
       <c r="G76" s="4">
-        <v>5.7395984617146599E-9</v>
+        <v>6.6306392026194604E-7</v>
       </c>
       <c r="H76" s="4">
-        <v>5.6509632883029799E-9</v>
+        <v>6.5282439114532299E-7</v>
+      </c>
+      <c r="I76">
+        <v>1.1902769595</v>
       </c>
     </row>
-    <row r="77" spans="5:8" x14ac:dyDescent="0.25">
+    <row r="77" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E77" s="1">
         <v>44781.438194444447</v>
       </c>
       <c r="F77" s="4">
-        <v>1.0095850280173401E-8</v>
+        <v>1.1438939623874601E-6</v>
       </c>
       <c r="G77" s="4">
-        <v>6.4907686245721097E-9</v>
+        <v>7.3542602501335596E-7</v>
       </c>
       <c r="H77" s="4">
-        <v>6.4023906307448604E-9</v>
+        <v>7.25412499582329E-7</v>
+      </c>
+      <c r="I77">
+        <v>1.228492825</v>
       </c>
     </row>
-    <row r="78" spans="5:8" x14ac:dyDescent="0.25">
+    <row r="78" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E78" s="1">
         <v>44781.448611111111</v>
       </c>
       <c r="F78" s="4">
-        <v>8.7185632776942095E-9</v>
+        <v>9.9576696049404601E-7</v>
       </c>
       <c r="G78" s="4">
-        <v>6.3293531595371501E-9</v>
+        <v>7.2288983366839196E-7</v>
       </c>
       <c r="H78" s="4">
-        <v>6.15037878880983E-9</v>
+        <v>7.0244876332904202E-7</v>
+      </c>
+      <c r="I78">
+        <v>1.212618097</v>
       </c>
     </row>
-    <row r="79" spans="5:8" x14ac:dyDescent="0.25">
+    <row r="79" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E79" s="1">
         <v>44781.459027777775</v>
       </c>
       <c r="F79" s="4">
-        <v>8.34725172528678E-9</v>
+        <v>9.580542360916839E-7</v>
       </c>
       <c r="G79" s="4">
-        <v>5.9759176962636097E-9</v>
+        <v>6.8588482196927205E-7</v>
       </c>
       <c r="H79" s="4">
-        <v>5.8063179443663297E-9</v>
+        <v>6.6641904257258096E-7</v>
+      </c>
+      <c r="I79">
+        <v>1.2029581084999901</v>
       </c>
     </row>
-    <row r="80" spans="5:8" x14ac:dyDescent="0.25">
+    <row r="80" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E80" s="1">
         <v>44781.469444444447</v>
       </c>
       <c r="F80" s="4">
-        <v>7.4372115329053898E-9</v>
+        <v>8.6436718894924899E-7</v>
       </c>
       <c r="G80" s="4">
-        <v>5.5646273014940503E-9</v>
+        <v>6.4673180759169101E-7</v>
       </c>
       <c r="H80" s="4">
-        <v>5.4778019322786803E-9</v>
+        <v>6.36640794311264E-7</v>
+      </c>
+      <c r="I80">
+        <v>1.1786703704999999</v>
       </c>
     </row>
-    <row r="81" spans="5:8" x14ac:dyDescent="0.25">
+    <row r="81" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E81" s="1">
         <v>44781.479861111111</v>
       </c>
       <c r="F81" s="4">
-        <v>9.9835595857672397E-9</v>
+        <v>1.1182665401864501E-6</v>
       </c>
       <c r="G81" s="4">
-        <v>7.0267352286048103E-9</v>
+        <v>7.8707026541901097E-7</v>
       </c>
       <c r="H81" s="4">
-        <v>6.89016388329679E-9</v>
+        <v>7.7177279917421495E-7</v>
+      </c>
+      <c r="I81">
+        <v>1.251653779</v>
       </c>
     </row>
-    <row r="82" spans="5:8" x14ac:dyDescent="0.25">
+    <row r="82" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E82" s="1">
         <v>44781.490277777775</v>
       </c>
       <c r="F82" s="4">
-        <v>1.1165384985735599E-8</v>
+        <v>1.2255001677109701E-6</v>
       </c>
       <c r="G82" s="4">
-        <v>8.1120448806285496E-9</v>
+        <v>8.9036897286747204E-7</v>
       </c>
       <c r="H82" s="4">
-        <v>8.0238818322631193E-9</v>
+        <v>8.8069229530340095E-7</v>
+      </c>
+      <c r="I82">
+        <v>1.2937263295000001</v>
       </c>
     </row>
-    <row r="83" spans="5:8" x14ac:dyDescent="0.25">
+    <row r="83" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E83" s="1">
         <v>44781.500694444447</v>
       </c>
       <c r="F83" s="4">
-        <v>6.9466293265400496E-9</v>
+        <v>8.0354235413597698E-7</v>
       </c>
       <c r="G83" s="4">
-        <v>5.7165196891903698E-9</v>
+        <v>6.6125101436823698E-7</v>
       </c>
       <c r="H83" s="4">
-        <v>5.6674283648872199E-9</v>
+        <v>6.5557243897037502E-7</v>
+      </c>
+      <c r="I83">
+        <v>1.1877777380000001</v>
       </c>
     </row>
-    <row r="84" spans="5:8" x14ac:dyDescent="0.25">
+    <row r="84" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E84" s="1">
         <v>44781.511111111111</v>
       </c>
       <c r="F84" s="4">
-        <v>6.8117547066147198E-9</v>
+        <v>8.0728139075582595E-7</v>
       </c>
       <c r="G84" s="4">
-        <v>4.6825188138704401E-9</v>
+        <v>5.5493928704257195E-7</v>
       </c>
       <c r="H84" s="4">
-        <v>4.5132726888042003E-9</v>
+        <v>5.3488142337848302E-7</v>
+      </c>
+      <c r="I84">
+        <v>1.141804142</v>
       </c>
     </row>
-    <row r="85" spans="5:8" x14ac:dyDescent="0.25">
+    <row r="85" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E85" s="1">
         <v>44781.521527777775</v>
       </c>
       <c r="F85" s="4">
-        <v>1.0063859852835099E-8</v>
+        <v>1.1238477036902599E-6</v>
       </c>
       <c r="G85" s="4">
-        <v>6.84540696641487E-9</v>
+        <v>7.6443780145253397E-7</v>
       </c>
       <c r="H85" s="4">
-        <v>6.6806401961204599E-9</v>
+        <v>7.4603802650363702E-7</v>
+      </c>
+      <c r="I85">
+        <v>1.2578480294999901</v>
       </c>
     </row>
-    <row r="86" spans="5:8" x14ac:dyDescent="0.25">
+    <row r="86" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E86" s="1">
         <v>44781.531944444447</v>
       </c>
       <c r="F86" s="4">
-        <v>1.2842809199053001E-8</v>
+        <v>1.3843005327694501E-6</v>
       </c>
       <c r="G86" s="4">
-        <v>9.2656323176021903E-9</v>
+        <v>9.9872384262512E-7</v>
       </c>
       <c r="H86" s="4">
-        <v>9.1296565686098997E-9</v>
+        <v>9.840672905496551E-7</v>
+      </c>
+      <c r="I86">
+        <v>1.3324552590000001</v>
       </c>
     </row>
-    <row r="87" spans="5:8" x14ac:dyDescent="0.25">
+    <row r="87" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E87" s="1">
         <v>44781.542361111111</v>
       </c>
       <c r="F87" s="4">
-        <v>3.5780196042316697E-8</v>
+        <v>3.4586284454806899E-6</v>
       </c>
       <c r="G87" s="4">
-        <v>2.3196453906791301E-8</v>
+        <v>2.2422435925554199E-6</v>
       </c>
       <c r="H87" s="4">
-        <v>2.3255763140541299E-8</v>
+        <v>2.24797661320171E-6</v>
+      </c>
+      <c r="I87">
+        <v>1.5909838079999901</v>
       </c>
     </row>
-    <row r="88" spans="5:8" x14ac:dyDescent="0.25">
+    <row r="88" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E88" s="1">
         <v>44781.552777777775</v>
       </c>
       <c r="F88" s="4">
-        <v>1.30816767464494E-7</v>
+        <v>1.04538029694326E-5</v>
       </c>
       <c r="G88" s="4">
-        <v>1.00964698710095E-7</v>
+        <v>8.0682705102349393E-6</v>
       </c>
       <c r="H88" s="4">
-        <v>9.92270244525908E-8</v>
+        <v>7.9294098377719094E-6</v>
+      </c>
+      <c r="I88">
+        <v>2.1687506614999998</v>
       </c>
     </row>
-    <row r="89" spans="5:8" x14ac:dyDescent="0.25">
+    <row r="89" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E89" s="1">
         <v>44781.563194444447</v>
       </c>
       <c r="F89" s="4">
-        <v>1.5853121918232999E-7</v>
+        <v>1.2216960823949901E-5</v>
       </c>
       <c r="G89" s="4">
-        <v>1.2432276051555401E-7</v>
+        <v>9.5807393811041394E-6</v>
       </c>
       <c r="H89" s="4">
-        <v>1.2201232736340701E-7</v>
+        <v>9.4026894584821297E-6</v>
+      </c>
+      <c r="I89">
+        <v>2.3007473825</v>
       </c>
     </row>
-    <row r="90" spans="5:8" x14ac:dyDescent="0.25">
+    <row r="90" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E90" s="1">
         <v>44781.573611111111</v>
       </c>
       <c r="F90" s="4">
-        <v>5.9807526318119304E-7</v>
+        <v>3.7170773087333501E-5</v>
       </c>
       <c r="G90" s="4">
-        <v>4.16410089823409E-7</v>
+        <v>2.5880162435940098E-5</v>
       </c>
       <c r="H90" s="4">
-        <v>4.0364332862755902E-7</v>
+        <v>2.5086699786166399E-5</v>
+      </c>
+      <c r="I90">
+        <v>3.2652481369999999</v>
       </c>
     </row>
-    <row r="91" spans="5:8" x14ac:dyDescent="0.25">
+    <row r="91" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E91" s="1">
         <v>44781.584027777775</v>
       </c>
-      <c r="F91" s="4">
-        <v>1.2616159790631901E-5</v>
-      </c>
-      <c r="G91" s="4">
-        <v>8.6544649020026392E-6</v>
-      </c>
-      <c r="H91" s="4">
-        <v>8.5031135066020596E-6</v>
+      <c r="F91">
+        <v>4.8837098868093401E-4</v>
+      </c>
+      <c r="G91">
+        <v>3.3501395439016602E-4</v>
+      </c>
+      <c r="H91">
+        <v>3.2915514855592399E-4</v>
+      </c>
+      <c r="I91">
+        <v>7.0573823745000004</v>
       </c>
     </row>
-    <row r="92" spans="5:8" x14ac:dyDescent="0.25">
+    <row r="92" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E92" s="1">
         <v>44781.594444444447</v>
       </c>
       <c r="F92">
-        <v>2.05117605670511E-4</v>
+        <v>5.3276258426810897E-3</v>
       </c>
       <c r="G92">
-        <v>1.63404252304588E-4</v>
+        <v>4.2441833040826197E-3</v>
       </c>
       <c r="H92">
-        <v>1.6231017287086301E-4</v>
+        <v>4.2157662121337898E-3</v>
+      </c>
+      <c r="I92">
+        <v>13.5126390895</v>
       </c>
     </row>
-    <row r="93" spans="5:8" x14ac:dyDescent="0.25">
+    <row r="93" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E93" s="1">
         <v>44781.604861111111</v>
       </c>
       <c r="F93">
-        <v>1.63328311290035E-3</v>
+        <v>3.2275768961475201E-2</v>
       </c>
       <c r="G93">
-        <v>1.25180167747011E-3</v>
+        <v>2.4737206555507499E-2</v>
       </c>
       <c r="H93">
-        <v>1.2599092890278999E-3</v>
+        <v>2.48974233577593E-2</v>
+      </c>
+      <c r="I93">
+        <v>21.08342828</v>
       </c>
     </row>
-    <row r="94" spans="5:8" x14ac:dyDescent="0.25">
+    <row r="94" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E94" s="1">
         <v>44781.615277777775</v>
       </c>
       <c r="F94">
-        <v>6.7965607237199599E-3</v>
+        <v>3.9279704565803299E-2</v>
       </c>
       <c r="G94">
-        <v>4.4555820701342201E-3</v>
+        <v>2.57503691198461E-2</v>
       </c>
       <c r="H94">
-        <v>4.4166965562598198E-3</v>
+        <v>2.5525636117230299E-2</v>
+      </c>
+      <c r="I94">
+        <v>28.119352749999901</v>
       </c>
     </row>
-    <row r="95" spans="5:8" x14ac:dyDescent="0.25">
+    <row r="95" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E95" s="1">
         <v>44781.625694444447</v>
       </c>
       <c r="F95">
-        <v>1.1009406946900099E-2</v>
+        <v>3.6602438192205301E-2</v>
       </c>
       <c r="G95">
-        <v>7.9700859123076097E-3</v>
+        <v>2.64977558191964E-2</v>
       </c>
       <c r="H95">
-        <v>7.8558091078931302E-3</v>
+        <v>2.6117825302450701E-2</v>
+      </c>
+      <c r="I95">
+        <v>32.007500319999998</v>
       </c>
     </row>
-    <row r="96" spans="5:8" x14ac:dyDescent="0.25">
+    <row r="96" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E96" s="1">
         <v>44781.636111111111</v>
       </c>
       <c r="F96">
-        <v>8.9943480211758207E-3</v>
+        <v>3.1495097104223102E-2</v>
       </c>
       <c r="G96">
-        <v>7.3498348235841596E-3</v>
+        <v>2.5736580452733099E-2</v>
       </c>
       <c r="H96">
-        <v>7.2506506127722097E-3</v>
+        <v>2.5389271637974199E-2</v>
+      </c>
+      <c r="I96">
+        <v>31.620971515000001</v>
       </c>
     </row>
-    <row r="97" spans="5:8" x14ac:dyDescent="0.25">
+    <row r="97" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E97" s="1">
         <v>44781.646527777775</v>
       </c>
       <c r="F97">
-        <v>9.0417129480271693E-3</v>
+        <v>3.5291894672967998E-2</v>
       </c>
       <c r="G97">
-        <v>6.6699275342222402E-3</v>
+        <v>2.6034268215854101E-2</v>
       </c>
       <c r="H97">
-        <v>6.5501312461542002E-3</v>
+        <v>2.5566675625074E-2</v>
+      </c>
+      <c r="I97">
+        <v>30.826982135000002</v>
       </c>
     </row>
-    <row r="98" spans="5:8" x14ac:dyDescent="0.25">
+    <row r="98" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E98" s="1">
         <v>44781.656944444447</v>
       </c>
       <c r="F98">
-        <v>7.9928147097117E-3</v>
+        <v>3.1356353549068197E-2</v>
       </c>
       <c r="G98">
-        <v>6.3767171823644999E-3</v>
+        <v>2.5016293472347899E-2</v>
       </c>
       <c r="H98">
-        <v>6.2249847404091899E-3</v>
+        <v>2.4421036823715402E-2</v>
+      </c>
+      <c r="I98">
+        <v>30.790400730000002</v>
       </c>
     </row>
-    <row r="99" spans="5:8" x14ac:dyDescent="0.25">
+    <row r="99" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E99" s="1">
         <v>44781.667361111111</v>
       </c>
       <c r="F99">
-        <v>5.4624617327883604E-3</v>
+        <v>2.96706979468652E-2</v>
       </c>
       <c r="G99">
-        <v>4.0903457913729997E-3</v>
+        <v>2.22177143589136E-2</v>
       </c>
       <c r="H99">
-        <v>4.1186212620550897E-3</v>
+        <v>2.2371299498981301E-2</v>
+      </c>
+      <c r="I99">
+        <v>28.530895780000002</v>
       </c>
     </row>
-    <row r="100" spans="5:8" x14ac:dyDescent="0.25">
+    <row r="100" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E100" s="1">
         <v>44781.677777777775</v>
       </c>
       <c r="F100">
-        <v>3.2876564977182398E-3</v>
+        <v>2.7637660054618599E-2</v>
       </c>
       <c r="G100">
-        <v>2.6058417642154902E-3</v>
+        <v>2.1905989535808901E-2</v>
       </c>
       <c r="H100">
-        <v>2.60414846254545E-3</v>
+        <v>2.1891754807669299E-2</v>
+      </c>
+      <c r="I100">
+        <v>25.756546825000001</v>
       </c>
     </row>
-    <row r="101" spans="5:8" x14ac:dyDescent="0.25">
+    <row r="101" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E101" s="1">
         <v>44781.688194444447</v>
       </c>
       <c r="F101">
-        <v>2.3816785486162899E-3</v>
+        <v>2.9751022048612699E-2</v>
       </c>
       <c r="G101">
-        <v>1.65565535718085E-3</v>
+        <v>2.06818166393531E-2</v>
       </c>
       <c r="H101">
-        <v>1.6056248710924999E-3</v>
+        <v>2.00568548468801E-2</v>
+      </c>
+      <c r="I101">
+        <v>23.474647859999902</v>
       </c>
     </row>
-    <row r="102" spans="5:8" x14ac:dyDescent="0.25">
+    <row r="102" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E102" s="1">
         <v>44781.698611111111</v>
       </c>
       <c r="F102">
-        <v>1.2548875026224501E-3</v>
+        <v>2.51241617425506E-2</v>
       </c>
       <c r="G102">
-        <v>9.5942405127783501E-4</v>
+        <v>1.9208674079211702E-2</v>
       </c>
       <c r="H102">
-        <v>9.4942941054271496E-4</v>
+        <v>1.90085709066799E-2</v>
+      </c>
+      <c r="I102">
+        <v>20.642438585000001</v>
       </c>
     </row>
-    <row r="103" spans="5:8" x14ac:dyDescent="0.25">
+    <row r="103" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E103" s="1">
         <v>44781.709027777775</v>
       </c>
       <c r="F103">
-        <v>6.8274708682035997E-4</v>
+        <v>1.4748069683948499E-2</v>
       </c>
       <c r="G103">
-        <v>5.2223097713969603E-4</v>
+        <v>1.1280749475975099E-2</v>
       </c>
       <c r="H103">
-        <v>5.1525208836084198E-4</v>
+        <v>1.1129997989932999E-2</v>
+      </c>
+      <c r="I103">
+        <v>18.24147606</v>
       </c>
     </row>
-    <row r="104" spans="5:8" x14ac:dyDescent="0.25">
+    <row r="104" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E104" s="1">
         <v>44781.719444444447</v>
       </c>
       <c r="F104">
-        <v>5.4547237763573103E-4</v>
+        <v>1.2178516722712701E-2</v>
       </c>
       <c r="G104">
-        <v>3.9229049757303399E-4</v>
+        <v>8.7584937035885494E-3</v>
       </c>
       <c r="H104">
-        <v>3.8322979368790101E-4</v>
+        <v>8.5561994382844803E-3</v>
+      </c>
+      <c r="I104">
+        <v>17.286459975</v>
       </c>
     </row>
-    <row r="105" spans="5:8" x14ac:dyDescent="0.25">
+    <row r="105" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E105" s="1">
         <v>44781.729861111111</v>
       </c>
       <c r="F105">
-        <v>4.5094874490155998E-4</v>
+        <v>1.04058977869618E-2</v>
       </c>
       <c r="G105">
-        <v>2.9796641496116199E-4</v>
+        <v>6.8757438469777997E-3</v>
       </c>
       <c r="H105">
-        <v>2.9198288635133899E-4</v>
+        <v>6.7376705341203897E-3</v>
+      </c>
+      <c r="I105">
+        <v>16.382398909999999</v>
       </c>
     </row>
-    <row r="106" spans="5:8" x14ac:dyDescent="0.25">
+    <row r="106" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E106" s="1">
         <v>44781.740277777775</v>
       </c>
       <c r="F106">
-        <v>2.8259038918480601E-4</v>
+        <v>7.0590765229654401E-3</v>
       </c>
       <c r="G106">
-        <v>1.93269127027081E-4</v>
+        <v>4.8278413188092397E-3</v>
       </c>
       <c r="H106">
-        <v>1.9338695347932401E-4</v>
+        <v>4.8307846104402802E-3</v>
+      </c>
+      <c r="I106">
+        <v>14.39848273</v>
       </c>
     </row>
-    <row r="107" spans="5:8" x14ac:dyDescent="0.25">
+    <row r="107" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E107" s="1">
         <v>44781.750694444447</v>
       </c>
       <c r="F107">
-        <v>3.6428215953024698E-4</v>
+        <v>8.7954581678172297E-3</v>
       </c>
       <c r="G107">
-        <v>2.40544330247799E-4</v>
+        <v>5.8078539913804404E-3</v>
       </c>
       <c r="H107">
-        <v>2.35452156714537E-4</v>
+        <v>5.6849053425008199E-3</v>
+      </c>
+      <c r="I107">
+        <v>15.218093735</v>
       </c>
     </row>
-    <row r="108" spans="5:8" x14ac:dyDescent="0.25">
+    <row r="108" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E108" s="1">
         <v>44781.761111111111</v>
       </c>
       <c r="F108">
-        <v>1.99936701875895E-4</v>
+        <v>5.1334705034063403E-3</v>
       </c>
       <c r="G108">
-        <v>1.5881093547220399E-4</v>
+        <v>4.0775467696984903E-3</v>
       </c>
       <c r="H108">
-        <v>1.58555042502395E-4</v>
+        <v>4.0709765951558296E-3</v>
+      </c>
+      <c r="I108">
+        <v>13.768905965</v>
       </c>
     </row>
-    <row r="109" spans="5:8" x14ac:dyDescent="0.25">
+    <row r="109" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E109" s="1">
         <v>44781.771527777775</v>
       </c>
-      <c r="F109" s="4">
-        <v>7.2645406357815107E-5</v>
-      </c>
-      <c r="G109" s="4">
-        <v>5.0985964398630101E-5</v>
-      </c>
-      <c r="H109" s="4">
-        <v>5.0794349781337597E-5</v>
+      <c r="F109">
+        <v>2.1760303881135801E-3</v>
+      </c>
+      <c r="G109">
+        <v>1.5272405161459201E-3</v>
+      </c>
+      <c r="H109">
+        <v>1.52150086580679E-3</v>
+      </c>
+      <c r="I109">
+        <v>10.713533245000001</v>
       </c>
     </row>
-    <row r="110" spans="5:8" x14ac:dyDescent="0.25">
+    <row r="110" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E110" s="1">
         <v>44781.781944444447</v>
       </c>
-      <c r="F110" s="4">
-        <v>7.56159547780217E-5</v>
-      </c>
-      <c r="G110" s="4">
-        <v>5.4033050677597897E-5</v>
-      </c>
-      <c r="H110" s="4">
-        <v>5.2433128207794903E-5</v>
+      <c r="F110">
+        <v>2.2618078613182899E-3</v>
+      </c>
+      <c r="G110">
+        <v>1.6162247656607599E-3</v>
+      </c>
+      <c r="H110">
+        <v>1.56836823553742E-3</v>
+      </c>
+      <c r="I110">
+        <v>10.73823973</v>
       </c>
     </row>
-    <row r="111" spans="5:8" x14ac:dyDescent="0.25">
+    <row r="111" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E111" s="1">
         <v>44781.792361111111</v>
       </c>
-      <c r="F111" s="4">
-        <v>4.5464583434314597E-5</v>
-      </c>
-      <c r="G111" s="4">
-        <v>2.93148134986538E-5</v>
-      </c>
-      <c r="H111" s="4">
-        <v>2.9015048710938999E-5</v>
+      <c r="F111">
+        <v>1.4743389202022299E-3</v>
+      </c>
+      <c r="G111">
+        <v>9.5062941778992205E-4</v>
+      </c>
+      <c r="H111">
+        <v>9.40908556856773E-4</v>
+      </c>
+      <c r="I111">
+        <v>9.41508928649999</v>
       </c>
     </row>
-    <row r="112" spans="5:8" x14ac:dyDescent="0.25">
+    <row r="112" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E112" s="1">
         <v>44781.802777777775</v>
       </c>
-      <c r="F112" s="4">
-        <v>4.915233559206E-5</v>
-      </c>
-      <c r="G112" s="4">
-        <v>3.2330376324374099E-5</v>
-      </c>
-      <c r="H112" s="4">
-        <v>3.1594489524102599E-5</v>
+      <c r="F112">
+        <v>1.5780972943542301E-3</v>
+      </c>
+      <c r="G112">
+        <v>1.03800722362975E-3</v>
+      </c>
+      <c r="H112">
+        <v>1.0143806562511099E-3</v>
+      </c>
+      <c r="I112">
+        <v>9.5693059164999994</v>
       </c>
     </row>
-    <row r="113" spans="5:8" x14ac:dyDescent="0.25">
+    <row r="113" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E113" s="1">
         <v>44781.813194444447</v>
       </c>
-      <c r="F113" s="4">
-        <v>7.5285953536546199E-5</v>
-      </c>
-      <c r="G113" s="4">
-        <v>4.0580614477313299E-5</v>
-      </c>
-      <c r="H113" s="4">
-        <v>3.9677423467233298E-5</v>
+      <c r="F113">
+        <v>2.3403702735392499E-3</v>
+      </c>
+      <c r="G113">
+        <v>1.26150575693274E-3</v>
+      </c>
+      <c r="H113">
+        <v>1.2334287878170301E-3</v>
+      </c>
+      <c r="I113">
+        <v>10.085595189999999</v>
       </c>
     </row>
-    <row r="114" spans="5:8" x14ac:dyDescent="0.25">
+    <row r="114" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E114" s="1">
         <v>44781.823611111111</v>
       </c>
-      <c r="F114" s="4">
-        <v>2.36274514213945E-5</v>
-      </c>
-      <c r="G114" s="4">
-        <v>1.5705980765168301E-5</v>
-      </c>
-      <c r="H114" s="4">
-        <v>1.5279521577596499E-5</v>
+      <c r="F114">
+        <v>8.4007814809293003E-4</v>
+      </c>
+      <c r="G114">
+        <v>5.5842888002905898E-4</v>
+      </c>
+      <c r="H114">
+        <v>5.4326604938560198E-4</v>
+      </c>
+      <c r="I114">
+        <v>8.104838397</v>
       </c>
     </row>
-    <row r="115" spans="5:8" x14ac:dyDescent="0.25">
+    <row r="115" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E115" s="1">
         <v>44781.834027777775</v>
       </c>
-      <c r="F115" s="4">
-        <v>1.30656236994048E-5</v>
-      </c>
-      <c r="G115" s="4">
-        <v>8.77531800676668E-6</v>
-      </c>
-      <c r="H115" s="4">
-        <v>8.7302394871148802E-6</v>
+      <c r="F115">
+        <v>5.0688171603719496E-4</v>
+      </c>
+      <c r="G115">
+        <v>3.4043902934367798E-4</v>
+      </c>
+      <c r="H115">
+        <v>3.38690205260236E-4</v>
+      </c>
+      <c r="I115">
+        <v>7.0321962280000001</v>
       </c>
     </row>
-    <row r="116" spans="5:8" x14ac:dyDescent="0.25">
+    <row r="116" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E116" s="1">
         <v>44781.844444444447</v>
       </c>
-      <c r="F116" s="4">
-        <v>1.62552722631288E-5</v>
-      </c>
-      <c r="G116" s="4">
-        <v>1.0637917979395899E-5</v>
-      </c>
-      <c r="H116" s="4">
-        <v>1.0440718273887999E-5</v>
+      <c r="F116">
+        <v>6.1092601709592399E-4</v>
+      </c>
+      <c r="G116">
+        <v>3.9980756742577403E-4</v>
+      </c>
+      <c r="H116">
+        <v>3.9239616092214501E-4</v>
+      </c>
+      <c r="I116">
+        <v>7.4050236140000001</v>
       </c>
     </row>
-    <row r="117" spans="5:8" x14ac:dyDescent="0.25">
+    <row r="117" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E117" s="1">
         <v>44781.854861111111</v>
       </c>
-      <c r="F117" s="4">
-        <v>8.4617179272708406E-6</v>
-      </c>
-      <c r="G117" s="4">
-        <v>5.7491088964468698E-6</v>
-      </c>
-      <c r="H117" s="4">
-        <v>5.73681912038392E-6</v>
+      <c r="F117">
+        <v>3.4973643501518302E-4</v>
+      </c>
+      <c r="G117">
+        <v>2.3761993335777101E-4</v>
+      </c>
+      <c r="H117">
+        <v>2.37111977112796E-4</v>
+      </c>
+      <c r="I117">
+        <v>6.3432970429999997</v>
       </c>
     </row>
-    <row r="118" spans="5:8" x14ac:dyDescent="0.25">
+    <row r="118" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E118" s="1">
         <v>44781.865277777775</v>
       </c>
-      <c r="F118" s="4">
-        <v>2.72060944319374E-6</v>
+      <c r="F118">
+        <v>1.30968077187232E-4</v>
       </c>
       <c r="G118" s="4">
-        <v>1.9582358708784901E-6</v>
+        <v>9.4267991067419101E-5</v>
       </c>
       <c r="H118" s="4">
-        <v>1.9247524491630602E-6</v>
+        <v>9.2656124516474797E-5</v>
+      </c>
+      <c r="I118">
+        <v>4.9490583829999997</v>
       </c>
     </row>
-    <row r="119" spans="5:8" x14ac:dyDescent="0.25">
+    <row r="119" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E119" s="1">
         <v>44781.875694444447</v>
       </c>
-      <c r="F119" s="4">
-        <v>8.6198066168450707E-6</v>
-      </c>
-      <c r="G119" s="4">
-        <v>5.7685786368914701E-6</v>
-      </c>
-      <c r="H119" s="4">
-        <v>5.8546820975153499E-6</v>
+      <c r="F119">
+        <v>3.5556397310524898E-4</v>
+      </c>
+      <c r="G119">
+        <v>2.3795182775074501E-4</v>
+      </c>
+      <c r="H119">
+        <v>2.4150356503508999E-4</v>
+      </c>
+      <c r="I119">
+        <v>6.3638281955</v>
       </c>
     </row>
-    <row r="120" spans="5:8" x14ac:dyDescent="0.25">
+    <row r="120" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E120" s="1">
         <v>44781.886111111111</v>
       </c>
-      <c r="F120" s="4">
-        <v>9.8737680565131194E-6</v>
-      </c>
-      <c r="G120" s="4">
-        <v>6.1346768815599898E-6</v>
-      </c>
-      <c r="H120" s="4">
-        <v>6.2000553674498902E-6</v>
+      <c r="F120">
+        <v>4.0571525773627098E-4</v>
+      </c>
+      <c r="G120">
+        <v>2.5207519539712002E-4</v>
+      </c>
+      <c r="H120">
+        <v>2.54761611469434E-4</v>
+      </c>
+      <c r="I120">
+        <v>6.4040720625000001</v>
       </c>
     </row>
-    <row r="121" spans="5:8" x14ac:dyDescent="0.25">
+    <row r="121" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E121" s="1">
         <v>44781.896527777775</v>
       </c>
-      <c r="F121" s="4">
-        <v>3.62543062105412E-6</v>
-      </c>
-      <c r="G121" s="4">
-        <v>2.5855560562754599E-6</v>
-      </c>
-      <c r="H121" s="4">
-        <v>2.58084513039978E-6</v>
+      <c r="F121">
+        <v>1.68088015066737E-4</v>
+      </c>
+      <c r="G121">
+        <v>1.1987568671669899E-4</v>
+      </c>
+      <c r="H121">
+        <v>1.19657271234632E-4</v>
+      </c>
+      <c r="I121">
+        <v>5.2612970189999997</v>
       </c>
     </row>
-    <row r="122" spans="5:8" x14ac:dyDescent="0.25">
+    <row r="122" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E122" s="1">
         <v>44781.906944444447</v>
       </c>
-      <c r="F122" s="4">
-        <v>5.1770196379375703E-6</v>
-      </c>
-      <c r="G122" s="4">
-        <v>3.1745913603245098E-6</v>
-      </c>
-      <c r="H122" s="4">
-        <v>3.0173175094738999E-6</v>
+      <c r="F122">
+        <v>2.33899170623301E-4</v>
+      </c>
+      <c r="G122">
+        <v>1.43428910490146E-4</v>
+      </c>
+      <c r="H122">
+        <v>1.36323234669229E-4</v>
+      </c>
+      <c r="I122">
+        <v>5.4874552459999997</v>
       </c>
     </row>
-    <row r="123" spans="5:8" x14ac:dyDescent="0.25">
+    <row r="123" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E123" s="1">
         <v>44781.917361111111</v>
       </c>
-      <c r="F123" s="4">
-        <v>4.1364578452331496E-6</v>
-      </c>
-      <c r="G123" s="4">
-        <v>2.6973673674495002E-6</v>
-      </c>
-      <c r="H123" s="4">
-        <v>2.66184554854633E-6</v>
+      <c r="F123">
+        <v>1.92992886362459E-4</v>
+      </c>
+      <c r="G123">
+        <v>1.25849877671578E-4</v>
+      </c>
+      <c r="H123">
+        <v>1.2419255185894699E-4</v>
+      </c>
+      <c r="I123">
+        <v>5.2076250220000002</v>
       </c>
     </row>
-    <row r="124" spans="5:8" x14ac:dyDescent="0.25">
+    <row r="124" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E124" s="1">
         <v>44781.927777777775</v>
       </c>
-      <c r="F124" s="4">
-        <v>2.24225319101812E-6</v>
+      <c r="F124">
+        <v>1.12462603863556E-4</v>
       </c>
       <c r="G124" s="4">
-        <v>1.6233024868994E-6</v>
+        <v>8.1418470166016497E-5</v>
       </c>
       <c r="H124" s="4">
-        <v>1.59912114367056E-6</v>
+        <v>8.0205629064744003E-5</v>
+      </c>
+      <c r="I124">
+        <v>4.6292118670000004</v>
       </c>
     </row>
-    <row r="125" spans="5:8" x14ac:dyDescent="0.25">
+    <row r="125" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E125" s="1">
         <v>44781.938194444447</v>
       </c>
       <c r="F125" s="4">
-        <v>1.1273321181959501E-6</v>
+        <v>6.3383183853455395E-5</v>
       </c>
       <c r="G125" s="4">
-        <v>7.4225391034485196E-7</v>
+        <v>4.1732525229678299E-5</v>
       </c>
       <c r="H125" s="4">
-        <v>7.4792324404798199E-7</v>
+        <v>4.20512781631517E-5</v>
+      </c>
+      <c r="I125">
+        <v>3.8438540350000001</v>
       </c>
     </row>
-    <row r="126" spans="5:8" x14ac:dyDescent="0.25">
+    <row r="126" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E126" s="1">
         <v>44781.948611111111</v>
       </c>
       <c r="F126" s="4">
-        <v>9.824868098894941E-7</v>
+        <v>5.8607773952383203E-5</v>
       </c>
       <c r="G126" s="4">
-        <v>5.0977265297958797E-7</v>
+        <v>3.0409202559192099E-5</v>
       </c>
       <c r="H126" s="4">
-        <v>5.07336801346938E-7</v>
+        <v>3.0263897970125302E-5</v>
+      </c>
+      <c r="I126">
+        <v>3.4907628965000002</v>
       </c>
     </row>
-    <row r="127" spans="5:8" x14ac:dyDescent="0.25">
+    <row r="127" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E127" s="1">
         <v>44781.959027777775</v>
       </c>
       <c r="F127" s="4">
-        <v>7.1336422085263801E-7</v>
+        <v>4.2298990704275399E-5</v>
       </c>
       <c r="G127" s="4">
-        <v>4.9967568047369495E-7</v>
+        <v>2.9628310960811101E-5</v>
       </c>
       <c r="H127" s="4">
-        <v>4.8813559378618197E-7</v>
+        <v>2.8944040562241099E-5</v>
+      </c>
+      <c r="I127">
+        <v>3.5250784804999999</v>
       </c>
     </row>
-    <row r="128" spans="5:8" x14ac:dyDescent="0.25">
+    <row r="128" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E128" s="1">
         <v>44781.969444444447</v>
       </c>
       <c r="F128" s="4">
-        <v>6.4931726402399996E-7</v>
+        <v>3.99181931276714E-5</v>
       </c>
       <c r="G128" s="4">
-        <v>4.11723051732112E-7</v>
+        <v>2.5311571406873598E-5</v>
       </c>
       <c r="H128" s="4">
-        <v>4.0816101818634101E-7</v>
+        <v>2.50925876364046E-5</v>
+      </c>
+      <c r="I128">
+        <v>3.3236783504999998</v>
       </c>
     </row>
-    <row r="129" spans="5:8" x14ac:dyDescent="0.25">
+    <row r="129" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E129" s="1">
         <v>44781.979861111111</v>
       </c>
       <c r="F129" s="4">
-        <v>5.2154391813663602E-7</v>
+        <v>3.2476970798245197E-5</v>
       </c>
       <c r="G129" s="4">
-        <v>3.7467868921224398E-7</v>
+        <v>2.3331551620226199E-5</v>
       </c>
       <c r="H129" s="4">
-        <v>3.6512831001573099E-7</v>
+        <v>2.2736841615560799E-5</v>
+      </c>
+      <c r="I129">
+        <v>3.2549971329999998</v>
       </c>
     </row>
-    <row r="130" spans="5:8" x14ac:dyDescent="0.25">
+    <row r="130" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E130" s="1">
         <v>44781.990277777775</v>
       </c>
       <c r="F130" s="4">
-        <v>6.7490505910082797E-7</v>
+        <v>4.1444873674415303E-5</v>
       </c>
       <c r="G130" s="4">
-        <v>4.1927363607223701E-7</v>
+        <v>2.5746944178216301E-5</v>
       </c>
       <c r="H130" s="4">
-        <v>4.0834177343066002E-7</v>
+        <v>2.5075635436668602E-5</v>
+      </c>
+      <c r="I130">
+        <v>3.3297358964999999</v>
       </c>
     </row>
-    <row r="131" spans="5:8" x14ac:dyDescent="0.25">
+    <row r="131" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E131" s="1">
         <v>44782.000694444447</v>
       </c>
       <c r="F131" s="4">
-        <v>6.6541966892078898E-7</v>
+        <v>4.0574092826454099E-5</v>
       </c>
       <c r="G131" s="4">
-        <v>4.4769911489172599E-7</v>
+        <v>2.72985399959777E-5</v>
       </c>
       <c r="H131" s="4">
-        <v>4.44382696822977E-7</v>
+        <v>2.7096320763431098E-5</v>
+      </c>
+      <c r="I131">
+        <v>3.3683360045000001</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
+  <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>